--- a/03_Time_Plans/L3_Tooling.xlsx
+++ b/03_Time_Plans/L3_Tooling.xlsx
@@ -1243,7 +1243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21"/>
   </cellStyleXfs>
-  <cellXfs count="184">
+  <cellXfs count="185">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -1668,11 +1668,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyAlignment="1" applyBorder="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="74">
+  <dxfs count="81">
     <dxf>
       <border>
         <left style="thick">
@@ -2521,6 +2524,89 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE74B3B"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF1F2430"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFED7D31"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FF1F2430"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF70AD47"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF4472C4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF9B59B6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFFFFFF"/>
+        <sz val="9"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF98A2B3"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2782,18 +2868,19 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" style="113" min="1" max="1"/>
-    <col width="2.42578125" customWidth="1" style="113" min="3" max="3"/>
+    <col width="12" customWidth="1" style="113" min="3" max="3"/>
     <col width="5" customWidth="1" style="113" min="4" max="4"/>
     <col width="51" bestFit="1" customWidth="1" style="113" min="5" max="5"/>
     <col width="14" customWidth="1" style="113" min="6" max="6"/>
-    <col width="16" customWidth="1" style="113" min="7" max="7"/>
-    <col width="8.140625" customWidth="1" style="113" min="8" max="11"/>
-    <col width="12" customWidth="1" style="113" min="12" max="12"/>
-    <col width="18" customWidth="1" style="113" min="13" max="13"/>
-    <col width="30" customWidth="1" style="113" min="14" max="14"/>
-    <col width="34" customWidth="1" style="113" min="15" max="15"/>
-    <col width="4" customWidth="1" style="113" min="23" max="23"/>
-    <col width="13" customWidth="1" style="113" min="24" max="25"/>
+    <col width="20" customWidth="1" style="113" min="7" max="7"/>
+    <col width="16" customWidth="1" style="113" min="8" max="8"/>
+    <col width="8.140625" customWidth="1" style="113" min="9" max="12"/>
+    <col width="12" customWidth="1" style="113" min="13" max="13"/>
+    <col width="18" customWidth="1" style="113" min="14" max="14"/>
+    <col width="30" customWidth="1" style="113" min="15" max="15"/>
+    <col width="34" customWidth="1" style="113" min="16" max="16"/>
+    <col width="4" customWidth="1" style="113" min="24" max="24"/>
+    <col width="13" customWidth="1" style="113" min="25" max="26"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" s="113" thickBot="1"/>
@@ -2960,7 +3047,11 @@
       <c r="V5" s="79" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1" s="113" thickBot="1">
-      <c r="C6" s="7" t="n"/>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colour</t>
+        </is>
+      </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
           <t>No.</t>
@@ -2978,52 +3069,61 @@
       </c>
       <c r="G6" s="7" t="inlineStr">
         <is>
+          <t xml:space="preserve">Department</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>Location</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>Start Wk</t>
         </is>
       </c>
-      <c r="I6" s="7" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Start Yr</t>
         </is>
       </c>
-      <c r="J6" s="7" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>End Wk</t>
         </is>
       </c>
-      <c r="K6" s="7" t="inlineStr">
+      <c r="L6" s="7" t="inlineStr">
         <is>
           <t>End Yr</t>
         </is>
       </c>
-      <c r="L6" s="7" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>Tracker</t>
         </is>
       </c>
-      <c r="M6" s="7" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="N6" s="7" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t>Comments / Notes</t>
         </is>
       </c>
-      <c r="O6" s="7" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>Dependencies</t>
         </is>
       </c>
     </row>
     <row r="7" ht="19.5" customHeight="1" s="113">
-      <c r="C7" s="8" t="n"/>
+      <c r="C7" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Blue</t>
+        </is>
+      </c>
       <c r="D7" s="82">
         <v>1</v>
       </c>
@@ -3039,43 +3139,52 @@
       </c>
       <c r="G7" s="84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tooling &amp; Dies</t>
+        </is>
+      </c>
+      <c r="H7" s="84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remote</t>
         </is>
       </c>
-      <c r="H7" s="84">
-        <v>9</v>
-      </c>
       <c r="I7" s="84">
+        <v>20</v>
+      </c>
+      <c r="J7" s="84">
         <v>2026</v>
       </c>
-      <c r="J7" s="84">
-        <v>12</v>
-      </c>
       <c r="K7" s="84">
+        <v>24</v>
+      </c>
+      <c r="L7" s="84">
         <v>2026</v>
       </c>
-      <c r="L7" s="85">
-        <f>IF(E7="","",IF(M7="Completed","On Track",IF(OR(J7="",K7=""),"",IF(($V$3*100+$U$3)&gt;(K7*100+J7),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M7" s="84" t="inlineStr">
+      <c r="M7" s="85">
+        <f>IF($E7="","",IF($N7="Completed","Completed",IF(OR($K7="",$L7=""),"",IF(TODAY()&gt;DATE($L7,1,4)-WEEKDAY(DATE($L7,1,4),3)+($K7-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L7,1,4)-WEEKDAY(DATE($L7,1,4),3)+($K7-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L7,1,4)-WEEKDAY(DATE($L7,1,4),3)+($K7-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N7" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">Completed</t>
         </is>
       </c>
-      <c r="N7" s="86" t="inlineStr">
+      <c r="O7" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O7" s="86" t="inlineStr">
+      <c r="P7" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve">L2_Bodyshop-1</t>
         </is>
       </c>
     </row>
     <row r="8" ht="19.5" customHeight="1" s="113">
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow</t>
+        </is>
+      </c>
       <c r="D8" s="10">
         <v>2</v>
       </c>
@@ -3091,43 +3200,52 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tooling &amp; Dies</t>
+        </is>
+      </c>
+      <c r="H8" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Remote</t>
         </is>
       </c>
-      <c r="H8" s="12">
-        <v>13</v>
-      </c>
       <c r="I8" s="12">
+        <v>25</v>
+      </c>
+      <c r="J8" s="12">
         <v>2026</v>
       </c>
-      <c r="J8" s="12">
-        <v>18</v>
-      </c>
       <c r="K8" s="12">
+        <v>30</v>
+      </c>
+      <c r="L8" s="12">
         <v>2026</v>
       </c>
-      <c r="L8" s="13">
-        <f>IF(E8="","",IF(M8="Completed","On Track",IF(OR(J8="",K8=""),"",IF(($V$3*100+$U$3)&gt;(K8*100+J8),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M8" s="12" t="inlineStr">
+      <c r="M8" s="13">
+        <f>IF($E8="","",IF($N8="Completed","Completed",IF(OR($K8="",$L8=""),"",IF(TODAY()&gt;DATE($L8,1,4)-WEEKDAY(DATE($L8,1,4),3)+($K8-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L8,1,4)-WEEKDAY(DATE($L8,1,4),3)+($K8-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L8,1,4)-WEEKDAY(DATE($L8,1,4),3)+($K8-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N8" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aligned</t>
+          <t xml:space="preserve">Completed</t>
         </is>
       </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="P8" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">L3_Tooling-1</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="9" ht="19.5" customHeight="1" s="113">
-      <c r="C9" s="15" t="n"/>
+      <c r="C9" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Green</t>
+        </is>
+      </c>
       <c r="D9" s="87">
         <v>3</v>
       </c>
@@ -3143,43 +3261,52 @@
       </c>
       <c r="G9" s="84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tooling &amp; Dies</t>
+        </is>
+      </c>
+      <c r="H9" s="84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suzhou</t>
         </is>
       </c>
-      <c r="H9" s="84">
-        <v>19</v>
-      </c>
       <c r="I9" s="84">
+        <v>31</v>
+      </c>
+      <c r="J9" s="84">
         <v>2026</v>
       </c>
-      <c r="J9" s="84">
-        <v>28</v>
-      </c>
       <c r="K9" s="84">
+        <v>40</v>
+      </c>
+      <c r="L9" s="84">
         <v>2026</v>
       </c>
-      <c r="L9" s="85">
-        <f>IF(E9="","",IF(M9="Completed","On Track",IF(OR(J9="",K9=""),"",IF(($V$3*100+$U$3)&gt;(K9*100+J9),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M9" s="84" t="inlineStr">
+      <c r="M9" s="85">
+        <f>IF($E9="","",IF($N9="Completed","Completed",IF(OR($K9="",$L9=""),"",IF(TODAY()&gt;DATE($L9,1,4)-WEEKDAY(DATE($L9,1,4),3)+($K9-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L9,1,4)-WEEKDAY(DATE($L9,1,4),3)+($K9-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L9,1,4)-WEEKDAY(DATE($L9,1,4),3)+($K9-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N9" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">Risk</t>
         </is>
       </c>
-      <c r="N9" s="86" t="inlineStr">
+      <c r="O9" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O9" s="86" t="inlineStr">
+      <c r="P9" s="86" t="inlineStr">
         <is>
-          <t xml:space="preserve">L3_Tooling-2; L5_Supplier_A-3</t>
+          <t xml:space="preserve">L2_Bodyshop-3</t>
         </is>
       </c>
     </row>
     <row r="10" ht="19.5" customHeight="1" s="113">
-      <c r="C10" s="16" t="n"/>
+      <c r="C10" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Yellow</t>
+        </is>
+      </c>
       <c r="D10" s="17">
         <v>4</v>
       </c>
@@ -3195,43 +3322,52 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tooling &amp; Dies</t>
+        </is>
+      </c>
+      <c r="H10" s="12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Suzhou</t>
         </is>
       </c>
-      <c r="H10" s="12">
-        <v>29</v>
-      </c>
       <c r="I10" s="12">
+        <v>41</v>
+      </c>
+      <c r="J10" s="12">
         <v>2026</v>
       </c>
-      <c r="J10" s="12">
-        <v>34</v>
-      </c>
       <c r="K10" s="12">
+        <v>44</v>
+      </c>
+      <c r="L10" s="12">
         <v>2026</v>
       </c>
-      <c r="L10" s="13">
-        <f>IF(E10="","",IF(M10="Completed","On Track",IF(OR(J10="",K10=""),"",IF(($V$3*100+$U$3)&gt;(K10*100+J10),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M10" s="12" t="inlineStr">
+      <c r="M10" s="13">
+        <f>IF($E10="","",IF($N10="Completed","Completed",IF(OR($K10="",$L10=""),"",IF(TODAY()&gt;DATE($L10,1,4)-WEEKDAY(DATE($L10,1,4),3)+($K10-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L10,1,4)-WEEKDAY(DATE($L10,1,4),3)+($K10-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L10,1,4)-WEEKDAY(DATE($L10,1,4),3)+($K10-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N10" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Planned</t>
         </is>
       </c>
-      <c r="N10" s="14" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O10" s="14" t="inlineStr">
+      <c r="P10" s="14" t="inlineStr">
         <is>
-          <t xml:space="preserve">L3_Tooling-3</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
     </row>
     <row r="11" ht="19.5" customHeight="1" s="113">
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Red</t>
+        </is>
+      </c>
       <c r="D11" s="88">
         <v>5</v>
       </c>
@@ -3247,43 +3383,48 @@
       </c>
       <c r="G11" s="84" t="inlineStr">
         <is>
+          <t xml:space="preserve">Tooling &amp; Dies</t>
+        </is>
+      </c>
+      <c r="H11" s="84" t="inlineStr">
+        <is>
           <t xml:space="preserve">Gothenburg</t>
         </is>
       </c>
-      <c r="H11" s="84">
-        <v>35</v>
-      </c>
       <c r="I11" s="84">
+        <v>43</v>
+      </c>
+      <c r="J11" s="84">
         <v>2026</v>
       </c>
-      <c r="J11" s="84">
-        <v>38</v>
-      </c>
       <c r="K11" s="84">
+        <v>48</v>
+      </c>
+      <c r="L11" s="84">
         <v>2026</v>
       </c>
-      <c r="L11" s="85">
-        <f>IF(E11="","",IF(M11="Completed","On Track",IF(OR(J11="",K11=""),"",IF(($V$3*100+$U$3)&gt;(K11*100+J11),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M11" s="84" t="inlineStr">
+      <c r="M11" s="85">
+        <f>IF($E11="","",IF($N11="Completed","Completed",IF(OR($K11="",$L11=""),"",IF(TODAY()&gt;DATE($L11,1,4)-WEEKDAY(DATE($L11,1,4),3)+($K11-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L11,1,4)-WEEKDAY(DATE($L11,1,4),3)+($K11-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L11,1,4)-WEEKDAY(DATE($L11,1,4),3)+($K11-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N11" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve">TBD</t>
         </is>
       </c>
-      <c r="N11" s="86" t="inlineStr">
+      <c r="O11" s="86" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="O11" s="86" t="inlineStr">
+      <c r="P11" s="86" t="inlineStr">
         <is>
-          <t xml:space="preserve">L3_Tooling-4</t>
+          <t xml:space="preserve">L2_Bodyshop-5</t>
         </is>
       </c>
     </row>
     <row r="12" ht="19.5" customHeight="1" s="113">
-      <c r="C12" s="19" t="n"/>
+      <c r="C12" s="184"/>
       <c r="D12" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3299,11 +3440,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G12" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G12" s="12" t="n"/>
       <c r="H12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3324,16 +3461,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L12" s="13">
-        <f>IF(E12="","",IF(M12="Completed","On Track",IF(OR(J12="",K12=""),"",IF(($V$3*100+$U$3)&gt;(K12*100+J12),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M12" s="12" t="inlineStr">
+      <c r="L12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N12" s="14" t="inlineStr">
+      <c r="M12" s="13">
+        <f>IF($E12="","",IF($N12="Completed","Completed",IF(OR($K12="",$L12=""),"",IF(TODAY()&gt;DATE($L12,1,4)-WEEKDAY(DATE($L12,1,4),3)+($K12-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L12,1,4)-WEEKDAY(DATE($L12,1,4),3)+($K12-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L12,1,4)-WEEKDAY(DATE($L12,1,4),3)+($K12-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N12" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3343,9 +3480,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P12" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="13" ht="19.5" customHeight="1" s="113">
-      <c r="C13" s="21" t="n"/>
+      <c r="C13" s="184"/>
       <c r="D13" s="89" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3361,11 +3503,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G13" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G13" s="84" t="n"/>
       <c r="H13" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3386,16 +3524,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L13" s="85">
-        <f>IF(E13="","",IF(M13="Completed","On Track",IF(OR(J13="",K13=""),"",IF(($V$3*100+$U$3)&gt;(K13*100+J13),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M13" s="84" t="inlineStr">
+      <c r="L13" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N13" s="86" t="inlineStr">
+      <c r="M13" s="85">
+        <f>IF($E13="","",IF($N13="Completed","Completed",IF(OR($K13="",$L13=""),"",IF(TODAY()&gt;DATE($L13,1,4)-WEEKDAY(DATE($L13,1,4),3)+($K13-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L13,1,4)-WEEKDAY(DATE($L13,1,4),3)+($K13-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L13,1,4)-WEEKDAY(DATE($L13,1,4),3)+($K13-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N13" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3405,9 +3543,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P13" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="14" ht="19.5" customHeight="1" s="113">
-      <c r="C14" s="174" t="n"/>
+      <c r="C14" s="184"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3423,11 +3566,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G14" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G14" s="12" t="n"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3448,16 +3587,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L14" s="13">
-        <f>IF(E14="","",IF(M14="Completed","On Track",IF(OR(J14="",K14=""),"",IF(($V$3*100+$U$3)&gt;(K14*100+J14),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M14" s="12" t="inlineStr">
+      <c r="L14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N14" s="14" t="inlineStr">
+      <c r="M14" s="13">
+        <f>IF($E14="","",IF($N14="Completed","Completed",IF(OR($K14="",$L14=""),"",IF(TODAY()&gt;DATE($L14,1,4)-WEEKDAY(DATE($L14,1,4),3)+($K14-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L14,1,4)-WEEKDAY(DATE($L14,1,4),3)+($K14-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L14,1,4)-WEEKDAY(DATE($L14,1,4),3)+($K14-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N14" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3467,9 +3606,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P14" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="15" ht="19.5" customHeight="1" s="113">
-      <c r="C15" s="24" t="n"/>
+      <c r="C15" s="184"/>
       <c r="D15" s="90" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3485,11 +3629,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G15" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G15" s="84" t="n"/>
       <c r="H15" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3510,16 +3650,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L15" s="85">
-        <f>IF(E15="","",IF(M15="Completed","On Track",IF(OR(J15="",K15=""),"",IF(($V$3*100+$U$3)&gt;(K15*100+J15),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M15" s="84" t="inlineStr">
+      <c r="L15" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N15" s="86" t="inlineStr">
+      <c r="M15" s="85">
+        <f>IF($E15="","",IF($N15="Completed","Completed",IF(OR($K15="",$L15=""),"",IF(TODAY()&gt;DATE($L15,1,4)-WEEKDAY(DATE($L15,1,4),3)+($K15-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L15,1,4)-WEEKDAY(DATE($L15,1,4),3)+($K15-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L15,1,4)-WEEKDAY(DATE($L15,1,4),3)+($K15-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N15" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3529,9 +3669,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P15" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="16" ht="19.5" customHeight="1" s="113">
-      <c r="C16" s="25" t="n"/>
+      <c r="C16" s="184"/>
       <c r="D16" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3547,11 +3692,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G16" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G16" s="12" t="n"/>
       <c r="H16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3572,16 +3713,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L16" s="13">
-        <f>IF(E16="","",IF(M16="Completed","On Track",IF(OR(J16="",K16=""),"",IF(($V$3*100+$U$3)&gt;(K16*100+J16),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M16" s="12" t="inlineStr">
+      <c r="L16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N16" s="14" t="inlineStr">
+      <c r="M16" s="13">
+        <f>IF($E16="","",IF($N16="Completed","Completed",IF(OR($K16="",$L16=""),"",IF(TODAY()&gt;DATE($L16,1,4)-WEEKDAY(DATE($L16,1,4),3)+($K16-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L16,1,4)-WEEKDAY(DATE($L16,1,4),3)+($K16-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L16,1,4)-WEEKDAY(DATE($L16,1,4),3)+($K16-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N16" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3591,9 +3732,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P16" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="17" ht="19.5" customHeight="1" s="113">
-      <c r="C17" s="27" t="n"/>
+      <c r="C17" s="184"/>
       <c r="D17" s="91" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3609,11 +3755,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G17" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G17" s="84" t="n"/>
       <c r="H17" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3634,16 +3776,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L17" s="85">
-        <f>IF(E17="","",IF(M17="Completed","On Track",IF(OR(J17="",K17=""),"",IF(($V$3*100+$U$3)&gt;(K17*100+J17),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M17" s="84" t="inlineStr">
+      <c r="L17" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N17" s="86" t="inlineStr">
+      <c r="M17" s="85">
+        <f>IF($E17="","",IF($N17="Completed","Completed",IF(OR($K17="",$L17=""),"",IF(TODAY()&gt;DATE($L17,1,4)-WEEKDAY(DATE($L17,1,4),3)+($K17-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L17,1,4)-WEEKDAY(DATE($L17,1,4),3)+($K17-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L17,1,4)-WEEKDAY(DATE($L17,1,4),3)+($K17-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N17" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3653,9 +3795,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P17" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="18" ht="19.5" customHeight="1" s="113">
-      <c r="C18" s="28" t="n"/>
+      <c r="C18" s="184"/>
       <c r="D18" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3671,11 +3818,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G18" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G18" s="12" t="n"/>
       <c r="H18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3696,16 +3839,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L18" s="13">
-        <f>IF(E18="","",IF(M18="Completed","On Track",IF(OR(J18="",K18=""),"",IF(($V$3*100+$U$3)&gt;(K18*100+J18),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M18" s="12" t="inlineStr">
+      <c r="L18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N18" s="14" t="inlineStr">
+      <c r="M18" s="13">
+        <f>IF($E18="","",IF($N18="Completed","Completed",IF(OR($K18="",$L18=""),"",IF(TODAY()&gt;DATE($L18,1,4)-WEEKDAY(DATE($L18,1,4),3)+($K18-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L18,1,4)-WEEKDAY(DATE($L18,1,4),3)+($K18-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L18,1,4)-WEEKDAY(DATE($L18,1,4),3)+($K18-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N18" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3715,9 +3858,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P18" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="19" ht="19.5" customHeight="1" s="113">
-      <c r="C19" s="30" t="n"/>
+      <c r="C19" s="184"/>
       <c r="D19" s="92" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3733,11 +3881,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G19" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G19" s="84" t="n"/>
       <c r="H19" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3758,16 +3902,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L19" s="85">
-        <f>IF(E19="","",IF(M19="Completed","On Track",IF(OR(J19="",K19=""),"",IF(($V$3*100+$U$3)&gt;(K19*100+J19),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M19" s="84" t="inlineStr">
+      <c r="L19" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N19" s="86" t="inlineStr">
+      <c r="M19" s="85">
+        <f>IF($E19="","",IF($N19="Completed","Completed",IF(OR($K19="",$L19=""),"",IF(TODAY()&gt;DATE($L19,1,4)-WEEKDAY(DATE($L19,1,4),3)+($K19-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L19,1,4)-WEEKDAY(DATE($L19,1,4),3)+($K19-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L19,1,4)-WEEKDAY(DATE($L19,1,4),3)+($K19-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N19" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3777,9 +3921,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P19" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="20" ht="19.5" customHeight="1" s="113">
-      <c r="C20" s="31" t="n"/>
+      <c r="C20" s="184"/>
       <c r="D20" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3795,11 +3944,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G20" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G20" s="12" t="n"/>
       <c r="H20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3820,16 +3965,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L20" s="13">
-        <f>IF(E20="","",IF(M20="Completed","On Track",IF(OR(J20="",K20=""),"",IF(($V$3*100+$U$3)&gt;(K20*100+J20),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M20" s="12" t="inlineStr">
+      <c r="L20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N20" s="14" t="inlineStr">
+      <c r="M20" s="13">
+        <f>IF($E20="","",IF($N20="Completed","Completed",IF(OR($K20="",$L20=""),"",IF(TODAY()&gt;DATE($L20,1,4)-WEEKDAY(DATE($L20,1,4),3)+($K20-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L20,1,4)-WEEKDAY(DATE($L20,1,4),3)+($K20-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L20,1,4)-WEEKDAY(DATE($L20,1,4),3)+($K20-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N20" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3839,9 +3984,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P20" s="14" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="21" ht="19.5" customHeight="1" s="113">
-      <c r="C21" s="33" t="n"/>
+      <c r="C21" s="184"/>
       <c r="D21" s="93" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3857,11 +4007,7 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="G21" s="84" t="inlineStr">
-        <is>
-          <t xml:space="preserve"/>
-        </is>
-      </c>
+      <c r="G21" s="84" t="n"/>
       <c r="H21" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
@@ -3882,16 +4028,16 @@
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="L21" s="85">
-        <f>IF(E21="","",IF(M21="Completed","On Track",IF(OR(J21="",K21=""),"",IF(($V$3*100+$U$3)&gt;(K21*100+J21),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M21" s="84" t="inlineStr">
+      <c r="L21" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
       </c>
-      <c r="N21" s="86" t="inlineStr">
+      <c r="M21" s="85">
+        <f>IF($E21="","",IF($N21="Completed","Completed",IF(OR($K21="",$L21=""),"",IF(TODAY()&gt;DATE($L21,1,4)-WEEKDAY(DATE($L21,1,4),3)+($K21-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L21,1,4)-WEEKDAY(DATE($L21,1,4),3)+($K21-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L21,1,4)-WEEKDAY(DATE($L21,1,4),3)+($K21-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N21" s="84" t="inlineStr">
         <is>
           <t xml:space="preserve"/>
         </is>
@@ -3901,9 +4047,14 @@
           <t xml:space="preserve"/>
         </is>
       </c>
+      <c r="P21" s="86" t="inlineStr">
+        <is>
+          <t xml:space="preserve"/>
+        </is>
+      </c>
     </row>
     <row r="22" ht="19.5" customHeight="1" s="113">
-      <c r="C22" s="34" t="n"/>
+      <c r="C22" s="184"/>
       <c r="D22" s="35" t="n">
         <v>16</v>
       </c>
@@ -3914,16 +4065,17 @@
       <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
       <c r="K22" s="12" t="n"/>
-      <c r="L22" s="13">
-        <f>IF(E22="","",IF(M22="Completed","On Track",IF(OR(J22="",K22=""),"",IF(($V$3*100+$U$3)&gt;(K22*100+J22),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M22" s="12" t="n"/>
-      <c r="N22" s="14" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="13">
+        <f>IF($E22="","",IF($N22="Completed","Completed",IF(OR($K22="",$L22=""),"",IF(TODAY()&gt;DATE($L22,1,4)-WEEKDAY(DATE($L22,1,4),3)+($K22-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L22,1,4)-WEEKDAY(DATE($L22,1,4),3)+($K22-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L22,1,4)-WEEKDAY(DATE($L22,1,4),3)+($K22-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N22" s="12" t="n"/>
       <c r="O22" s="14" t="n"/>
+      <c r="P22" s="14" t="n"/>
     </row>
     <row r="23" ht="19.5" customHeight="1" s="113">
-      <c r="C23" s="36" t="n"/>
+      <c r="C23" s="184"/>
       <c r="D23" s="94" t="n">
         <v>17</v>
       </c>
@@ -3934,16 +4086,17 @@
       <c r="I23" s="84" t="n"/>
       <c r="J23" s="84" t="n"/>
       <c r="K23" s="84" t="n"/>
-      <c r="L23" s="85">
-        <f>IF(E23="","",IF(M23="Completed","On Track",IF(OR(J23="",K23=""),"",IF(($V$3*100+$U$3)&gt;(K23*100+J23),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M23" s="84" t="n"/>
-      <c r="N23" s="86" t="n"/>
+      <c r="L23" s="84" t="n"/>
+      <c r="M23" s="85">
+        <f>IF($E23="","",IF($N23="Completed","Completed",IF(OR($K23="",$L23=""),"",IF(TODAY()&gt;DATE($L23,1,4)-WEEKDAY(DATE($L23,1,4),3)+($K23-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L23,1,4)-WEEKDAY(DATE($L23,1,4),3)+($K23-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L23,1,4)-WEEKDAY(DATE($L23,1,4),3)+($K23-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N23" s="84" t="n"/>
       <c r="O23" s="86" t="n"/>
+      <c r="P23" s="86" t="n"/>
     </row>
     <row r="24" ht="19.5" customHeight="1" s="113">
-      <c r="C24" s="37" t="n"/>
+      <c r="C24" s="184"/>
       <c r="D24" s="38" t="n">
         <v>18</v>
       </c>
@@ -3954,16 +4107,17 @@
       <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
       <c r="K24" s="12" t="n"/>
-      <c r="L24" s="13">
-        <f>IF(E24="","",IF(M24="Completed","On Track",IF(OR(J24="",K24=""),"",IF(($V$3*100+$U$3)&gt;(K24*100+J24),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="14" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="13">
+        <f>IF($E24="","",IF($N24="Completed","Completed",IF(OR($K24="",$L24=""),"",IF(TODAY()&gt;DATE($L24,1,4)-WEEKDAY(DATE($L24,1,4),3)+($K24-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L24,1,4)-WEEKDAY(DATE($L24,1,4),3)+($K24-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L24,1,4)-WEEKDAY(DATE($L24,1,4),3)+($K24-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N24" s="12" t="n"/>
       <c r="O24" s="14" t="n"/>
+      <c r="P24" s="14" t="n"/>
     </row>
     <row r="25" ht="19.5" customHeight="1" s="113">
-      <c r="C25" s="39" t="n"/>
+      <c r="C25" s="184"/>
       <c r="D25" s="95" t="n">
         <v>19</v>
       </c>
@@ -3974,16 +4128,17 @@
       <c r="I25" s="84" t="n"/>
       <c r="J25" s="84" t="n"/>
       <c r="K25" s="84" t="n"/>
-      <c r="L25" s="85">
-        <f>IF(E25="","",IF(M25="Completed","On Track",IF(OR(J25="",K25=""),"",IF(($V$3*100+$U$3)&gt;(K25*100+J25),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M25" s="84" t="n"/>
-      <c r="N25" s="86" t="n"/>
+      <c r="L25" s="84" t="n"/>
+      <c r="M25" s="85">
+        <f>IF($E25="","",IF($N25="Completed","Completed",IF(OR($K25="",$L25=""),"",IF(TODAY()&gt;DATE($L25,1,4)-WEEKDAY(DATE($L25,1,4),3)+($K25-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L25,1,4)-WEEKDAY(DATE($L25,1,4),3)+($K25-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L25,1,4)-WEEKDAY(DATE($L25,1,4),3)+($K25-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N25" s="84" t="n"/>
       <c r="O25" s="86" t="n"/>
+      <c r="P25" s="86" t="n"/>
     </row>
     <row r="26" ht="19.5" customHeight="1" s="113">
-      <c r="C26" s="40" t="n"/>
+      <c r="C26" s="184"/>
       <c r="D26" s="41" t="n">
         <v>20</v>
       </c>
@@ -3994,16 +4149,17 @@
       <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
       <c r="K26" s="12" t="n"/>
-      <c r="L26" s="13">
-        <f>IF(E26="","",IF(M26="Completed","On Track",IF(OR(J26="",K26=""),"",IF(($V$3*100+$U$3)&gt;(K26*100+J26),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="14" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="13">
+        <f>IF($E26="","",IF($N26="Completed","Completed",IF(OR($K26="",$L26=""),"",IF(TODAY()&gt;DATE($L26,1,4)-WEEKDAY(DATE($L26,1,4),3)+($K26-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L26,1,4)-WEEKDAY(DATE($L26,1,4),3)+($K26-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L26,1,4)-WEEKDAY(DATE($L26,1,4),3)+($K26-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N26" s="12" t="n"/>
       <c r="O26" s="14" t="n"/>
+      <c r="P26" s="14" t="n"/>
     </row>
     <row r="27" ht="19.5" customHeight="1" s="113">
-      <c r="C27" s="42" t="n"/>
+      <c r="C27" s="184"/>
       <c r="D27" s="96" t="n">
         <v>21</v>
       </c>
@@ -4014,16 +4170,17 @@
       <c r="I27" s="84" t="n"/>
       <c r="J27" s="84" t="n"/>
       <c r="K27" s="84" t="n"/>
-      <c r="L27" s="85">
-        <f>IF(E27="","",IF(M27="Completed","On Track",IF(OR(J27="",K27=""),"",IF(($V$3*100+$U$3)&gt;(K27*100+J27),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M27" s="84" t="n"/>
-      <c r="N27" s="86" t="n"/>
+      <c r="L27" s="84" t="n"/>
+      <c r="M27" s="85">
+        <f>IF($E27="","",IF($N27="Completed","Completed",IF(OR($K27="",$L27=""),"",IF(TODAY()&gt;DATE($L27,1,4)-WEEKDAY(DATE($L27,1,4),3)+($K27-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L27,1,4)-WEEKDAY(DATE($L27,1,4),3)+($K27-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L27,1,4)-WEEKDAY(DATE($L27,1,4),3)+($K27-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N27" s="84" t="n"/>
       <c r="O27" s="86" t="n"/>
+      <c r="P27" s="86" t="n"/>
     </row>
     <row r="28" ht="19.5" customHeight="1" s="113">
-      <c r="C28" s="175" t="n"/>
+      <c r="C28" s="184"/>
       <c r="D28" s="44" t="n">
         <v>22</v>
       </c>
@@ -4034,16 +4191,17 @@
       <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
       <c r="K28" s="12" t="n"/>
-      <c r="L28" s="13">
-        <f>IF(E28="","",IF(M28="Completed","On Track",IF(OR(J28="",K28=""),"",IF(($V$3*100+$U$3)&gt;(K28*100+J28),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="14" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="13">
+        <f>IF($E28="","",IF($N28="Completed","Completed",IF(OR($K28="",$L28=""),"",IF(TODAY()&gt;DATE($L28,1,4)-WEEKDAY(DATE($L28,1,4),3)+($K28-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L28,1,4)-WEEKDAY(DATE($L28,1,4),3)+($K28-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L28,1,4)-WEEKDAY(DATE($L28,1,4),3)+($K28-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N28" s="12" t="n"/>
       <c r="O28" s="14" t="n"/>
+      <c r="P28" s="14" t="n"/>
     </row>
     <row r="29" ht="19.5" customHeight="1" s="113">
-      <c r="C29" s="176" t="n"/>
+      <c r="C29" s="184"/>
       <c r="D29" s="97" t="n">
         <v>23</v>
       </c>
@@ -4054,16 +4212,17 @@
       <c r="I29" s="84" t="n"/>
       <c r="J29" s="84" t="n"/>
       <c r="K29" s="84" t="n"/>
-      <c r="L29" s="85">
-        <f>IF(E29="","",IF(M29="Completed","On Track",IF(OR(J29="",K29=""),"",IF(($V$3*100+$U$3)&gt;(K29*100+J29),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M29" s="84" t="n"/>
-      <c r="N29" s="86" t="n"/>
+      <c r="L29" s="84" t="n"/>
+      <c r="M29" s="85">
+        <f>IF($E29="","",IF($N29="Completed","Completed",IF(OR($K29="",$L29=""),"",IF(TODAY()&gt;DATE($L29,1,4)-WEEKDAY(DATE($L29,1,4),3)+($K29-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L29,1,4)-WEEKDAY(DATE($L29,1,4),3)+($K29-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L29,1,4)-WEEKDAY(DATE($L29,1,4),3)+($K29-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N29" s="84" t="n"/>
       <c r="O29" s="86" t="n"/>
+      <c r="P29" s="86" t="n"/>
     </row>
     <row r="30" ht="19.5" customHeight="1" s="113">
-      <c r="C30" s="46" t="n"/>
+      <c r="C30" s="184"/>
       <c r="D30" s="47" t="n">
         <v>24</v>
       </c>
@@ -4074,16 +4233,17 @@
       <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
       <c r="K30" s="12" t="n"/>
-      <c r="L30" s="13">
-        <f>IF(E30="","",IF(M30="Completed","On Track",IF(OR(J30="",K30=""),"",IF(($V$3*100+$U$3)&gt;(K30*100+J30),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="14" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="13">
+        <f>IF($E30="","",IF($N30="Completed","Completed",IF(OR($K30="",$L30=""),"",IF(TODAY()&gt;DATE($L30,1,4)-WEEKDAY(DATE($L30,1,4),3)+($K30-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L30,1,4)-WEEKDAY(DATE($L30,1,4),3)+($K30-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L30,1,4)-WEEKDAY(DATE($L30,1,4),3)+($K30-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N30" s="12" t="n"/>
       <c r="O30" s="14" t="n"/>
+      <c r="P30" s="14" t="n"/>
     </row>
     <row r="31" ht="19.5" customHeight="1" s="113">
-      <c r="C31" s="48" t="n"/>
+      <c r="C31" s="184"/>
       <c r="D31" s="98" t="n">
         <v>25</v>
       </c>
@@ -4094,16 +4254,17 @@
       <c r="I31" s="84" t="n"/>
       <c r="J31" s="84" t="n"/>
       <c r="K31" s="84" t="n"/>
-      <c r="L31" s="85">
-        <f>IF(E31="","",IF(M31="Completed","On Track",IF(OR(J31="",K31=""),"",IF(($V$3*100+$U$3)&gt;(K31*100+J31),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M31" s="84" t="n"/>
-      <c r="N31" s="86" t="n"/>
+      <c r="L31" s="84" t="n"/>
+      <c r="M31" s="85">
+        <f>IF($E31="","",IF($N31="Completed","Completed",IF(OR($K31="",$L31=""),"",IF(TODAY()&gt;DATE($L31,1,4)-WEEKDAY(DATE($L31,1,4),3)+($K31-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L31,1,4)-WEEKDAY(DATE($L31,1,4),3)+($K31-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L31,1,4)-WEEKDAY(DATE($L31,1,4),3)+($K31-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N31" s="84" t="n"/>
       <c r="O31" s="86" t="n"/>
+      <c r="P31" s="86" t="n"/>
     </row>
     <row r="32" ht="19.5" customHeight="1" s="113">
-      <c r="C32" s="177" t="n"/>
+      <c r="C32" s="184"/>
       <c r="D32" s="50" t="n">
         <v>26</v>
       </c>
@@ -4114,16 +4275,17 @@
       <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
       <c r="K32" s="12" t="n"/>
-      <c r="L32" s="13">
-        <f>IF(E32="","",IF(M32="Completed","On Track",IF(OR(J32="",K32=""),"",IF(($V$3*100+$U$3)&gt;(K32*100+J32),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="14" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="13">
+        <f>IF($E32="","",IF($N32="Completed","Completed",IF(OR($K32="",$L32=""),"",IF(TODAY()&gt;DATE($L32,1,4)-WEEKDAY(DATE($L32,1,4),3)+($K32-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L32,1,4)-WEEKDAY(DATE($L32,1,4),3)+($K32-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L32,1,4)-WEEKDAY(DATE($L32,1,4),3)+($K32-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N32" s="12" t="n"/>
       <c r="O32" s="14" t="n"/>
+      <c r="P32" s="14" t="n"/>
     </row>
     <row r="33" ht="19.5" customHeight="1" s="113">
-      <c r="C33" s="51" t="n"/>
+      <c r="C33" s="184"/>
       <c r="D33" s="99" t="n">
         <v>27</v>
       </c>
@@ -4134,16 +4296,17 @@
       <c r="I33" s="84" t="n"/>
       <c r="J33" s="84" t="n"/>
       <c r="K33" s="84" t="n"/>
-      <c r="L33" s="85">
-        <f>IF(E33="","",IF(M33="Completed","On Track",IF(OR(J33="",K33=""),"",IF(($V$3*100+$U$3)&gt;(K33*100+J33),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M33" s="84" t="n"/>
-      <c r="N33" s="86" t="n"/>
+      <c r="L33" s="84" t="n"/>
+      <c r="M33" s="85">
+        <f>IF($E33="","",IF($N33="Completed","Completed",IF(OR($K33="",$L33=""),"",IF(TODAY()&gt;DATE($L33,1,4)-WEEKDAY(DATE($L33,1,4),3)+($K33-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L33,1,4)-WEEKDAY(DATE($L33,1,4),3)+($K33-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L33,1,4)-WEEKDAY(DATE($L33,1,4),3)+($K33-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N33" s="84" t="n"/>
       <c r="O33" s="86" t="n"/>
+      <c r="P33" s="86" t="n"/>
     </row>
     <row r="34" ht="19.5" customHeight="1" s="113">
-      <c r="C34" s="52" t="n"/>
+      <c r="C34" s="184"/>
       <c r="D34" s="53" t="n">
         <v>28</v>
       </c>
@@ -4154,16 +4317,17 @@
       <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
       <c r="K34" s="12" t="n"/>
-      <c r="L34" s="13">
-        <f>IF(E34="","",IF(M34="Completed","On Track",IF(OR(J34="",K34=""),"",IF(($V$3*100+$U$3)&gt;(K34*100+J34),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="14" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="13">
+        <f>IF($E34="","",IF($N34="Completed","Completed",IF(OR($K34="",$L34=""),"",IF(TODAY()&gt;DATE($L34,1,4)-WEEKDAY(DATE($L34,1,4),3)+($K34-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L34,1,4)-WEEKDAY(DATE($L34,1,4),3)+($K34-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L34,1,4)-WEEKDAY(DATE($L34,1,4),3)+($K34-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N34" s="12" t="n"/>
       <c r="O34" s="14" t="n"/>
+      <c r="P34" s="14" t="n"/>
     </row>
     <row r="35" ht="19.5" customHeight="1" s="113">
-      <c r="C35" s="54" t="n"/>
+      <c r="C35" s="184"/>
       <c r="D35" s="100" t="n">
         <v>29</v>
       </c>
@@ -4174,16 +4338,17 @@
       <c r="I35" s="84" t="n"/>
       <c r="J35" s="84" t="n"/>
       <c r="K35" s="84" t="n"/>
-      <c r="L35" s="85">
-        <f>IF(E35="","",IF(M35="Completed","On Track",IF(OR(J35="",K35=""),"",IF(($V$3*100+$U$3)&gt;(K35*100+J35),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M35" s="84" t="n"/>
-      <c r="N35" s="86" t="n"/>
+      <c r="L35" s="84" t="n"/>
+      <c r="M35" s="85">
+        <f>IF($E35="","",IF($N35="Completed","Completed",IF(OR($K35="",$L35=""),"",IF(TODAY()&gt;DATE($L35,1,4)-WEEKDAY(DATE($L35,1,4),3)+($K35-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L35,1,4)-WEEKDAY(DATE($L35,1,4),3)+($K35-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L35,1,4)-WEEKDAY(DATE($L35,1,4),3)+($K35-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N35" s="84" t="n"/>
       <c r="O35" s="86" t="n"/>
+      <c r="P35" s="86" t="n"/>
     </row>
     <row r="36" ht="19.5" customHeight="1" s="113">
-      <c r="C36" s="178" t="n"/>
+      <c r="C36" s="184"/>
       <c r="D36" s="56" t="n">
         <v>30</v>
       </c>
@@ -4194,16 +4359,17 @@
       <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
       <c r="K36" s="12" t="n"/>
-      <c r="L36" s="13">
-        <f>IF(E36="","",IF(M36="Completed","On Track",IF(OR(J36="",K36=""),"",IF(($V$3*100+$U$3)&gt;(K36*100+J36),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="14" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="13">
+        <f>IF($E36="","",IF($N36="Completed","Completed",IF(OR($K36="",$L36=""),"",IF(TODAY()&gt;DATE($L36,1,4)-WEEKDAY(DATE($L36,1,4),3)+($K36-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L36,1,4)-WEEKDAY(DATE($L36,1,4),3)+($K36-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L36,1,4)-WEEKDAY(DATE($L36,1,4),3)+($K36-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N36" s="12" t="n"/>
       <c r="O36" s="14" t="n"/>
+      <c r="P36" s="14" t="n"/>
     </row>
     <row r="37" ht="19.5" customHeight="1" s="113">
-      <c r="C37" s="179" t="n"/>
+      <c r="C37" s="184"/>
       <c r="D37" s="101" t="n">
         <v>31</v>
       </c>
@@ -4214,16 +4380,17 @@
       <c r="I37" s="84" t="n"/>
       <c r="J37" s="84" t="n"/>
       <c r="K37" s="84" t="n"/>
-      <c r="L37" s="85">
-        <f>IF(E37="","",IF(M37="Completed","On Track",IF(OR(J37="",K37=""),"",IF(($V$3*100+$U$3)&gt;(K37*100+J37),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M37" s="84" t="n"/>
-      <c r="N37" s="86" t="n"/>
+      <c r="L37" s="84" t="n"/>
+      <c r="M37" s="85">
+        <f>IF($E37="","",IF($N37="Completed","Completed",IF(OR($K37="",$L37=""),"",IF(TODAY()&gt;DATE($L37,1,4)-WEEKDAY(DATE($L37,1,4),3)+($K37-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L37,1,4)-WEEKDAY(DATE($L37,1,4),3)+($K37-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L37,1,4)-WEEKDAY(DATE($L37,1,4),3)+($K37-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N37" s="84" t="n"/>
       <c r="O37" s="86" t="n"/>
+      <c r="P37" s="86" t="n"/>
     </row>
     <row r="38" ht="19.5" customHeight="1" s="113">
-      <c r="C38" s="28" t="n"/>
+      <c r="C38" s="184"/>
       <c r="D38" s="29" t="n">
         <v>32</v>
       </c>
@@ -4234,16 +4401,17 @@
       <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
       <c r="K38" s="12" t="n"/>
-      <c r="L38" s="13">
-        <f>IF(E38="","",IF(M38="Completed","On Track",IF(OR(J38="",K38=""),"",IF(($V$3*100+$U$3)&gt;(K38*100+J38),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="14" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="13">
+        <f>IF($E38="","",IF($N38="Completed","Completed",IF(OR($K38="",$L38=""),"",IF(TODAY()&gt;DATE($L38,1,4)-WEEKDAY(DATE($L38,1,4),3)+($K38-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L38,1,4)-WEEKDAY(DATE($L38,1,4),3)+($K38-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L38,1,4)-WEEKDAY(DATE($L38,1,4),3)+($K38-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N38" s="12" t="n"/>
       <c r="O38" s="14" t="n"/>
+      <c r="P38" s="14" t="n"/>
     </row>
     <row r="39" ht="19.5" customHeight="1" s="113">
-      <c r="C39" s="58" t="n"/>
+      <c r="C39" s="184"/>
       <c r="D39" s="102" t="n">
         <v>33</v>
       </c>
@@ -4254,16 +4422,17 @@
       <c r="I39" s="84" t="n"/>
       <c r="J39" s="84" t="n"/>
       <c r="K39" s="84" t="n"/>
-      <c r="L39" s="85">
-        <f>IF(E39="","",IF(M39="Completed","On Track",IF(OR(J39="",K39=""),"",IF(($V$3*100+$U$3)&gt;(K39*100+J39),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M39" s="84" t="n"/>
-      <c r="N39" s="86" t="n"/>
+      <c r="L39" s="84" t="n"/>
+      <c r="M39" s="85">
+        <f>IF($E39="","",IF($N39="Completed","Completed",IF(OR($K39="",$L39=""),"",IF(TODAY()&gt;DATE($L39,1,4)-WEEKDAY(DATE($L39,1,4),3)+($K39-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L39,1,4)-WEEKDAY(DATE($L39,1,4),3)+($K39-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L39,1,4)-WEEKDAY(DATE($L39,1,4),3)+($K39-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N39" s="84" t="n"/>
       <c r="O39" s="86" t="n"/>
+      <c r="P39" s="86" t="n"/>
     </row>
     <row r="40" ht="19.5" customHeight="1" s="113">
-      <c r="C40" s="180" t="n"/>
+      <c r="C40" s="184"/>
       <c r="D40" s="60" t="n">
         <v>34</v>
       </c>
@@ -4274,16 +4443,17 @@
       <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
       <c r="K40" s="12" t="n"/>
-      <c r="L40" s="13">
-        <f>IF(E40="","",IF(M40="Completed","On Track",IF(OR(J40="",K40=""),"",IF(($V$3*100+$U$3)&gt;(K40*100+J40),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="14" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="13">
+        <f>IF($E40="","",IF($N40="Completed","Completed",IF(OR($K40="",$L40=""),"",IF(TODAY()&gt;DATE($L40,1,4)-WEEKDAY(DATE($L40,1,4),3)+($K40-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L40,1,4)-WEEKDAY(DATE($L40,1,4),3)+($K40-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L40,1,4)-WEEKDAY(DATE($L40,1,4),3)+($K40-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N40" s="12" t="n"/>
       <c r="O40" s="14" t="n"/>
+      <c r="P40" s="14" t="n"/>
     </row>
     <row r="41" ht="19.5" customHeight="1" s="113">
-      <c r="C41" s="61" t="n"/>
+      <c r="C41" s="184"/>
       <c r="D41" s="103" t="n">
         <v>35</v>
       </c>
@@ -4294,16 +4464,17 @@
       <c r="I41" s="84" t="n"/>
       <c r="J41" s="84" t="n"/>
       <c r="K41" s="84" t="n"/>
-      <c r="L41" s="85">
-        <f>IF(E41="","",IF(M41="Completed","On Track",IF(OR(J41="",K41=""),"",IF(($V$3*100+$U$3)&gt;(K41*100+J41),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M41" s="84" t="n"/>
-      <c r="N41" s="86" t="n"/>
+      <c r="L41" s="84" t="n"/>
+      <c r="M41" s="85">
+        <f>IF($E41="","",IF($N41="Completed","Completed",IF(OR($K41="",$L41=""),"",IF(TODAY()&gt;DATE($L41,1,4)-WEEKDAY(DATE($L41,1,4),3)+($K41-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L41,1,4)-WEEKDAY(DATE($L41,1,4),3)+($K41-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L41,1,4)-WEEKDAY(DATE($L41,1,4),3)+($K41-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N41" s="84" t="n"/>
       <c r="O41" s="86" t="n"/>
+      <c r="P41" s="86" t="n"/>
     </row>
     <row r="42" ht="19.5" customHeight="1" s="113">
-      <c r="C42" s="62" t="n"/>
+      <c r="C42" s="184"/>
       <c r="D42" s="63" t="n">
         <v>36</v>
       </c>
@@ -4314,16 +4485,17 @@
       <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
       <c r="K42" s="12" t="n"/>
-      <c r="L42" s="13">
-        <f>IF(E42="","",IF(M42="Completed","On Track",IF(OR(J42="",K42=""),"",IF(($V$3*100+$U$3)&gt;(K42*100+J42),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M42" s="12" t="n"/>
-      <c r="N42" s="14" t="n"/>
+      <c r="L42" s="12" t="n"/>
+      <c r="M42" s="13">
+        <f>IF($E42="","",IF($N42="Completed","Completed",IF(OR($K42="",$L42=""),"",IF(TODAY()&gt;DATE($L42,1,4)-WEEKDAY(DATE($L42,1,4),3)+($K42-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L42,1,4)-WEEKDAY(DATE($L42,1,4),3)+($K42-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L42,1,4)-WEEKDAY(DATE($L42,1,4),3)+($K42-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N42" s="12" t="n"/>
       <c r="O42" s="14" t="n"/>
+      <c r="P42" s="14" t="n"/>
     </row>
     <row r="43" ht="19.5" customHeight="1" s="113">
-      <c r="C43" s="181" t="n"/>
+      <c r="C43" s="184"/>
       <c r="D43" s="104" t="n">
         <v>37</v>
       </c>
@@ -4334,16 +4506,17 @@
       <c r="I43" s="84" t="n"/>
       <c r="J43" s="84" t="n"/>
       <c r="K43" s="84" t="n"/>
-      <c r="L43" s="85">
-        <f>IF(E43="","",IF(M43="Completed","On Track",IF(OR(J43="",K43=""),"",IF(($V$3*100+$U$3)&gt;(K43*100+J43),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M43" s="84" t="n"/>
-      <c r="N43" s="86" t="n"/>
+      <c r="L43" s="84" t="n"/>
+      <c r="M43" s="85">
+        <f>IF($E43="","",IF($N43="Completed","Completed",IF(OR($K43="",$L43=""),"",IF(TODAY()&gt;DATE($L43,1,4)-WEEKDAY(DATE($L43,1,4),3)+($K43-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L43,1,4)-WEEKDAY(DATE($L43,1,4),3)+($K43-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L43,1,4)-WEEKDAY(DATE($L43,1,4),3)+($K43-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N43" s="84" t="n"/>
       <c r="O43" s="86" t="n"/>
+      <c r="P43" s="86" t="n"/>
     </row>
     <row r="44" ht="19.5" customHeight="1" s="113">
-      <c r="C44" s="15" t="n"/>
+      <c r="C44" s="184"/>
       <c r="D44" s="65" t="n">
         <v>38</v>
       </c>
@@ -4354,16 +4527,17 @@
       <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
       <c r="K44" s="12" t="n"/>
-      <c r="L44" s="13">
-        <f>IF(E44="","",IF(M44="Completed","On Track",IF(OR(J44="",K44=""),"",IF(($V$3*100+$U$3)&gt;(K44*100+J44),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M44" s="12" t="n"/>
-      <c r="N44" s="14" t="n"/>
+      <c r="L44" s="12" t="n"/>
+      <c r="M44" s="13">
+        <f>IF($E44="","",IF($N44="Completed","Completed",IF(OR($K44="",$L44=""),"",IF(TODAY()&gt;DATE($L44,1,4)-WEEKDAY(DATE($L44,1,4),3)+($K44-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L44,1,4)-WEEKDAY(DATE($L44,1,4),3)+($K44-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L44,1,4)-WEEKDAY(DATE($L44,1,4),3)+($K44-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N44" s="12" t="n"/>
       <c r="O44" s="14" t="n"/>
+      <c r="P44" s="14" t="n"/>
     </row>
     <row r="45" ht="19.5" customHeight="1" s="113">
-      <c r="C45" s="9" t="n"/>
+      <c r="C45" s="184"/>
       <c r="D45" s="105" t="n">
         <v>39</v>
       </c>
@@ -4374,16 +4548,17 @@
       <c r="I45" s="84" t="n"/>
       <c r="J45" s="84" t="n"/>
       <c r="K45" s="84" t="n"/>
-      <c r="L45" s="85">
-        <f>IF(E45="","",IF(M45="Completed","On Track",IF(OR(J45="",K45=""),"",IF(($V$3*100+$U$3)&gt;(K45*100+J45),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M45" s="84" t="n"/>
-      <c r="N45" s="86" t="n"/>
+      <c r="L45" s="84" t="n"/>
+      <c r="M45" s="85">
+        <f>IF($E45="","",IF($N45="Completed","Completed",IF(OR($K45="",$L45=""),"",IF(TODAY()&gt;DATE($L45,1,4)-WEEKDAY(DATE($L45,1,4),3)+($K45-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L45,1,4)-WEEKDAY(DATE($L45,1,4),3)+($K45-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L45,1,4)-WEEKDAY(DATE($L45,1,4),3)+($K45-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N45" s="84" t="n"/>
       <c r="O45" s="86" t="n"/>
+      <c r="P45" s="86" t="n"/>
     </row>
     <row r="46" ht="19.5" customHeight="1" s="113">
-      <c r="C46" s="8" t="n"/>
+      <c r="C46" s="184"/>
       <c r="D46" s="66" t="n">
         <v>40</v>
       </c>
@@ -4394,16 +4569,17 @@
       <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
       <c r="K46" s="12" t="n"/>
-      <c r="L46" s="13">
-        <f>IF(E46="","",IF(M46="Completed","On Track",IF(OR(J46="",K46=""),"",IF(($V$3*100+$U$3)&gt;(K46*100+J46),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M46" s="12" t="n"/>
-      <c r="N46" s="14" t="n"/>
+      <c r="L46" s="12" t="n"/>
+      <c r="M46" s="13">
+        <f>IF($E46="","",IF($N46="Completed","Completed",IF(OR($K46="",$L46=""),"",IF(TODAY()&gt;DATE($L46,1,4)-WEEKDAY(DATE($L46,1,4),3)+($K46-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L46,1,4)-WEEKDAY(DATE($L46,1,4),3)+($K46-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L46,1,4)-WEEKDAY(DATE($L46,1,4),3)+($K46-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N46" s="12" t="n"/>
       <c r="O46" s="14" t="n"/>
+      <c r="P46" s="14" t="n"/>
     </row>
     <row r="47" ht="19.5" customHeight="1" s="113">
-      <c r="C47" s="34" t="n"/>
+      <c r="C47" s="184"/>
       <c r="D47" s="106" t="n">
         <v>41</v>
       </c>
@@ -4414,16 +4590,17 @@
       <c r="I47" s="84" t="n"/>
       <c r="J47" s="84" t="n"/>
       <c r="K47" s="84" t="n"/>
-      <c r="L47" s="85">
-        <f>IF(E47="","",IF(M47="Completed","On Track",IF(OR(J47="",K47=""),"",IF(($V$3*100+$U$3)&gt;(K47*100+J47),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M47" s="84" t="n"/>
-      <c r="N47" s="86" t="n"/>
+      <c r="L47" s="84" t="n"/>
+      <c r="M47" s="85">
+        <f>IF($E47="","",IF($N47="Completed","Completed",IF(OR($K47="",$L47=""),"",IF(TODAY()&gt;DATE($L47,1,4)-WEEKDAY(DATE($L47,1,4),3)+($K47-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L47,1,4)-WEEKDAY(DATE($L47,1,4),3)+($K47-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L47,1,4)-WEEKDAY(DATE($L47,1,4),3)+($K47-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N47" s="84" t="n"/>
       <c r="O47" s="86" t="n"/>
+      <c r="P47" s="86" t="n"/>
     </row>
     <row r="48" ht="19.5" customHeight="1" s="113">
-      <c r="C48" s="18" t="n"/>
+      <c r="C48" s="184"/>
       <c r="D48" s="67" t="n">
         <v>42</v>
       </c>
@@ -4434,16 +4611,17 @@
       <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
       <c r="K48" s="12" t="n"/>
-      <c r="L48" s="13">
-        <f>IF(E48="","",IF(M48="Completed","On Track",IF(OR(J48="",K48=""),"",IF(($V$3*100+$U$3)&gt;(K48*100+J48),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M48" s="12" t="n"/>
-      <c r="N48" s="14" t="n"/>
+      <c r="L48" s="12" t="n"/>
+      <c r="M48" s="13">
+        <f>IF($E48="","",IF($N48="Completed","Completed",IF(OR($K48="",$L48=""),"",IF(TODAY()&gt;DATE($L48,1,4)-WEEKDAY(DATE($L48,1,4),3)+($K48-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L48,1,4)-WEEKDAY(DATE($L48,1,4),3)+($K48-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L48,1,4)-WEEKDAY(DATE($L48,1,4),3)+($K48-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N48" s="12" t="n"/>
       <c r="O48" s="14" t="n"/>
+      <c r="P48" s="14" t="n"/>
     </row>
     <row r="49" ht="19.5" customHeight="1" s="113">
-      <c r="C49" s="21" t="n"/>
+      <c r="C49" s="184"/>
       <c r="D49" s="89" t="n">
         <v>43</v>
       </c>
@@ -4454,16 +4632,17 @@
       <c r="I49" s="84" t="n"/>
       <c r="J49" s="84" t="n"/>
       <c r="K49" s="84" t="n"/>
-      <c r="L49" s="85">
-        <f>IF(E49="","",IF(M49="Completed","On Track",IF(OR(J49="",K49=""),"",IF(($V$3*100+$U$3)&gt;(K49*100+J49),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M49" s="84" t="n"/>
-      <c r="N49" s="86" t="n"/>
+      <c r="L49" s="84" t="n"/>
+      <c r="M49" s="85">
+        <f>IF($E49="","",IF($N49="Completed","Completed",IF(OR($K49="",$L49=""),"",IF(TODAY()&gt;DATE($L49,1,4)-WEEKDAY(DATE($L49,1,4),3)+($K49-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L49,1,4)-WEEKDAY(DATE($L49,1,4),3)+($K49-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L49,1,4)-WEEKDAY(DATE($L49,1,4),3)+($K49-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N49" s="84" t="n"/>
       <c r="O49" s="86" t="n"/>
+      <c r="P49" s="86" t="n"/>
     </row>
     <row r="50" ht="19.5" customHeight="1" s="113">
-      <c r="C50" s="24" t="n"/>
+      <c r="C50" s="184"/>
       <c r="D50" s="68" t="n">
         <v>44</v>
       </c>
@@ -4474,16 +4653,17 @@
       <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
       <c r="K50" s="12" t="n"/>
-      <c r="L50" s="13">
-        <f>IF(E50="","",IF(M50="Completed","On Track",IF(OR(J50="",K50=""),"",IF(($V$3*100+$U$3)&gt;(K50*100+J50),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="14" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="13">
+        <f>IF($E50="","",IF($N50="Completed","Completed",IF(OR($K50="",$L50=""),"",IF(TODAY()&gt;DATE($L50,1,4)-WEEKDAY(DATE($L50,1,4),3)+($K50-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L50,1,4)-WEEKDAY(DATE($L50,1,4),3)+($K50-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L50,1,4)-WEEKDAY(DATE($L50,1,4),3)+($K50-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N50" s="12" t="n"/>
       <c r="O50" s="14" t="n"/>
+      <c r="P50" s="14" t="n"/>
     </row>
     <row r="51" ht="19.5" customHeight="1" s="113">
-      <c r="C51" s="25" t="n"/>
+      <c r="C51" s="184"/>
       <c r="D51" s="107" t="n">
         <v>45</v>
       </c>
@@ -4494,16 +4674,17 @@
       <c r="I51" s="84" t="n"/>
       <c r="J51" s="84" t="n"/>
       <c r="K51" s="84" t="n"/>
-      <c r="L51" s="85">
-        <f>IF(E51="","",IF(M51="Completed","On Track",IF(OR(J51="",K51=""),"",IF(($V$3*100+$U$3)&gt;(K51*100+J51),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M51" s="84" t="n"/>
-      <c r="N51" s="86" t="n"/>
+      <c r="L51" s="84" t="n"/>
+      <c r="M51" s="85">
+        <f>IF($E51="","",IF($N51="Completed","Completed",IF(OR($K51="",$L51=""),"",IF(TODAY()&gt;DATE($L51,1,4)-WEEKDAY(DATE($L51,1,4),3)+($K51-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L51,1,4)-WEEKDAY(DATE($L51,1,4),3)+($K51-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L51,1,4)-WEEKDAY(DATE($L51,1,4),3)+($K51-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N51" s="84" t="n"/>
       <c r="O51" s="86" t="n"/>
+      <c r="P51" s="86" t="n"/>
     </row>
     <row r="52" ht="19.5" customHeight="1" s="113">
-      <c r="C52" s="174" t="n"/>
+      <c r="C52" s="184"/>
       <c r="D52" s="23" t="n">
         <v>46</v>
       </c>
@@ -4514,16 +4695,17 @@
       <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
       <c r="K52" s="12" t="n"/>
-      <c r="L52" s="13">
-        <f>IF(E52="","",IF(M52="Completed","On Track",IF(OR(J52="",K52=""),"",IF(($V$3*100+$U$3)&gt;(K52*100+J52),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="14" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="13">
+        <f>IF($E52="","",IF($N52="Completed","Completed",IF(OR($K52="",$L52=""),"",IF(TODAY()&gt;DATE($L52,1,4)-WEEKDAY(DATE($L52,1,4),3)+($K52-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L52,1,4)-WEEKDAY(DATE($L52,1,4),3)+($K52-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L52,1,4)-WEEKDAY(DATE($L52,1,4),3)+($K52-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N52" s="12" t="n"/>
       <c r="O52" s="14" t="n"/>
+      <c r="P52" s="14" t="n"/>
     </row>
     <row r="53" ht="19.5" customHeight="1" s="113">
-      <c r="C53" s="19" t="n"/>
+      <c r="C53" s="184"/>
       <c r="D53" s="108" t="n">
         <v>47</v>
       </c>
@@ -4534,16 +4716,17 @@
       <c r="I53" s="84" t="n"/>
       <c r="J53" s="84" t="n"/>
       <c r="K53" s="84" t="n"/>
-      <c r="L53" s="85">
-        <f>IF(E53="","",IF(M53="Completed","On Track",IF(OR(J53="",K53=""),"",IF(($V$3*100+$U$3)&gt;(K53*100+J53),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M53" s="84" t="n"/>
-      <c r="N53" s="86" t="n"/>
+      <c r="L53" s="84" t="n"/>
+      <c r="M53" s="85">
+        <f>IF($E53="","",IF($N53="Completed","Completed",IF(OR($K53="",$L53=""),"",IF(TODAY()&gt;DATE($L53,1,4)-WEEKDAY(DATE($L53,1,4),3)+($K53-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L53,1,4)-WEEKDAY(DATE($L53,1,4),3)+($K53-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L53,1,4)-WEEKDAY(DATE($L53,1,4),3)+($K53-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N53" s="84" t="n"/>
       <c r="O53" s="86" t="n"/>
+      <c r="P53" s="86" t="n"/>
     </row>
     <row r="54" ht="19.5" customHeight="1" s="113">
-      <c r="C54" s="33" t="n"/>
+      <c r="C54" s="184"/>
       <c r="D54" s="69" t="n">
         <v>48</v>
       </c>
@@ -4554,16 +4737,17 @@
       <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
       <c r="K54" s="12" t="n"/>
-      <c r="L54" s="13">
-        <f>IF(E54="","",IF(M54="Completed","On Track",IF(OR(J54="",K54=""),"",IF(($V$3*100+$U$3)&gt;(K54*100+J54),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="14" t="n"/>
+      <c r="L54" s="12" t="n"/>
+      <c r="M54" s="13">
+        <f>IF($E54="","",IF($N54="Completed","Completed",IF(OR($K54="",$L54=""),"",IF(TODAY()&gt;DATE($L54,1,4)-WEEKDAY(DATE($L54,1,4),3)+($K54-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L54,1,4)-WEEKDAY(DATE($L54,1,4),3)+($K54-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L54,1,4)-WEEKDAY(DATE($L54,1,4),3)+($K54-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N54" s="12" t="n"/>
       <c r="O54" s="14" t="n"/>
+      <c r="P54" s="14" t="n"/>
     </row>
     <row r="55" ht="19.5" customHeight="1" s="113">
-      <c r="C55" s="27" t="n"/>
+      <c r="C55" s="184"/>
       <c r="D55" s="91" t="n">
         <v>49</v>
       </c>
@@ -4574,16 +4758,17 @@
       <c r="I55" s="84" t="n"/>
       <c r="J55" s="84" t="n"/>
       <c r="K55" s="84" t="n"/>
-      <c r="L55" s="85">
-        <f>IF(E55="","",IF(M55="Completed","On Track",IF(OR(J55="",K55=""),"",IF(($V$3*100+$U$3)&gt;(K55*100+J55),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M55" s="84" t="n"/>
-      <c r="N55" s="86" t="n"/>
+      <c r="L55" s="84" t="n"/>
+      <c r="M55" s="85">
+        <f>IF($E55="","",IF($N55="Completed","Completed",IF(OR($K55="",$L55=""),"",IF(TODAY()&gt;DATE($L55,1,4)-WEEKDAY(DATE($L55,1,4),3)+($K55-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L55,1,4)-WEEKDAY(DATE($L55,1,4),3)+($K55-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L55,1,4)-WEEKDAY(DATE($L55,1,4),3)+($K55-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N55" s="84" t="n"/>
       <c r="O55" s="86" t="n"/>
+      <c r="P55" s="86" t="n"/>
     </row>
     <row r="56" ht="19.5" customHeight="1" s="113">
-      <c r="C56" s="8" t="n"/>
+      <c r="C56" s="184"/>
       <c r="D56" s="66" t="n">
         <v>50</v>
       </c>
@@ -4594,16 +4779,17 @@
       <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
       <c r="K56" s="12" t="n"/>
-      <c r="L56" s="13">
-        <f>IF(E56="","",IF(M56="Completed","On Track",IF(OR(J56="",K56=""),"",IF(($V$3*100+$U$3)&gt;(K56*100+J56),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M56" s="12" t="n"/>
-      <c r="N56" s="14" t="n"/>
+      <c r="L56" s="12" t="n"/>
+      <c r="M56" s="13">
+        <f>IF($E56="","",IF($N56="Completed","Completed",IF(OR($K56="",$L56=""),"",IF(TODAY()&gt;DATE($L56,1,4)-WEEKDAY(DATE($L56,1,4),3)+($K56-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L56,1,4)-WEEKDAY(DATE($L56,1,4),3)+($K56-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L56,1,4)-WEEKDAY(DATE($L56,1,4),3)+($K56-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N56" s="12" t="n"/>
       <c r="O56" s="14" t="n"/>
+      <c r="P56" s="14" t="n"/>
     </row>
     <row r="57" ht="19.5" customHeight="1" s="113">
-      <c r="C57" s="8" t="n"/>
+      <c r="C57" s="184"/>
       <c r="D57" s="82" t="n">
         <v>51</v>
       </c>
@@ -4614,16 +4800,17 @@
       <c r="I57" s="84" t="n"/>
       <c r="J57" s="84" t="n"/>
       <c r="K57" s="84" t="n"/>
-      <c r="L57" s="85">
-        <f>IF(E57="","",IF(M57="Completed","On Track",IF(OR(J57="",K57=""),"",IF(($V$3*100+$U$3)&gt;(K57*100+J57),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M57" s="84" t="n"/>
-      <c r="N57" s="86" t="n"/>
+      <c r="L57" s="84" t="n"/>
+      <c r="M57" s="85">
+        <f>IF($E57="","",IF($N57="Completed","Completed",IF(OR($K57="",$L57=""),"",IF(TODAY()&gt;DATE($L57,1,4)-WEEKDAY(DATE($L57,1,4),3)+($K57-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L57,1,4)-WEEKDAY(DATE($L57,1,4),3)+($K57-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L57,1,4)-WEEKDAY(DATE($L57,1,4),3)+($K57-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N57" s="84" t="n"/>
       <c r="O57" s="86" t="n"/>
+      <c r="P57" s="86" t="n"/>
     </row>
     <row r="58" ht="19.5" customHeight="1" s="113">
-      <c r="C58" s="9" t="n"/>
+      <c r="C58" s="184"/>
       <c r="D58" s="10" t="n">
         <v>52</v>
       </c>
@@ -4634,16 +4821,17 @@
       <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
       <c r="K58" s="12" t="n"/>
-      <c r="L58" s="13">
-        <f>IF(E58="","",IF(M58="Completed","On Track",IF(OR(J58="",K58=""),"",IF(($V$3*100+$U$3)&gt;(K58*100+J58),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="14" t="n"/>
+      <c r="L58" s="12" t="n"/>
+      <c r="M58" s="13">
+        <f>IF($E58="","",IF($N58="Completed","Completed",IF(OR($K58="",$L58=""),"",IF(TODAY()&gt;DATE($L58,1,4)-WEEKDAY(DATE($L58,1,4),3)+($K58-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L58,1,4)-WEEKDAY(DATE($L58,1,4),3)+($K58-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L58,1,4)-WEEKDAY(DATE($L58,1,4),3)+($K58-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N58" s="12" t="n"/>
       <c r="O58" s="14" t="n"/>
+      <c r="P58" s="14" t="n"/>
     </row>
     <row r="59" ht="19.5" customHeight="1" s="113">
-      <c r="C59" s="15" t="n"/>
+      <c r="C59" s="184"/>
       <c r="D59" s="87" t="n">
         <v>53</v>
       </c>
@@ -4654,16 +4842,17 @@
       <c r="I59" s="84" t="n"/>
       <c r="J59" s="84" t="n"/>
       <c r="K59" s="84" t="n"/>
-      <c r="L59" s="85">
-        <f>IF(E59="","",IF(M59="Completed","On Track",IF(OR(J59="",K59=""),"",IF(($V$3*100+$U$3)&gt;(K59*100+J59),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M59" s="84" t="n"/>
-      <c r="N59" s="86" t="n"/>
+      <c r="L59" s="84" t="n"/>
+      <c r="M59" s="85">
+        <f>IF($E59="","",IF($N59="Completed","Completed",IF(OR($K59="",$L59=""),"",IF(TODAY()&gt;DATE($L59,1,4)-WEEKDAY(DATE($L59,1,4),3)+($K59-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L59,1,4)-WEEKDAY(DATE($L59,1,4),3)+($K59-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L59,1,4)-WEEKDAY(DATE($L59,1,4),3)+($K59-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N59" s="84" t="n"/>
       <c r="O59" s="86" t="n"/>
+      <c r="P59" s="86" t="n"/>
     </row>
     <row r="60" ht="19.5" customHeight="1" s="113">
-      <c r="C60" s="16" t="n"/>
+      <c r="C60" s="184"/>
       <c r="D60" s="17" t="n">
         <v>54</v>
       </c>
@@ -4674,16 +4863,17 @@
       <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
       <c r="K60" s="12" t="n"/>
-      <c r="L60" s="13">
-        <f>IF(E60="","",IF(M60="Completed","On Track",IF(OR(J60="",K60=""),"",IF(($V$3*100+$U$3)&gt;(K60*100+J60),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="14" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="13">
+        <f>IF($E60="","",IF($N60="Completed","Completed",IF(OR($K60="",$L60=""),"",IF(TODAY()&gt;DATE($L60,1,4)-WEEKDAY(DATE($L60,1,4),3)+($K60-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L60,1,4)-WEEKDAY(DATE($L60,1,4),3)+($K60-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L60,1,4)-WEEKDAY(DATE($L60,1,4),3)+($K60-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N60" s="12" t="n"/>
       <c r="O60" s="14" t="n"/>
+      <c r="P60" s="14" t="n"/>
     </row>
     <row r="61" ht="19.5" customHeight="1" s="113">
-      <c r="C61" s="18" t="n"/>
+      <c r="C61" s="184"/>
       <c r="D61" s="88" t="n">
         <v>55</v>
       </c>
@@ -4694,16 +4884,17 @@
       <c r="I61" s="84" t="n"/>
       <c r="J61" s="84" t="n"/>
       <c r="K61" s="84" t="n"/>
-      <c r="L61" s="85">
-        <f>IF(E61="","",IF(M61="Completed","On Track",IF(OR(J61="",K61=""),"",IF(($V$3*100+$U$3)&gt;(K61*100+J61),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M61" s="84" t="n"/>
-      <c r="N61" s="86" t="n"/>
+      <c r="L61" s="84" t="n"/>
+      <c r="M61" s="85">
+        <f>IF($E61="","",IF($N61="Completed","Completed",IF(OR($K61="",$L61=""),"",IF(TODAY()&gt;DATE($L61,1,4)-WEEKDAY(DATE($L61,1,4),3)+($K61-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L61,1,4)-WEEKDAY(DATE($L61,1,4),3)+($K61-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L61,1,4)-WEEKDAY(DATE($L61,1,4),3)+($K61-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N61" s="84" t="n"/>
       <c r="O61" s="86" t="n"/>
+      <c r="P61" s="86" t="n"/>
     </row>
     <row r="62" ht="19.5" customHeight="1" s="113">
-      <c r="C62" s="19" t="n"/>
+      <c r="C62" s="184"/>
       <c r="D62" s="20" t="n">
         <v>56</v>
       </c>
@@ -4714,16 +4905,17 @@
       <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
       <c r="K62" s="12" t="n"/>
-      <c r="L62" s="13">
-        <f>IF(E62="","",IF(M62="Completed","On Track",IF(OR(J62="",K62=""),"",IF(($V$3*100+$U$3)&gt;(K62*100+J62),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="14" t="n"/>
+      <c r="L62" s="12" t="n"/>
+      <c r="M62" s="13">
+        <f>IF($E62="","",IF($N62="Completed","Completed",IF(OR($K62="",$L62=""),"",IF(TODAY()&gt;DATE($L62,1,4)-WEEKDAY(DATE($L62,1,4),3)+($K62-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L62,1,4)-WEEKDAY(DATE($L62,1,4),3)+($K62-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L62,1,4)-WEEKDAY(DATE($L62,1,4),3)+($K62-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N62" s="12" t="n"/>
       <c r="O62" s="14" t="n"/>
+      <c r="P62" s="14" t="n"/>
     </row>
     <row r="63" ht="19.5" customHeight="1" s="113">
-      <c r="C63" s="21" t="n"/>
+      <c r="C63" s="184"/>
       <c r="D63" s="89" t="n">
         <v>57</v>
       </c>
@@ -4734,16 +4926,17 @@
       <c r="I63" s="84" t="n"/>
       <c r="J63" s="84" t="n"/>
       <c r="K63" s="84" t="n"/>
-      <c r="L63" s="85">
-        <f>IF(E63="","",IF(M63="Completed","On Track",IF(OR(J63="",K63=""),"",IF(($V$3*100+$U$3)&gt;(K63*100+J63),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M63" s="84" t="n"/>
-      <c r="N63" s="86" t="n"/>
+      <c r="L63" s="84" t="n"/>
+      <c r="M63" s="85">
+        <f>IF($E63="","",IF($N63="Completed","Completed",IF(OR($K63="",$L63=""),"",IF(TODAY()&gt;DATE($L63,1,4)-WEEKDAY(DATE($L63,1,4),3)+($K63-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L63,1,4)-WEEKDAY(DATE($L63,1,4),3)+($K63-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L63,1,4)-WEEKDAY(DATE($L63,1,4),3)+($K63-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N63" s="84" t="n"/>
       <c r="O63" s="86" t="n"/>
+      <c r="P63" s="86" t="n"/>
     </row>
     <row r="64" ht="19.5" customHeight="1" s="113">
-      <c r="C64" s="174" t="n"/>
+      <c r="C64" s="184"/>
       <c r="D64" s="23" t="n">
         <v>58</v>
       </c>
@@ -4754,16 +4947,17 @@
       <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
       <c r="K64" s="12" t="n"/>
-      <c r="L64" s="13">
-        <f>IF(E64="","",IF(M64="Completed","On Track",IF(OR(J64="",K64=""),"",IF(($V$3*100+$U$3)&gt;(K64*100+J64),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="14" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="13">
+        <f>IF($E64="","",IF($N64="Completed","Completed",IF(OR($K64="",$L64=""),"",IF(TODAY()&gt;DATE($L64,1,4)-WEEKDAY(DATE($L64,1,4),3)+($K64-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L64,1,4)-WEEKDAY(DATE($L64,1,4),3)+($K64-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L64,1,4)-WEEKDAY(DATE($L64,1,4),3)+($K64-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N64" s="12" t="n"/>
       <c r="O64" s="14" t="n"/>
+      <c r="P64" s="14" t="n"/>
     </row>
     <row r="65" ht="19.5" customHeight="1" s="113">
-      <c r="C65" s="24" t="n"/>
+      <c r="C65" s="184"/>
       <c r="D65" s="90" t="n">
         <v>59</v>
       </c>
@@ -4774,16 +4968,17 @@
       <c r="I65" s="84" t="n"/>
       <c r="J65" s="84" t="n"/>
       <c r="K65" s="84" t="n"/>
-      <c r="L65" s="85">
-        <f>IF(E65="","",IF(M65="Completed","On Track",IF(OR(J65="",K65=""),"",IF(($V$3*100+$U$3)&gt;(K65*100+J65),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M65" s="84" t="n"/>
-      <c r="N65" s="86" t="n"/>
+      <c r="L65" s="84" t="n"/>
+      <c r="M65" s="85">
+        <f>IF($E65="","",IF($N65="Completed","Completed",IF(OR($K65="",$L65=""),"",IF(TODAY()&gt;DATE($L65,1,4)-WEEKDAY(DATE($L65,1,4),3)+($K65-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L65,1,4)-WEEKDAY(DATE($L65,1,4),3)+($K65-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L65,1,4)-WEEKDAY(DATE($L65,1,4),3)+($K65-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N65" s="84" t="n"/>
       <c r="O65" s="86" t="n"/>
+      <c r="P65" s="86" t="n"/>
     </row>
     <row r="66" ht="19.5" customHeight="1" s="113">
-      <c r="C66" s="25" t="n"/>
+      <c r="C66" s="184"/>
       <c r="D66" s="26" t="n">
         <v>60</v>
       </c>
@@ -4794,16 +4989,17 @@
       <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
       <c r="K66" s="12" t="n"/>
-      <c r="L66" s="13">
-        <f>IF(E66="","",IF(M66="Completed","On Track",IF(OR(J66="",K66=""),"",IF(($V$3*100+$U$3)&gt;(K66*100+J66),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="14" t="n"/>
+      <c r="L66" s="12" t="n"/>
+      <c r="M66" s="13">
+        <f>IF($E66="","",IF($N66="Completed","Completed",IF(OR($K66="",$L66=""),"",IF(TODAY()&gt;DATE($L66,1,4)-WEEKDAY(DATE($L66,1,4),3)+($K66-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L66,1,4)-WEEKDAY(DATE($L66,1,4),3)+($K66-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L66,1,4)-WEEKDAY(DATE($L66,1,4),3)+($K66-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N66" s="12" t="n"/>
       <c r="O66" s="14" t="n"/>
+      <c r="P66" s="14" t="n"/>
     </row>
     <row r="67" ht="19.5" customHeight="1" s="113">
-      <c r="C67" s="27" t="n"/>
+      <c r="C67" s="184"/>
       <c r="D67" s="91" t="n">
         <v>61</v>
       </c>
@@ -4814,16 +5010,17 @@
       <c r="I67" s="84" t="n"/>
       <c r="J67" s="84" t="n"/>
       <c r="K67" s="84" t="n"/>
-      <c r="L67" s="85">
-        <f>IF(E67="","",IF(M67="Completed","On Track",IF(OR(J67="",K67=""),"",IF(($V$3*100+$U$3)&gt;(K67*100+J67),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M67" s="84" t="n"/>
-      <c r="N67" s="86" t="n"/>
+      <c r="L67" s="84" t="n"/>
+      <c r="M67" s="85">
+        <f>IF($E67="","",IF($N67="Completed","Completed",IF(OR($K67="",$L67=""),"",IF(TODAY()&gt;DATE($L67,1,4)-WEEKDAY(DATE($L67,1,4),3)+($K67-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L67,1,4)-WEEKDAY(DATE($L67,1,4),3)+($K67-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L67,1,4)-WEEKDAY(DATE($L67,1,4),3)+($K67-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N67" s="84" t="n"/>
       <c r="O67" s="86" t="n"/>
+      <c r="P67" s="86" t="n"/>
     </row>
     <row r="68" ht="19.5" customHeight="1" s="113">
-      <c r="C68" s="28" t="n"/>
+      <c r="C68" s="184"/>
       <c r="D68" s="29" t="n">
         <v>62</v>
       </c>
@@ -4834,16 +5031,17 @@
       <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
       <c r="K68" s="12" t="n"/>
-      <c r="L68" s="13">
-        <f>IF(E68="","",IF(M68="Completed","On Track",IF(OR(J68="",K68=""),"",IF(($V$3*100+$U$3)&gt;(K68*100+J68),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="14" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="13">
+        <f>IF($E68="","",IF($N68="Completed","Completed",IF(OR($K68="",$L68=""),"",IF(TODAY()&gt;DATE($L68,1,4)-WEEKDAY(DATE($L68,1,4),3)+($K68-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L68,1,4)-WEEKDAY(DATE($L68,1,4),3)+($K68-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L68,1,4)-WEEKDAY(DATE($L68,1,4),3)+($K68-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N68" s="12" t="n"/>
       <c r="O68" s="14" t="n"/>
+      <c r="P68" s="14" t="n"/>
     </row>
     <row r="69" ht="19.5" customHeight="1" s="113">
-      <c r="C69" s="30" t="n"/>
+      <c r="C69" s="184"/>
       <c r="D69" s="92" t="n">
         <v>63</v>
       </c>
@@ -4854,16 +5052,17 @@
       <c r="I69" s="84" t="n"/>
       <c r="J69" s="84" t="n"/>
       <c r="K69" s="84" t="n"/>
-      <c r="L69" s="85">
-        <f>IF(E69="","",IF(M69="Completed","On Track",IF(OR(J69="",K69=""),"",IF(($V$3*100+$U$3)&gt;(K69*100+J69),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M69" s="84" t="n"/>
-      <c r="N69" s="86" t="n"/>
+      <c r="L69" s="84" t="n"/>
+      <c r="M69" s="85">
+        <f>IF($E69="","",IF($N69="Completed","Completed",IF(OR($K69="",$L69=""),"",IF(TODAY()&gt;DATE($L69,1,4)-WEEKDAY(DATE($L69,1,4),3)+($K69-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L69,1,4)-WEEKDAY(DATE($L69,1,4),3)+($K69-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L69,1,4)-WEEKDAY(DATE($L69,1,4),3)+($K69-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N69" s="84" t="n"/>
       <c r="O69" s="86" t="n"/>
+      <c r="P69" s="86" t="n"/>
     </row>
     <row r="70" ht="19.5" customHeight="1" s="113">
-      <c r="C70" s="31" t="n"/>
+      <c r="C70" s="184"/>
       <c r="D70" s="32" t="n">
         <v>64</v>
       </c>
@@ -4874,16 +5073,17 @@
       <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
       <c r="K70" s="12" t="n"/>
-      <c r="L70" s="13">
-        <f>IF(E70="","",IF(M70="Completed","On Track",IF(OR(J70="",K70=""),"",IF(($V$3*100+$U$3)&gt;(K70*100+J70),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="14" t="n"/>
+      <c r="L70" s="12" t="n"/>
+      <c r="M70" s="13">
+        <f>IF($E70="","",IF($N70="Completed","Completed",IF(OR($K70="",$L70=""),"",IF(TODAY()&gt;DATE($L70,1,4)-WEEKDAY(DATE($L70,1,4),3)+($K70-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L70,1,4)-WEEKDAY(DATE($L70,1,4),3)+($K70-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L70,1,4)-WEEKDAY(DATE($L70,1,4),3)+($K70-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N70" s="12" t="n"/>
       <c r="O70" s="14" t="n"/>
+      <c r="P70" s="14" t="n"/>
     </row>
     <row r="71" ht="19.5" customHeight="1" s="113">
-      <c r="C71" s="33" t="n"/>
+      <c r="C71" s="184"/>
       <c r="D71" s="93" t="n">
         <v>65</v>
       </c>
@@ -4894,16 +5094,17 @@
       <c r="I71" s="84" t="n"/>
       <c r="J71" s="84" t="n"/>
       <c r="K71" s="84" t="n"/>
-      <c r="L71" s="85">
-        <f>IF(E71="","",IF(M71="Completed","On Track",IF(OR(J71="",K71=""),"",IF(($V$3*100+$U$3)&gt;(K71*100+J71),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M71" s="84" t="n"/>
-      <c r="N71" s="86" t="n"/>
+      <c r="L71" s="84" t="n"/>
+      <c r="M71" s="85">
+        <f>IF($E71="","",IF($N71="Completed","Completed",IF(OR($K71="",$L71=""),"",IF(TODAY()&gt;DATE($L71,1,4)-WEEKDAY(DATE($L71,1,4),3)+($K71-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L71,1,4)-WEEKDAY(DATE($L71,1,4),3)+($K71-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L71,1,4)-WEEKDAY(DATE($L71,1,4),3)+($K71-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N71" s="84" t="n"/>
       <c r="O71" s="86" t="n"/>
+      <c r="P71" s="86" t="n"/>
     </row>
     <row r="72" ht="19.5" customHeight="1" s="113">
-      <c r="C72" s="34" t="n"/>
+      <c r="C72" s="184"/>
       <c r="D72" s="35" t="n">
         <v>66</v>
       </c>
@@ -4914,16 +5115,17 @@
       <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
       <c r="K72" s="12" t="n"/>
-      <c r="L72" s="13">
-        <f>IF(E72="","",IF(M72="Completed","On Track",IF(OR(J72="",K72=""),"",IF(($V$3*100+$U$3)&gt;(K72*100+J72),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="14" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="13">
+        <f>IF($E72="","",IF($N72="Completed","Completed",IF(OR($K72="",$L72=""),"",IF(TODAY()&gt;DATE($L72,1,4)-WEEKDAY(DATE($L72,1,4),3)+($K72-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L72,1,4)-WEEKDAY(DATE($L72,1,4),3)+($K72-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L72,1,4)-WEEKDAY(DATE($L72,1,4),3)+($K72-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N72" s="12" t="n"/>
       <c r="O72" s="14" t="n"/>
+      <c r="P72" s="14" t="n"/>
     </row>
     <row r="73" ht="19.5" customHeight="1" s="113">
-      <c r="C73" s="36" t="n"/>
+      <c r="C73" s="184"/>
       <c r="D73" s="94" t="n">
         <v>67</v>
       </c>
@@ -4934,16 +5136,17 @@
       <c r="I73" s="84" t="n"/>
       <c r="J73" s="84" t="n"/>
       <c r="K73" s="84" t="n"/>
-      <c r="L73" s="85">
-        <f>IF(E73="","",IF(M73="Completed","On Track",IF(OR(J73="",K73=""),"",IF(($V$3*100+$U$3)&gt;(K73*100+J73),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M73" s="84" t="n"/>
-      <c r="N73" s="86" t="n"/>
+      <c r="L73" s="84" t="n"/>
+      <c r="M73" s="85">
+        <f>IF($E73="","",IF($N73="Completed","Completed",IF(OR($K73="",$L73=""),"",IF(TODAY()&gt;DATE($L73,1,4)-WEEKDAY(DATE($L73,1,4),3)+($K73-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L73,1,4)-WEEKDAY(DATE($L73,1,4),3)+($K73-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L73,1,4)-WEEKDAY(DATE($L73,1,4),3)+($K73-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N73" s="84" t="n"/>
       <c r="O73" s="86" t="n"/>
+      <c r="P73" s="86" t="n"/>
     </row>
     <row r="74" ht="19.5" customHeight="1" s="113">
-      <c r="C74" s="37" t="n"/>
+      <c r="C74" s="184"/>
       <c r="D74" s="38" t="n">
         <v>68</v>
       </c>
@@ -4954,16 +5157,17 @@
       <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
       <c r="K74" s="12" t="n"/>
-      <c r="L74" s="13">
-        <f>IF(E74="","",IF(M74="Completed","On Track",IF(OR(J74="",K74=""),"",IF(($V$3*100+$U$3)&gt;(K74*100+J74),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="14" t="n"/>
+      <c r="L74" s="12" t="n"/>
+      <c r="M74" s="13">
+        <f>IF($E74="","",IF($N74="Completed","Completed",IF(OR($K74="",$L74=""),"",IF(TODAY()&gt;DATE($L74,1,4)-WEEKDAY(DATE($L74,1,4),3)+($K74-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L74,1,4)-WEEKDAY(DATE($L74,1,4),3)+($K74-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L74,1,4)-WEEKDAY(DATE($L74,1,4),3)+($K74-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N74" s="12" t="n"/>
       <c r="O74" s="14" t="n"/>
+      <c r="P74" s="14" t="n"/>
     </row>
     <row r="75" ht="19.5" customHeight="1" s="113">
-      <c r="C75" s="39" t="n"/>
+      <c r="C75" s="184"/>
       <c r="D75" s="95" t="n">
         <v>69</v>
       </c>
@@ -4974,16 +5178,17 @@
       <c r="I75" s="84" t="n"/>
       <c r="J75" s="84" t="n"/>
       <c r="K75" s="84" t="n"/>
-      <c r="L75" s="85">
-        <f>IF(E75="","",IF(M75="Completed","On Track",IF(OR(J75="",K75=""),"",IF(($V$3*100+$U$3)&gt;(K75*100+J75),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M75" s="84" t="n"/>
-      <c r="N75" s="86" t="n"/>
+      <c r="L75" s="84" t="n"/>
+      <c r="M75" s="85">
+        <f>IF($E75="","",IF($N75="Completed","Completed",IF(OR($K75="",$L75=""),"",IF(TODAY()&gt;DATE($L75,1,4)-WEEKDAY(DATE($L75,1,4),3)+($K75-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L75,1,4)-WEEKDAY(DATE($L75,1,4),3)+($K75-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L75,1,4)-WEEKDAY(DATE($L75,1,4),3)+($K75-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N75" s="84" t="n"/>
       <c r="O75" s="86" t="n"/>
+      <c r="P75" s="86" t="n"/>
     </row>
     <row r="76" ht="19.5" customHeight="1" s="113">
-      <c r="C76" s="40" t="n"/>
+      <c r="C76" s="184"/>
       <c r="D76" s="41" t="n">
         <v>70</v>
       </c>
@@ -4994,16 +5199,17 @@
       <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
       <c r="K76" s="12" t="n"/>
-      <c r="L76" s="13">
-        <f>IF(E76="","",IF(M76="Completed","On Track",IF(OR(J76="",K76=""),"",IF(($V$3*100+$U$3)&gt;(K76*100+J76),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="14" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="13">
+        <f>IF($E76="","",IF($N76="Completed","Completed",IF(OR($K76="",$L76=""),"",IF(TODAY()&gt;DATE($L76,1,4)-WEEKDAY(DATE($L76,1,4),3)+($K76-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L76,1,4)-WEEKDAY(DATE($L76,1,4),3)+($K76-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L76,1,4)-WEEKDAY(DATE($L76,1,4),3)+($K76-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N76" s="12" t="n"/>
       <c r="O76" s="14" t="n"/>
+      <c r="P76" s="14" t="n"/>
     </row>
     <row r="77" ht="19.5" customHeight="1" s="113">
-      <c r="C77" s="42" t="n"/>
+      <c r="C77" s="184"/>
       <c r="D77" s="96" t="n">
         <v>71</v>
       </c>
@@ -5014,16 +5220,17 @@
       <c r="I77" s="84" t="n"/>
       <c r="J77" s="84" t="n"/>
       <c r="K77" s="84" t="n"/>
-      <c r="L77" s="85">
-        <f>IF(E77="","",IF(M77="Completed","On Track",IF(OR(J77="",K77=""),"",IF(($V$3*100+$U$3)&gt;(K77*100+J77),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M77" s="84" t="n"/>
-      <c r="N77" s="86" t="n"/>
+      <c r="L77" s="84" t="n"/>
+      <c r="M77" s="85">
+        <f>IF($E77="","",IF($N77="Completed","Completed",IF(OR($K77="",$L77=""),"",IF(TODAY()&gt;DATE($L77,1,4)-WEEKDAY(DATE($L77,1,4),3)+($K77-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L77,1,4)-WEEKDAY(DATE($L77,1,4),3)+($K77-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L77,1,4)-WEEKDAY(DATE($L77,1,4),3)+($K77-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N77" s="84" t="n"/>
       <c r="O77" s="86" t="n"/>
+      <c r="P77" s="86" t="n"/>
     </row>
     <row r="78" ht="19.5" customHeight="1" s="113">
-      <c r="C78" s="175" t="n"/>
+      <c r="C78" s="184"/>
       <c r="D78" s="44" t="n">
         <v>72</v>
       </c>
@@ -5034,16 +5241,17 @@
       <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
       <c r="K78" s="12" t="n"/>
-      <c r="L78" s="13">
-        <f>IF(E78="","",IF(M78="Completed","On Track",IF(OR(J78="",K78=""),"",IF(($V$3*100+$U$3)&gt;(K78*100+J78),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M78" s="12" t="n"/>
-      <c r="N78" s="14" t="n"/>
+      <c r="L78" s="12" t="n"/>
+      <c r="M78" s="13">
+        <f>IF($E78="","",IF($N78="Completed","Completed",IF(OR($K78="",$L78=""),"",IF(TODAY()&gt;DATE($L78,1,4)-WEEKDAY(DATE($L78,1,4),3)+($K78-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L78,1,4)-WEEKDAY(DATE($L78,1,4),3)+($K78-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L78,1,4)-WEEKDAY(DATE($L78,1,4),3)+($K78-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N78" s="12" t="n"/>
       <c r="O78" s="14" t="n"/>
+      <c r="P78" s="14" t="n"/>
     </row>
     <row r="79" ht="19.5" customHeight="1" s="113">
-      <c r="C79" s="176" t="n"/>
+      <c r="C79" s="184"/>
       <c r="D79" s="97" t="n">
         <v>73</v>
       </c>
@@ -5054,16 +5262,17 @@
       <c r="I79" s="84" t="n"/>
       <c r="J79" s="84" t="n"/>
       <c r="K79" s="84" t="n"/>
-      <c r="L79" s="85">
-        <f>IF(E79="","",IF(M79="Completed","On Track",IF(OR(J79="",K79=""),"",IF(($V$3*100+$U$3)&gt;(K79*100+J79),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M79" s="84" t="n"/>
-      <c r="N79" s="86" t="n"/>
+      <c r="L79" s="84" t="n"/>
+      <c r="M79" s="85">
+        <f>IF($E79="","",IF($N79="Completed","Completed",IF(OR($K79="",$L79=""),"",IF(TODAY()&gt;DATE($L79,1,4)-WEEKDAY(DATE($L79,1,4),3)+($K79-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L79,1,4)-WEEKDAY(DATE($L79,1,4),3)+($K79-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L79,1,4)-WEEKDAY(DATE($L79,1,4),3)+($K79-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N79" s="84" t="n"/>
       <c r="O79" s="86" t="n"/>
+      <c r="P79" s="86" t="n"/>
     </row>
     <row r="80" ht="19.5" customHeight="1" s="113">
-      <c r="C80" s="46" t="n"/>
+      <c r="C80" s="184"/>
       <c r="D80" s="47" t="n">
         <v>74</v>
       </c>
@@ -5074,16 +5283,17 @@
       <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
       <c r="K80" s="12" t="n"/>
-      <c r="L80" s="13">
-        <f>IF(E80="","",IF(M80="Completed","On Track",IF(OR(J80="",K80=""),"",IF(($V$3*100+$U$3)&gt;(K80*100+J80),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="14" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="13">
+        <f>IF($E80="","",IF($N80="Completed","Completed",IF(OR($K80="",$L80=""),"",IF(TODAY()&gt;DATE($L80,1,4)-WEEKDAY(DATE($L80,1,4),3)+($K80-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L80,1,4)-WEEKDAY(DATE($L80,1,4),3)+($K80-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L80,1,4)-WEEKDAY(DATE($L80,1,4),3)+($K80-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N80" s="12" t="n"/>
       <c r="O80" s="14" t="n"/>
+      <c r="P80" s="14" t="n"/>
     </row>
     <row r="81" ht="19.5" customHeight="1" s="113">
-      <c r="C81" s="48" t="n"/>
+      <c r="C81" s="184"/>
       <c r="D81" s="98" t="n">
         <v>75</v>
       </c>
@@ -5094,16 +5304,17 @@
       <c r="I81" s="84" t="n"/>
       <c r="J81" s="84" t="n"/>
       <c r="K81" s="84" t="n"/>
-      <c r="L81" s="85">
-        <f>IF(E81="","",IF(M81="Completed","On Track",IF(OR(J81="",K81=""),"",IF(($V$3*100+$U$3)&gt;(K81*100+J81),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M81" s="84" t="n"/>
-      <c r="N81" s="86" t="n"/>
+      <c r="L81" s="84" t="n"/>
+      <c r="M81" s="85">
+        <f>IF($E81="","",IF($N81="Completed","Completed",IF(OR($K81="",$L81=""),"",IF(TODAY()&gt;DATE($L81,1,4)-WEEKDAY(DATE($L81,1,4),3)+($K81-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L81,1,4)-WEEKDAY(DATE($L81,1,4),3)+($K81-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L81,1,4)-WEEKDAY(DATE($L81,1,4),3)+($K81-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N81" s="84" t="n"/>
       <c r="O81" s="86" t="n"/>
+      <c r="P81" s="86" t="n"/>
     </row>
     <row r="82" ht="19.5" customHeight="1" s="113">
-      <c r="C82" s="177" t="n"/>
+      <c r="C82" s="184"/>
       <c r="D82" s="50" t="n">
         <v>76</v>
       </c>
@@ -5114,16 +5325,17 @@
       <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
       <c r="K82" s="12" t="n"/>
-      <c r="L82" s="13">
-        <f>IF(E82="","",IF(M82="Completed","On Track",IF(OR(J82="",K82=""),"",IF(($V$3*100+$U$3)&gt;(K82*100+J82),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="14" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="13">
+        <f>IF($E82="","",IF($N82="Completed","Completed",IF(OR($K82="",$L82=""),"",IF(TODAY()&gt;DATE($L82,1,4)-WEEKDAY(DATE($L82,1,4),3)+($K82-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L82,1,4)-WEEKDAY(DATE($L82,1,4),3)+($K82-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L82,1,4)-WEEKDAY(DATE($L82,1,4),3)+($K82-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N82" s="12" t="n"/>
       <c r="O82" s="14" t="n"/>
+      <c r="P82" s="14" t="n"/>
     </row>
     <row r="83" ht="19.5" customHeight="1" s="113">
-      <c r="C83" s="51" t="n"/>
+      <c r="C83" s="184"/>
       <c r="D83" s="99" t="n">
         <v>77</v>
       </c>
@@ -5134,16 +5346,17 @@
       <c r="I83" s="84" t="n"/>
       <c r="J83" s="84" t="n"/>
       <c r="K83" s="84" t="n"/>
-      <c r="L83" s="85">
-        <f>IF(E83="","",IF(M83="Completed","On Track",IF(OR(J83="",K83=""),"",IF(($V$3*100+$U$3)&gt;(K83*100+J83),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M83" s="84" t="n"/>
-      <c r="N83" s="86" t="n"/>
+      <c r="L83" s="84" t="n"/>
+      <c r="M83" s="85">
+        <f>IF($E83="","",IF($N83="Completed","Completed",IF(OR($K83="",$L83=""),"",IF(TODAY()&gt;DATE($L83,1,4)-WEEKDAY(DATE($L83,1,4),3)+($K83-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L83,1,4)-WEEKDAY(DATE($L83,1,4),3)+($K83-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L83,1,4)-WEEKDAY(DATE($L83,1,4),3)+($K83-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N83" s="84" t="n"/>
       <c r="O83" s="86" t="n"/>
+      <c r="P83" s="86" t="n"/>
     </row>
     <row r="84" ht="19.5" customHeight="1" s="113">
-      <c r="C84" s="52" t="n"/>
+      <c r="C84" s="184"/>
       <c r="D84" s="53" t="n">
         <v>78</v>
       </c>
@@ -5154,16 +5367,17 @@
       <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
       <c r="K84" s="12" t="n"/>
-      <c r="L84" s="13">
-        <f>IF(E84="","",IF(M84="Completed","On Track",IF(OR(J84="",K84=""),"",IF(($V$3*100+$U$3)&gt;(K84*100+J84),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="14" t="n"/>
+      <c r="L84" s="12" t="n"/>
+      <c r="M84" s="13">
+        <f>IF($E84="","",IF($N84="Completed","Completed",IF(OR($K84="",$L84=""),"",IF(TODAY()&gt;DATE($L84,1,4)-WEEKDAY(DATE($L84,1,4),3)+($K84-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L84,1,4)-WEEKDAY(DATE($L84,1,4),3)+($K84-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L84,1,4)-WEEKDAY(DATE($L84,1,4),3)+($K84-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N84" s="12" t="n"/>
       <c r="O84" s="14" t="n"/>
+      <c r="P84" s="14" t="n"/>
     </row>
     <row r="85" ht="19.5" customHeight="1" s="113">
-      <c r="C85" s="54" t="n"/>
+      <c r="C85" s="184"/>
       <c r="D85" s="100" t="n">
         <v>79</v>
       </c>
@@ -5174,16 +5388,17 @@
       <c r="I85" s="84" t="n"/>
       <c r="J85" s="84" t="n"/>
       <c r="K85" s="84" t="n"/>
-      <c r="L85" s="85">
-        <f>IF(E85="","",IF(M85="Completed","On Track",IF(OR(J85="",K85=""),"",IF(($V$3*100+$U$3)&gt;(K85*100+J85),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M85" s="84" t="n"/>
-      <c r="N85" s="86" t="n"/>
+      <c r="L85" s="84" t="n"/>
+      <c r="M85" s="85">
+        <f>IF($E85="","",IF($N85="Completed","Completed",IF(OR($K85="",$L85=""),"",IF(TODAY()&gt;DATE($L85,1,4)-WEEKDAY(DATE($L85,1,4),3)+($K85-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L85,1,4)-WEEKDAY(DATE($L85,1,4),3)+($K85-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L85,1,4)-WEEKDAY(DATE($L85,1,4),3)+($K85-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N85" s="84" t="n"/>
       <c r="O85" s="86" t="n"/>
+      <c r="P85" s="86" t="n"/>
     </row>
     <row r="86" ht="19.5" customHeight="1" s="113">
-      <c r="C86" s="178" t="n"/>
+      <c r="C86" s="184"/>
       <c r="D86" s="56" t="n">
         <v>80</v>
       </c>
@@ -5194,16 +5409,17 @@
       <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
       <c r="K86" s="12" t="n"/>
-      <c r="L86" s="13">
-        <f>IF(E86="","",IF(M86="Completed","On Track",IF(OR(J86="",K86=""),"",IF(($V$3*100+$U$3)&gt;(K86*100+J86),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M86" s="12" t="n"/>
-      <c r="N86" s="14" t="n"/>
+      <c r="L86" s="12" t="n"/>
+      <c r="M86" s="13">
+        <f>IF($E86="","",IF($N86="Completed","Completed",IF(OR($K86="",$L86=""),"",IF(TODAY()&gt;DATE($L86,1,4)-WEEKDAY(DATE($L86,1,4),3)+($K86-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L86,1,4)-WEEKDAY(DATE($L86,1,4),3)+($K86-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L86,1,4)-WEEKDAY(DATE($L86,1,4),3)+($K86-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N86" s="12" t="n"/>
       <c r="O86" s="14" t="n"/>
+      <c r="P86" s="14" t="n"/>
     </row>
     <row r="87" ht="19.5" customHeight="1" s="113">
-      <c r="C87" s="179" t="n"/>
+      <c r="C87" s="184"/>
       <c r="D87" s="101" t="n">
         <v>81</v>
       </c>
@@ -5214,16 +5430,17 @@
       <c r="I87" s="84" t="n"/>
       <c r="J87" s="84" t="n"/>
       <c r="K87" s="84" t="n"/>
-      <c r="L87" s="85">
-        <f>IF(E87="","",IF(M87="Completed","On Track",IF(OR(J87="",K87=""),"",IF(($V$3*100+$U$3)&gt;(K87*100+J87),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M87" s="84" t="n"/>
-      <c r="N87" s="86" t="n"/>
+      <c r="L87" s="84" t="n"/>
+      <c r="M87" s="85">
+        <f>IF($E87="","",IF($N87="Completed","Completed",IF(OR($K87="",$L87=""),"",IF(TODAY()&gt;DATE($L87,1,4)-WEEKDAY(DATE($L87,1,4),3)+($K87-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L87,1,4)-WEEKDAY(DATE($L87,1,4),3)+($K87-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L87,1,4)-WEEKDAY(DATE($L87,1,4),3)+($K87-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N87" s="84" t="n"/>
       <c r="O87" s="86" t="n"/>
+      <c r="P87" s="86" t="n"/>
     </row>
     <row r="88" ht="19.5" customHeight="1" s="113">
-      <c r="C88" s="28" t="n"/>
+      <c r="C88" s="184"/>
       <c r="D88" s="29" t="n">
         <v>82</v>
       </c>
@@ -5234,16 +5451,17 @@
       <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
       <c r="K88" s="12" t="n"/>
-      <c r="L88" s="13">
-        <f>IF(E88="","",IF(M88="Completed","On Track",IF(OR(J88="",K88=""),"",IF(($V$3*100+$U$3)&gt;(K88*100+J88),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M88" s="12" t="n"/>
-      <c r="N88" s="14" t="n"/>
+      <c r="L88" s="12" t="n"/>
+      <c r="M88" s="13">
+        <f>IF($E88="","",IF($N88="Completed","Completed",IF(OR($K88="",$L88=""),"",IF(TODAY()&gt;DATE($L88,1,4)-WEEKDAY(DATE($L88,1,4),3)+($K88-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L88,1,4)-WEEKDAY(DATE($L88,1,4),3)+($K88-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L88,1,4)-WEEKDAY(DATE($L88,1,4),3)+($K88-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N88" s="12" t="n"/>
       <c r="O88" s="14" t="n"/>
+      <c r="P88" s="14" t="n"/>
     </row>
     <row r="89" ht="19.5" customHeight="1" s="113">
-      <c r="C89" s="58" t="n"/>
+      <c r="C89" s="184"/>
       <c r="D89" s="102" t="n">
         <v>83</v>
       </c>
@@ -5254,16 +5472,17 @@
       <c r="I89" s="84" t="n"/>
       <c r="J89" s="84" t="n"/>
       <c r="K89" s="84" t="n"/>
-      <c r="L89" s="85">
-        <f>IF(E89="","",IF(M89="Completed","On Track",IF(OR(J89="",K89=""),"",IF(($V$3*100+$U$3)&gt;(K89*100+J89),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M89" s="84" t="n"/>
-      <c r="N89" s="86" t="n"/>
+      <c r="L89" s="84" t="n"/>
+      <c r="M89" s="85">
+        <f>IF($E89="","",IF($N89="Completed","Completed",IF(OR($K89="",$L89=""),"",IF(TODAY()&gt;DATE($L89,1,4)-WEEKDAY(DATE($L89,1,4),3)+($K89-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L89,1,4)-WEEKDAY(DATE($L89,1,4),3)+($K89-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L89,1,4)-WEEKDAY(DATE($L89,1,4),3)+($K89-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N89" s="84" t="n"/>
       <c r="O89" s="86" t="n"/>
+      <c r="P89" s="86" t="n"/>
     </row>
     <row r="90" ht="19.5" customHeight="1" s="113">
-      <c r="C90" s="180" t="n"/>
+      <c r="C90" s="184"/>
       <c r="D90" s="60" t="n">
         <v>84</v>
       </c>
@@ -5274,16 +5493,17 @@
       <c r="I90" s="12" t="n"/>
       <c r="J90" s="12" t="n"/>
       <c r="K90" s="12" t="n"/>
-      <c r="L90" s="13">
-        <f>IF(E90="","",IF(M90="Completed","On Track",IF(OR(J90="",K90=""),"",IF(($V$3*100+$U$3)&gt;(K90*100+J90),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M90" s="12" t="n"/>
-      <c r="N90" s="14" t="n"/>
+      <c r="L90" s="12" t="n"/>
+      <c r="M90" s="13">
+        <f>IF($E90="","",IF($N90="Completed","Completed",IF(OR($K90="",$L90=""),"",IF(TODAY()&gt;DATE($L90,1,4)-WEEKDAY(DATE($L90,1,4),3)+($K90-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L90,1,4)-WEEKDAY(DATE($L90,1,4),3)+($K90-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L90,1,4)-WEEKDAY(DATE($L90,1,4),3)+($K90-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N90" s="12" t="n"/>
       <c r="O90" s="14" t="n"/>
+      <c r="P90" s="14" t="n"/>
     </row>
     <row r="91" ht="19.5" customHeight="1" s="113">
-      <c r="C91" s="61" t="n"/>
+      <c r="C91" s="184"/>
       <c r="D91" s="103" t="n">
         <v>85</v>
       </c>
@@ -5294,16 +5514,17 @@
       <c r="I91" s="84" t="n"/>
       <c r="J91" s="84" t="n"/>
       <c r="K91" s="84" t="n"/>
-      <c r="L91" s="85">
-        <f>IF(E91="","",IF(M91="Completed","On Track",IF(OR(J91="",K91=""),"",IF(($V$3*100+$U$3)&gt;(K91*100+J91),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M91" s="84" t="n"/>
-      <c r="N91" s="86" t="n"/>
+      <c r="L91" s="84" t="n"/>
+      <c r="M91" s="85">
+        <f>IF($E91="","",IF($N91="Completed","Completed",IF(OR($K91="",$L91=""),"",IF(TODAY()&gt;DATE($L91,1,4)-WEEKDAY(DATE($L91,1,4),3)+($K91-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L91,1,4)-WEEKDAY(DATE($L91,1,4),3)+($K91-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L91,1,4)-WEEKDAY(DATE($L91,1,4),3)+($K91-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N91" s="84" t="n"/>
       <c r="O91" s="86" t="n"/>
+      <c r="P91" s="86" t="n"/>
     </row>
     <row r="92" ht="19.5" customHeight="1" s="113">
-      <c r="C92" s="62" t="n"/>
+      <c r="C92" s="184"/>
       <c r="D92" s="63" t="n">
         <v>86</v>
       </c>
@@ -5314,16 +5535,17 @@
       <c r="I92" s="12" t="n"/>
       <c r="J92" s="12" t="n"/>
       <c r="K92" s="12" t="n"/>
-      <c r="L92" s="13">
-        <f>IF(E92="","",IF(M92="Completed","On Track",IF(OR(J92="",K92=""),"",IF(($V$3*100+$U$3)&gt;(K92*100+J92),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M92" s="12" t="n"/>
-      <c r="N92" s="14" t="n"/>
+      <c r="L92" s="12" t="n"/>
+      <c r="M92" s="13">
+        <f>IF($E92="","",IF($N92="Completed","Completed",IF(OR($K92="",$L92=""),"",IF(TODAY()&gt;DATE($L92,1,4)-WEEKDAY(DATE($L92,1,4),3)+($K92-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L92,1,4)-WEEKDAY(DATE($L92,1,4),3)+($K92-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L92,1,4)-WEEKDAY(DATE($L92,1,4),3)+($K92-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N92" s="12" t="n"/>
       <c r="O92" s="14" t="n"/>
+      <c r="P92" s="14" t="n"/>
     </row>
     <row r="93" ht="19.5" customHeight="1" s="113">
-      <c r="C93" s="181" t="n"/>
+      <c r="C93" s="184"/>
       <c r="D93" s="104" t="n">
         <v>87</v>
       </c>
@@ -5334,16 +5556,17 @@
       <c r="I93" s="84" t="n"/>
       <c r="J93" s="84" t="n"/>
       <c r="K93" s="84" t="n"/>
-      <c r="L93" s="85">
-        <f>IF(E93="","",IF(M93="Completed","On Track",IF(OR(J93="",K93=""),"",IF(($V$3*100+$U$3)&gt;(K93*100+J93),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M93" s="84" t="n"/>
-      <c r="N93" s="86" t="n"/>
+      <c r="L93" s="84" t="n"/>
+      <c r="M93" s="85">
+        <f>IF($E93="","",IF($N93="Completed","Completed",IF(OR($K93="",$L93=""),"",IF(TODAY()&gt;DATE($L93,1,4)-WEEKDAY(DATE($L93,1,4),3)+($K93-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L93,1,4)-WEEKDAY(DATE($L93,1,4),3)+($K93-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L93,1,4)-WEEKDAY(DATE($L93,1,4),3)+($K93-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N93" s="84" t="n"/>
       <c r="O93" s="86" t="n"/>
+      <c r="P93" s="86" t="n"/>
     </row>
     <row r="94" ht="19.5" customHeight="1" s="113">
-      <c r="C94" s="15" t="n"/>
+      <c r="C94" s="184"/>
       <c r="D94" s="65" t="n">
         <v>88</v>
       </c>
@@ -5354,16 +5577,17 @@
       <c r="I94" s="12" t="n"/>
       <c r="J94" s="12" t="n"/>
       <c r="K94" s="12" t="n"/>
-      <c r="L94" s="13">
-        <f>IF(E94="","",IF(M94="Completed","On Track",IF(OR(J94="",K94=""),"",IF(($V$3*100+$U$3)&gt;(K94*100+J94),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M94" s="12" t="n"/>
-      <c r="N94" s="14" t="n"/>
+      <c r="L94" s="12" t="n"/>
+      <c r="M94" s="13">
+        <f>IF($E94="","",IF($N94="Completed","Completed",IF(OR($K94="",$L94=""),"",IF(TODAY()&gt;DATE($L94,1,4)-WEEKDAY(DATE($L94,1,4),3)+($K94-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L94,1,4)-WEEKDAY(DATE($L94,1,4),3)+($K94-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L94,1,4)-WEEKDAY(DATE($L94,1,4),3)+($K94-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N94" s="12" t="n"/>
       <c r="O94" s="14" t="n"/>
+      <c r="P94" s="14" t="n"/>
     </row>
     <row r="95" ht="19.5" customHeight="1" s="113">
-      <c r="C95" s="9" t="n"/>
+      <c r="C95" s="184"/>
       <c r="D95" s="105" t="n">
         <v>89</v>
       </c>
@@ -5374,16 +5598,17 @@
       <c r="I95" s="84" t="n"/>
       <c r="J95" s="84" t="n"/>
       <c r="K95" s="84" t="n"/>
-      <c r="L95" s="85">
-        <f>IF(E95="","",IF(M95="Completed","On Track",IF(OR(J95="",K95=""),"",IF(($V$3*100+$U$3)&gt;(K95*100+J95),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M95" s="84" t="n"/>
-      <c r="N95" s="86" t="n"/>
+      <c r="L95" s="84" t="n"/>
+      <c r="M95" s="85">
+        <f>IF($E95="","",IF($N95="Completed","Completed",IF(OR($K95="",$L95=""),"",IF(TODAY()&gt;DATE($L95,1,4)-WEEKDAY(DATE($L95,1,4),3)+($K95-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L95,1,4)-WEEKDAY(DATE($L95,1,4),3)+($K95-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L95,1,4)-WEEKDAY(DATE($L95,1,4),3)+($K95-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N95" s="84" t="n"/>
       <c r="O95" s="86" t="n"/>
+      <c r="P95" s="86" t="n"/>
     </row>
     <row r="96" ht="19.5" customHeight="1" s="113">
-      <c r="C96" s="8" t="n"/>
+      <c r="C96" s="184"/>
       <c r="D96" s="66" t="n">
         <v>90</v>
       </c>
@@ -5394,16 +5619,17 @@
       <c r="I96" s="12" t="n"/>
       <c r="J96" s="12" t="n"/>
       <c r="K96" s="12" t="n"/>
-      <c r="L96" s="13">
-        <f>IF(E96="","",IF(M96="Completed","On Track",IF(OR(J96="",K96=""),"",IF(($V$3*100+$U$3)&gt;(K96*100+J96),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M96" s="12" t="n"/>
-      <c r="N96" s="14" t="n"/>
+      <c r="L96" s="12" t="n"/>
+      <c r="M96" s="13">
+        <f>IF($E96="","",IF($N96="Completed","Completed",IF(OR($K96="",$L96=""),"",IF(TODAY()&gt;DATE($L96,1,4)-WEEKDAY(DATE($L96,1,4),3)+($K96-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L96,1,4)-WEEKDAY(DATE($L96,1,4),3)+($K96-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L96,1,4)-WEEKDAY(DATE($L96,1,4),3)+($K96-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N96" s="12" t="n"/>
       <c r="O96" s="14" t="n"/>
+      <c r="P96" s="14" t="n"/>
     </row>
     <row r="97" ht="19.5" customHeight="1" s="113">
-      <c r="C97" s="34" t="n"/>
+      <c r="C97" s="184"/>
       <c r="D97" s="106" t="n">
         <v>91</v>
       </c>
@@ -5414,16 +5640,17 @@
       <c r="I97" s="84" t="n"/>
       <c r="J97" s="84" t="n"/>
       <c r="K97" s="84" t="n"/>
-      <c r="L97" s="85">
-        <f>IF(E97="","",IF(M97="Completed","On Track",IF(OR(J97="",K97=""),"",IF(($V$3*100+$U$3)&gt;(K97*100+J97),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M97" s="84" t="n"/>
-      <c r="N97" s="86" t="n"/>
+      <c r="L97" s="84" t="n"/>
+      <c r="M97" s="85">
+        <f>IF($E97="","",IF($N97="Completed","Completed",IF(OR($K97="",$L97=""),"",IF(TODAY()&gt;DATE($L97,1,4)-WEEKDAY(DATE($L97,1,4),3)+($K97-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L97,1,4)-WEEKDAY(DATE($L97,1,4),3)+($K97-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L97,1,4)-WEEKDAY(DATE($L97,1,4),3)+($K97-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N97" s="84" t="n"/>
       <c r="O97" s="86" t="n"/>
+      <c r="P97" s="86" t="n"/>
     </row>
     <row r="98" ht="19.5" customHeight="1" s="113">
-      <c r="C98" s="18" t="n"/>
+      <c r="C98" s="184"/>
       <c r="D98" s="67" t="n">
         <v>92</v>
       </c>
@@ -5434,16 +5661,17 @@
       <c r="I98" s="12" t="n"/>
       <c r="J98" s="12" t="n"/>
       <c r="K98" s="12" t="n"/>
-      <c r="L98" s="13">
-        <f>IF(E98="","",IF(M98="Completed","On Track",IF(OR(J98="",K98=""),"",IF(($V$3*100+$U$3)&gt;(K98*100+J98),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M98" s="12" t="n"/>
-      <c r="N98" s="14" t="n"/>
+      <c r="L98" s="12" t="n"/>
+      <c r="M98" s="13">
+        <f>IF($E98="","",IF($N98="Completed","Completed",IF(OR($K98="",$L98=""),"",IF(TODAY()&gt;DATE($L98,1,4)-WEEKDAY(DATE($L98,1,4),3)+($K98-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L98,1,4)-WEEKDAY(DATE($L98,1,4),3)+($K98-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L98,1,4)-WEEKDAY(DATE($L98,1,4),3)+($K98-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N98" s="12" t="n"/>
       <c r="O98" s="14" t="n"/>
+      <c r="P98" s="14" t="n"/>
     </row>
     <row r="99" ht="19.5" customHeight="1" s="113">
-      <c r="C99" s="21" t="n"/>
+      <c r="C99" s="184"/>
       <c r="D99" s="89" t="n">
         <v>93</v>
       </c>
@@ -5454,16 +5682,17 @@
       <c r="I99" s="84" t="n"/>
       <c r="J99" s="84" t="n"/>
       <c r="K99" s="84" t="n"/>
-      <c r="L99" s="85">
-        <f>IF(E99="","",IF(M99="Completed","On Track",IF(OR(J99="",K99=""),"",IF(($V$3*100+$U$3)&gt;(K99*100+J99),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M99" s="84" t="n"/>
-      <c r="N99" s="86" t="n"/>
+      <c r="L99" s="84" t="n"/>
+      <c r="M99" s="85">
+        <f>IF($E99="","",IF($N99="Completed","Completed",IF(OR($K99="",$L99=""),"",IF(TODAY()&gt;DATE($L99,1,4)-WEEKDAY(DATE($L99,1,4),3)+($K99-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L99,1,4)-WEEKDAY(DATE($L99,1,4),3)+($K99-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L99,1,4)-WEEKDAY(DATE($L99,1,4),3)+($K99-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N99" s="84" t="n"/>
       <c r="O99" s="86" t="n"/>
+      <c r="P99" s="86" t="n"/>
     </row>
     <row r="100" ht="19.5" customHeight="1" s="113">
-      <c r="C100" s="24" t="n"/>
+      <c r="C100" s="184"/>
       <c r="D100" s="68" t="n">
         <v>94</v>
       </c>
@@ -5474,16 +5703,17 @@
       <c r="I100" s="12" t="n"/>
       <c r="J100" s="12" t="n"/>
       <c r="K100" s="12" t="n"/>
-      <c r="L100" s="13">
-        <f>IF(E100="","",IF(M100="Completed","On Track",IF(OR(J100="",K100=""),"",IF(($V$3*100+$U$3)&gt;(K100*100+J100),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M100" s="12" t="n"/>
-      <c r="N100" s="14" t="n"/>
+      <c r="L100" s="12" t="n"/>
+      <c r="M100" s="13">
+        <f>IF($E100="","",IF($N100="Completed","Completed",IF(OR($K100="",$L100=""),"",IF(TODAY()&gt;DATE($L100,1,4)-WEEKDAY(DATE($L100,1,4),3)+($K100-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L100,1,4)-WEEKDAY(DATE($L100,1,4),3)+($K100-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L100,1,4)-WEEKDAY(DATE($L100,1,4),3)+($K100-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N100" s="12" t="n"/>
       <c r="O100" s="14" t="n"/>
+      <c r="P100" s="14" t="n"/>
     </row>
     <row r="101" ht="19.5" customHeight="1" s="113">
-      <c r="C101" s="25" t="n"/>
+      <c r="C101" s="184"/>
       <c r="D101" s="107" t="n">
         <v>95</v>
       </c>
@@ -5494,16 +5724,17 @@
       <c r="I101" s="84" t="n"/>
       <c r="J101" s="84" t="n"/>
       <c r="K101" s="84" t="n"/>
-      <c r="L101" s="85">
-        <f>IF(E101="","",IF(M101="Completed","On Track",IF(OR(J101="",K101=""),"",IF(($V$3*100+$U$3)&gt;(K101*100+J101),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M101" s="84" t="n"/>
-      <c r="N101" s="86" t="n"/>
+      <c r="L101" s="84" t="n"/>
+      <c r="M101" s="85">
+        <f>IF($E101="","",IF($N101="Completed","Completed",IF(OR($K101="",$L101=""),"",IF(TODAY()&gt;DATE($L101,1,4)-WEEKDAY(DATE($L101,1,4),3)+($K101-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L101,1,4)-WEEKDAY(DATE($L101,1,4),3)+($K101-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L101,1,4)-WEEKDAY(DATE($L101,1,4),3)+($K101-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N101" s="84" t="n"/>
       <c r="O101" s="86" t="n"/>
+      <c r="P101" s="86" t="n"/>
     </row>
     <row r="102" ht="19.5" customHeight="1" s="113">
-      <c r="C102" s="174" t="n"/>
+      <c r="C102" s="184"/>
       <c r="D102" s="23" t="n">
         <v>96</v>
       </c>
@@ -5514,16 +5745,17 @@
       <c r="I102" s="12" t="n"/>
       <c r="J102" s="12" t="n"/>
       <c r="K102" s="12" t="n"/>
-      <c r="L102" s="13">
-        <f>IF(E102="","",IF(M102="Completed","On Track",IF(OR(J102="",K102=""),"",IF(($V$3*100+$U$3)&gt;(K102*100+J102),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M102" s="12" t="n"/>
-      <c r="N102" s="14" t="n"/>
+      <c r="L102" s="12" t="n"/>
+      <c r="M102" s="13">
+        <f>IF($E102="","",IF($N102="Completed","Completed",IF(OR($K102="",$L102=""),"",IF(TODAY()&gt;DATE($L102,1,4)-WEEKDAY(DATE($L102,1,4),3)+($K102-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L102,1,4)-WEEKDAY(DATE($L102,1,4),3)+($K102-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L102,1,4)-WEEKDAY(DATE($L102,1,4),3)+($K102-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N102" s="12" t="n"/>
       <c r="O102" s="14" t="n"/>
+      <c r="P102" s="14" t="n"/>
     </row>
     <row r="103" ht="19.5" customHeight="1" s="113">
-      <c r="C103" s="19" t="n"/>
+      <c r="C103" s="184"/>
       <c r="D103" s="108" t="n">
         <v>97</v>
       </c>
@@ -5534,16 +5766,17 @@
       <c r="I103" s="84" t="n"/>
       <c r="J103" s="84" t="n"/>
       <c r="K103" s="84" t="n"/>
-      <c r="L103" s="85">
-        <f>IF(E103="","",IF(M103="Completed","On Track",IF(OR(J103="",K103=""),"",IF(($V$3*100+$U$3)&gt;(K103*100+J103),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M103" s="84" t="n"/>
-      <c r="N103" s="86" t="n"/>
+      <c r="L103" s="84" t="n"/>
+      <c r="M103" s="85">
+        <f>IF($E103="","",IF($N103="Completed","Completed",IF(OR($K103="",$L103=""),"",IF(TODAY()&gt;DATE($L103,1,4)-WEEKDAY(DATE($L103,1,4),3)+($K103-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L103,1,4)-WEEKDAY(DATE($L103,1,4),3)+($K103-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L103,1,4)-WEEKDAY(DATE($L103,1,4),3)+($K103-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N103" s="84" t="n"/>
       <c r="O103" s="86" t="n"/>
+      <c r="P103" s="86" t="n"/>
     </row>
     <row r="104" ht="19.5" customHeight="1" s="113">
-      <c r="C104" s="33" t="n"/>
+      <c r="C104" s="184"/>
       <c r="D104" s="69" t="n">
         <v>98</v>
       </c>
@@ -5554,16 +5787,17 @@
       <c r="I104" s="12" t="n"/>
       <c r="J104" s="12" t="n"/>
       <c r="K104" s="12" t="n"/>
-      <c r="L104" s="13">
-        <f>IF(E104="","",IF(M104="Completed","On Track",IF(OR(J104="",K104=""),"",IF(($V$3*100+$U$3)&gt;(K104*100+J104),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M104" s="12" t="n"/>
-      <c r="N104" s="14" t="n"/>
+      <c r="L104" s="12" t="n"/>
+      <c r="M104" s="13">
+        <f>IF($E104="","",IF($N104="Completed","Completed",IF(OR($K104="",$L104=""),"",IF(TODAY()&gt;DATE($L104,1,4)-WEEKDAY(DATE($L104,1,4),3)+($K104-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L104,1,4)-WEEKDAY(DATE($L104,1,4),3)+($K104-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L104,1,4)-WEEKDAY(DATE($L104,1,4),3)+($K104-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N104" s="12" t="n"/>
       <c r="O104" s="14" t="n"/>
+      <c r="P104" s="14" t="n"/>
     </row>
     <row r="105" ht="19.5" customHeight="1" s="113">
-      <c r="C105" s="27" t="n"/>
+      <c r="C105" s="184"/>
       <c r="D105" s="91" t="n">
         <v>99</v>
       </c>
@@ -5574,16 +5808,17 @@
       <c r="I105" s="84" t="n"/>
       <c r="J105" s="84" t="n"/>
       <c r="K105" s="84" t="n"/>
-      <c r="L105" s="85">
-        <f>IF(E105="","",IF(M105="Completed","On Track",IF(OR(J105="",K105=""),"",IF(($V$3*100+$U$3)&gt;(K105*100+J105),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M105" s="84" t="n"/>
-      <c r="N105" s="86" t="n"/>
+      <c r="L105" s="84" t="n"/>
+      <c r="M105" s="85">
+        <f>IF($E105="","",IF($N105="Completed","Completed",IF(OR($K105="",$L105=""),"",IF(TODAY()&gt;DATE($L105,1,4)-WEEKDAY(DATE($L105,1,4),3)+($K105-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L105,1,4)-WEEKDAY(DATE($L105,1,4),3)+($K105-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L105,1,4)-WEEKDAY(DATE($L105,1,4),3)+($K105-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N105" s="84" t="n"/>
       <c r="O105" s="86" t="n"/>
+      <c r="P105" s="86" t="n"/>
     </row>
     <row r="106" ht="19.5" customHeight="1" s="113">
-      <c r="C106" s="8" t="n"/>
+      <c r="C106" s="184"/>
       <c r="D106" s="66" t="n">
         <v>100</v>
       </c>
@@ -5594,13 +5829,14 @@
       <c r="I106" s="12" t="n"/>
       <c r="J106" s="12" t="n"/>
       <c r="K106" s="12" t="n"/>
-      <c r="L106" s="13">
-        <f>IF(E106="","",IF(M106="Completed","On Track",IF(OR(J106="",K106=""),"",IF(($V$3*100+$U$3)&gt;(K106*100+J106),"Delayed","On Track"))))</f>
-        <v/>
-      </c>
-      <c r="M106" s="12" t="n"/>
-      <c r="N106" s="14" t="n"/>
+      <c r="L106" s="12" t="n"/>
+      <c r="M106" s="13">
+        <f>IF($E106="","",IF($N106="Completed","Completed",IF(OR($K106="",$L106=""),"",IF(TODAY()&gt;DATE($L106,1,4)-WEEKDAY(DATE($L106,1,4),3)+($K106-1)*7+6,"Delayed "&amp;ROUNDUP((TODAY()-(DATE($L106,1,4)-WEEKDAY(DATE($L106,1,4),3)+($K106-1)*7+6))/7,0)&amp;"w",IF(TODAY()&gt;=DATE($L106,1,4)-WEEKDAY(DATE($L106,1,4),3)+($K106-1)*7,"Due this week","On Track")))))</f>
+        <v/>
+      </c>
+      <c r="N106" s="12" t="n"/>
       <c r="O106" s="14" t="n"/>
+      <c r="P106" s="14" t="n"/>
     </row>
     <row r="107" ht="19.5" customHeight="1" s="113">
       <c r="C107" s="70" t="n"/>
@@ -5615,6 +5851,7 @@
       <c r="L107" s="70" t="n"/>
       <c r="M107" s="70" t="n"/>
       <c r="N107" s="70" t="n"/>
+      <c r="O107" s="70" t="n"/>
     </row>
     <row r="108" ht="19.5" customHeight="1" s="113">
       <c r="C108" s="70" t="n"/>
@@ -5629,6 +5866,7 @@
       <c r="L108" s="70" t="n"/>
       <c r="M108" s="70" t="n"/>
       <c r="N108" s="70" t="n"/>
+      <c r="O108" s="70" t="n"/>
     </row>
     <row r="109" ht="19.5" customHeight="1" s="113">
       <c r="C109" s="70" t="n"/>
@@ -5643,6 +5881,7 @@
       <c r="L109" s="70" t="n"/>
       <c r="M109" s="70" t="n"/>
       <c r="N109" s="70" t="n"/>
+      <c r="O109" s="70" t="n"/>
     </row>
     <row r="110" ht="19.5" customHeight="1" s="113">
       <c r="C110" s="70" t="n"/>
@@ -5657,6 +5896,7 @@
       <c r="L110" s="70" t="n"/>
       <c r="M110" s="70" t="n"/>
       <c r="N110" s="70" t="n"/>
+      <c r="O110" s="70" t="n"/>
     </row>
     <row r="111" ht="19.5" customHeight="1" s="113">
       <c r="C111" s="70" t="n"/>
@@ -5671,6 +5911,7 @@
       <c r="L111" s="70" t="n"/>
       <c r="M111" s="70" t="n"/>
       <c r="N111" s="70" t="n"/>
+      <c r="O111" s="70" t="n"/>
     </row>
     <row r="112" ht="19.5" customHeight="1" s="113">
       <c r="C112" s="70" t="n"/>
@@ -5685,6 +5926,7 @@
       <c r="L112" s="70" t="n"/>
       <c r="M112" s="70" t="n"/>
       <c r="N112" s="70" t="n"/>
+      <c r="O112" s="70" t="n"/>
     </row>
     <row r="113" ht="19.5" customHeight="1" s="113">
       <c r="C113" s="70" t="n"/>
@@ -5699,6 +5941,7 @@
       <c r="L113" s="70" t="n"/>
       <c r="M113" s="70" t="n"/>
       <c r="N113" s="70" t="n"/>
+      <c r="O113" s="70" t="n"/>
     </row>
     <row r="114" ht="19.5" customHeight="1" s="113">
       <c r="C114" s="70" t="n"/>
@@ -5713,6 +5956,7 @@
       <c r="L114" s="70" t="n"/>
       <c r="M114" s="70" t="n"/>
       <c r="N114" s="70" t="n"/>
+      <c r="O114" s="70" t="n"/>
     </row>
     <row r="115" ht="19.5" customHeight="1" s="113"/>
     <row r="116" ht="19.5" customHeight="1" s="113"/>
@@ -5816,7 +6060,7 @@
     <row r="214" ht="15" customHeight="1" s="113"/>
     <row r="216" ht="15.75" customHeight="1" s="113"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="11">
     <mergeCell ref="B3:D3"/>
     <mergeCell ref="E4:N4"/>
     <mergeCell ref="B4:D4"/>
@@ -5825,50 +6069,81 @@
     <mergeCell ref="E2:N2"/>
     <mergeCell ref="U4:V4"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="E5:N5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="K5:N5"/>
   </mergeCells>
-  <conditionalFormatting sqref="L7:L106">
-    <cfRule type="containsText" priority="9" operator="containsText" dxfId="64" text="On Track">
-      <formula>NOT(ISERROR(SEARCH("On Track",L7)))</formula>
+  <conditionalFormatting sqref="C7:C106">
+    <cfRule type="cellIs" priority="200" operator="equal" dxfId="74">
+      <formula>"Red"</formula>
     </cfRule>
-    <cfRule type="containsText" priority="10" operator="containsText" dxfId="72" text="Delayed">
-      <formula>NOT(ISERROR(SEARCH("Delayed",L7)))</formula>
+    <cfRule type="cellIs" priority="202" operator="equal" dxfId="76">
+      <formula>"Yellow"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="203" operator="equal" dxfId="77">
+      <formula>"Green"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="204" operator="equal" dxfId="78">
+      <formula>"Blue"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="205" operator="equal" dxfId="79">
+      <formula>"Purple"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="206" dxfId="80">
+      <formula>AND($C7="",$E7&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="M7:M106">
+    <cfRule type="containsText" priority="9" operator="containsText" dxfId="72" text="Delayed">
+      <formula>NOT(ISERROR(SEARCH("Delayed",M7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="10" operator="containsText" dxfId="59" text="Due this week">
+      <formula>NOT(ISERROR(SEARCH("Due this week",M7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="11" operator="containsText" dxfId="64" text="Completed">
+      <formula>NOT(ISERROR(SEARCH("Completed",M7)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="12" operator="containsText" dxfId="61" text="On Track">
+      <formula>NOT(ISERROR(SEARCH("On Track",M7)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N7:N106">
     <cfRule type="containsText" priority="1" operator="containsText" dxfId="63" text="TBD">
-      <formula>NOT(ISERROR(SEARCH("TBD",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("TBD",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="2" operator="containsText" dxfId="62" text="Planned">
-      <formula>NOT(ISERROR(SEARCH("Planned",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Planned",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="3" operator="containsText" dxfId="61" text="Aligned">
-      <formula>NOT(ISERROR(SEARCH("Aligned",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Aligned",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="4" operator="containsText" dxfId="60" text="Dependency">
-      <formula>NOT(ISERROR(SEARCH("Dependency",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Dependency",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="5" operator="containsText" dxfId="59" text="Risk">
-      <formula>NOT(ISERROR(SEARCH("Risk",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Risk",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="6" operator="containsText" dxfId="58" text="Blocker">
-      <formula>NOT(ISERROR(SEARCH("Blocker",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Blocker",N7)))</formula>
     </cfRule>
     <cfRule type="containsText" priority="7" operator="containsText" dxfId="64" text="Completed">
-      <formula>NOT(ISERROR(SEARCH("Completed",M7)))</formula>
+      <formula>NOT(ISERROR(SEARCH("Completed",N7)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="3">
-    <dataValidation sqref="M7:M106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+  <dataValidations count="4">
+    <dataValidation sqref="N7:N106" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"TBD,Planned,Aligned,Dependency,Risk,Blocker,Completed"</formula1>
     </dataValidation>
-    <dataValidation sqref="H7:H106 J7:J106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid week" error="Week must be a whole number between 1 and 53." type="whole">
+    <dataValidation sqref="I7:I106 K7:K106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid week" error="Week must be a whole number between 1 and 53." type="whole">
       <formula1>1</formula1>
       <formula2>53</formula2>
     </dataValidation>
-    <dataValidation sqref="I7:I106 K7:K106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid year" error="Year must be a 4-digit whole number." type="whole">
+    <dataValidation sqref="J7:J106 L7:L106" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid year" error="Year must be a 4-digit whole number." type="whole">
       <formula1>1000</formula1>
       <formula2>9999</formula2>
+    </dataValidation>
+    <dataValidation sqref="C7:C106" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Activity colour" prompt="Pick a colour name. It fills this cell, the bars on the time plan sheet and the bars in the HTML dashboard." errorTitle="Unknown colour" error="Choose one of: Red, Yellow, Green, Blue, Purple." type="list">
+      <formula1>"Red,Yellow,Green,Blue,Purple"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -10526,11 +10801,11 @@
         <v/>
       </c>
       <c r="D7" s="76">
-        <f>IF('L3 input'!G7&lt;&gt;"",'L3 input'!G7,"")</f>
+        <f>IF('L3 input'!H7&lt;&gt;"",'L3 input'!H7,"")</f>
         <v/>
       </c>
       <c r="E7" s="76">
-        <f>IF('L3 input'!M7&lt;&gt;"",'L3 input'!M7,"")</f>
+        <f>IF('L3 input'!N7&lt;&gt;"",'L3 input'!N7,"")</f>
         <v/>
       </c>
       <c r="F7" s="81" t="n"/>
@@ -10873,11 +11148,11 @@
         <v/>
       </c>
       <c r="D8" s="76">
-        <f>IF('L3 input'!G8&lt;&gt;"",'L3 input'!G8,"")</f>
+        <f>IF('L3 input'!H8&lt;&gt;"",'L3 input'!H8,"")</f>
         <v/>
       </c>
       <c r="E8" s="76">
-        <f>IF('L3 input'!M8&lt;&gt;"",'L3 input'!M8,"")</f>
+        <f>IF('L3 input'!N8&lt;&gt;"",'L3 input'!N8,"")</f>
         <v/>
       </c>
       <c r="F8" s="77" t="n"/>
@@ -11220,11 +11495,11 @@
         <v/>
       </c>
       <c r="D9" s="76">
-        <f>IF('L3 input'!G9&lt;&gt;"",'L3 input'!G9,"")</f>
+        <f>IF('L3 input'!H9&lt;&gt;"",'L3 input'!H9,"")</f>
         <v/>
       </c>
       <c r="E9" s="76">
-        <f>IF('L3 input'!M9&lt;&gt;"",'L3 input'!M9,"")</f>
+        <f>IF('L3 input'!N9&lt;&gt;"",'L3 input'!N9,"")</f>
         <v/>
       </c>
       <c r="F9" s="81" t="n"/>
@@ -11567,11 +11842,11 @@
         <v/>
       </c>
       <c r="D10" s="76">
-        <f>IF('L3 input'!G10&lt;&gt;"",'L3 input'!G10,"")</f>
+        <f>IF('L3 input'!H10&lt;&gt;"",'L3 input'!H10,"")</f>
         <v/>
       </c>
       <c r="E10" s="76">
-        <f>IF('L3 input'!M10&lt;&gt;"",'L3 input'!M10,"")</f>
+        <f>IF('L3 input'!N10&lt;&gt;"",'L3 input'!N10,"")</f>
         <v/>
       </c>
       <c r="F10" s="77" t="n"/>
@@ -11914,11 +12189,11 @@
         <v/>
       </c>
       <c r="D11" s="76">
-        <f>IF('L3 input'!G11&lt;&gt;"",'L3 input'!G11,"")</f>
+        <f>IF('L3 input'!H11&lt;&gt;"",'L3 input'!H11,"")</f>
         <v/>
       </c>
       <c r="E11" s="76">
-        <f>IF('L3 input'!M11&lt;&gt;"",'L3 input'!M11,"")</f>
+        <f>IF('L3 input'!N11&lt;&gt;"",'L3 input'!N11,"")</f>
         <v/>
       </c>
       <c r="F11" s="81" t="n"/>
@@ -12261,11 +12536,11 @@
         <v/>
       </c>
       <c r="D12" s="76">
-        <f>IF('L3 input'!G12&lt;&gt;"",'L3 input'!G12,"")</f>
+        <f>IF('L3 input'!H12&lt;&gt;"",'L3 input'!H12,"")</f>
         <v/>
       </c>
       <c r="E12" s="76">
-        <f>IF('L3 input'!M12&lt;&gt;"",'L3 input'!M12,"")</f>
+        <f>IF('L3 input'!N12&lt;&gt;"",'L3 input'!N12,"")</f>
         <v/>
       </c>
       <c r="F12" s="77" t="n"/>
@@ -12608,11 +12883,11 @@
         <v/>
       </c>
       <c r="D13" s="76">
-        <f>IF('L3 input'!G13&lt;&gt;"",'L3 input'!G13,"")</f>
+        <f>IF('L3 input'!H13&lt;&gt;"",'L3 input'!H13,"")</f>
         <v/>
       </c>
       <c r="E13" s="76">
-        <f>IF('L3 input'!M13&lt;&gt;"",'L3 input'!M13,"")</f>
+        <f>IF('L3 input'!N13&lt;&gt;"",'L3 input'!N13,"")</f>
         <v/>
       </c>
       <c r="F13" s="81" t="n"/>
@@ -12955,11 +13230,11 @@
         <v/>
       </c>
       <c r="D14" s="76">
-        <f>IF('L3 input'!G14&lt;&gt;"",'L3 input'!G14,"")</f>
+        <f>IF('L3 input'!H14&lt;&gt;"",'L3 input'!H14,"")</f>
         <v/>
       </c>
       <c r="E14" s="76">
-        <f>IF('L3 input'!M14&lt;&gt;"",'L3 input'!M14,"")</f>
+        <f>IF('L3 input'!N14&lt;&gt;"",'L3 input'!N14,"")</f>
         <v/>
       </c>
       <c r="F14" s="77" t="n"/>
@@ -13302,11 +13577,11 @@
         <v/>
       </c>
       <c r="D15" s="76">
-        <f>IF('L3 input'!G15&lt;&gt;"",'L3 input'!G15,"")</f>
+        <f>IF('L3 input'!H15&lt;&gt;"",'L3 input'!H15,"")</f>
         <v/>
       </c>
       <c r="E15" s="76">
-        <f>IF('L3 input'!M15&lt;&gt;"",'L3 input'!M15,"")</f>
+        <f>IF('L3 input'!N15&lt;&gt;"",'L3 input'!N15,"")</f>
         <v/>
       </c>
       <c r="F15" s="81" t="n"/>
@@ -13649,11 +13924,11 @@
         <v/>
       </c>
       <c r="D16" s="76">
-        <f>IF('L3 input'!G16&lt;&gt;"",'L3 input'!G16,"")</f>
+        <f>IF('L3 input'!H16&lt;&gt;"",'L3 input'!H16,"")</f>
         <v/>
       </c>
       <c r="E16" s="76">
-        <f>IF('L3 input'!M16&lt;&gt;"",'L3 input'!M16,"")</f>
+        <f>IF('L3 input'!N16&lt;&gt;"",'L3 input'!N16,"")</f>
         <v/>
       </c>
       <c r="F16" s="77" t="n"/>
@@ -13996,11 +14271,11 @@
         <v/>
       </c>
       <c r="D17" s="76">
-        <f>IF('L3 input'!G17&lt;&gt;"",'L3 input'!G17,"")</f>
+        <f>IF('L3 input'!H17&lt;&gt;"",'L3 input'!H17,"")</f>
         <v/>
       </c>
       <c r="E17" s="76">
-        <f>IF('L3 input'!M17&lt;&gt;"",'L3 input'!M17,"")</f>
+        <f>IF('L3 input'!N17&lt;&gt;"",'L3 input'!N17,"")</f>
         <v/>
       </c>
       <c r="F17" s="81" t="n"/>
@@ -14343,11 +14618,11 @@
         <v/>
       </c>
       <c r="D18" s="76">
-        <f>IF('L3 input'!G18&lt;&gt;"",'L3 input'!G18,"")</f>
+        <f>IF('L3 input'!H18&lt;&gt;"",'L3 input'!H18,"")</f>
         <v/>
       </c>
       <c r="E18" s="76">
-        <f>IF('L3 input'!M18&lt;&gt;"",'L3 input'!M18,"")</f>
+        <f>IF('L3 input'!N18&lt;&gt;"",'L3 input'!N18,"")</f>
         <v/>
       </c>
       <c r="F18" s="77" t="n"/>
@@ -14690,11 +14965,11 @@
         <v/>
       </c>
       <c r="D19" s="76">
-        <f>IF('L3 input'!G19&lt;&gt;"",'L3 input'!G19,"")</f>
+        <f>IF('L3 input'!H19&lt;&gt;"",'L3 input'!H19,"")</f>
         <v/>
       </c>
       <c r="E19" s="76">
-        <f>IF('L3 input'!M19&lt;&gt;"",'L3 input'!M19,"")</f>
+        <f>IF('L3 input'!N19&lt;&gt;"",'L3 input'!N19,"")</f>
         <v/>
       </c>
       <c r="F19" s="81" t="n"/>
@@ -15037,11 +15312,11 @@
         <v/>
       </c>
       <c r="D20" s="76">
-        <f>IF('L3 input'!G20&lt;&gt;"",'L3 input'!G20,"")</f>
+        <f>IF('L3 input'!H20&lt;&gt;"",'L3 input'!H20,"")</f>
         <v/>
       </c>
       <c r="E20" s="76">
-        <f>IF('L3 input'!M20&lt;&gt;"",'L3 input'!M20,"")</f>
+        <f>IF('L3 input'!N20&lt;&gt;"",'L3 input'!N20,"")</f>
         <v/>
       </c>
       <c r="F20" s="77" t="n"/>
@@ -15384,11 +15659,11 @@
         <v/>
       </c>
       <c r="D21" s="76">
-        <f>IF('L3 input'!G21&lt;&gt;"",'L3 input'!G21,"")</f>
+        <f>IF('L3 input'!H21&lt;&gt;"",'L3 input'!H21,"")</f>
         <v/>
       </c>
       <c r="E21" s="76">
-        <f>IF('L3 input'!M21&lt;&gt;"",'L3 input'!M21,"")</f>
+        <f>IF('L3 input'!N21&lt;&gt;"",'L3 input'!N21,"")</f>
         <v/>
       </c>
       <c r="F21" s="81" t="n"/>
@@ -15731,11 +16006,11 @@
         <v/>
       </c>
       <c r="D22" s="76">
-        <f>IF('L3 input'!G22&lt;&gt;"",'L3 input'!G22,"")</f>
+        <f>IF('L3 input'!H22&lt;&gt;"",'L3 input'!H22,"")</f>
         <v/>
       </c>
       <c r="E22" s="76">
-        <f>IF('L3 input'!M22&lt;&gt;"",'L3 input'!M22,"")</f>
+        <f>IF('L3 input'!N22&lt;&gt;"",'L3 input'!N22,"")</f>
         <v/>
       </c>
       <c r="F22" s="77" t="n"/>
@@ -16078,11 +16353,11 @@
         <v/>
       </c>
       <c r="D23" s="76">
-        <f>IF('L3 input'!G23&lt;&gt;"",'L3 input'!G23,"")</f>
+        <f>IF('L3 input'!H23&lt;&gt;"",'L3 input'!H23,"")</f>
         <v/>
       </c>
       <c r="E23" s="76">
-        <f>IF('L3 input'!M23&lt;&gt;"",'L3 input'!M23,"")</f>
+        <f>IF('L3 input'!N23&lt;&gt;"",'L3 input'!N23,"")</f>
         <v/>
       </c>
       <c r="F23" s="81" t="n"/>
@@ -16425,11 +16700,11 @@
         <v/>
       </c>
       <c r="D24" s="76">
-        <f>IF('L3 input'!G24&lt;&gt;"",'L3 input'!G24,"")</f>
+        <f>IF('L3 input'!H24&lt;&gt;"",'L3 input'!H24,"")</f>
         <v/>
       </c>
       <c r="E24" s="76">
-        <f>IF('L3 input'!M24&lt;&gt;"",'L3 input'!M24,"")</f>
+        <f>IF('L3 input'!N24&lt;&gt;"",'L3 input'!N24,"")</f>
         <v/>
       </c>
       <c r="F24" s="77" t="n"/>
@@ -16772,11 +17047,11 @@
         <v/>
       </c>
       <c r="D25" s="76">
-        <f>IF('L3 input'!G25&lt;&gt;"",'L3 input'!G25,"")</f>
+        <f>IF('L3 input'!H25&lt;&gt;"",'L3 input'!H25,"")</f>
         <v/>
       </c>
       <c r="E25" s="76">
-        <f>IF('L3 input'!M25&lt;&gt;"",'L3 input'!M25,"")</f>
+        <f>IF('L3 input'!N25&lt;&gt;"",'L3 input'!N25,"")</f>
         <v/>
       </c>
       <c r="F25" s="81" t="n"/>
@@ -17119,11 +17394,11 @@
         <v/>
       </c>
       <c r="D26" s="76">
-        <f>IF('L3 input'!G26&lt;&gt;"",'L3 input'!G26,"")</f>
+        <f>IF('L3 input'!H26&lt;&gt;"",'L3 input'!H26,"")</f>
         <v/>
       </c>
       <c r="E26" s="76">
-        <f>IF('L3 input'!M26&lt;&gt;"",'L3 input'!M26,"")</f>
+        <f>IF('L3 input'!N26&lt;&gt;"",'L3 input'!N26,"")</f>
         <v/>
       </c>
       <c r="F26" s="77" t="n"/>
@@ -17466,11 +17741,11 @@
         <v/>
       </c>
       <c r="D27" s="76">
-        <f>IF('L3 input'!G27&lt;&gt;"",'L3 input'!G27,"")</f>
+        <f>IF('L3 input'!H27&lt;&gt;"",'L3 input'!H27,"")</f>
         <v/>
       </c>
       <c r="E27" s="76">
-        <f>IF('L3 input'!M27&lt;&gt;"",'L3 input'!M27,"")</f>
+        <f>IF('L3 input'!N27&lt;&gt;"",'L3 input'!N27,"")</f>
         <v/>
       </c>
       <c r="F27" s="81" t="n"/>
@@ -17813,11 +18088,11 @@
         <v/>
       </c>
       <c r="D28" s="76">
-        <f>IF('L3 input'!G28&lt;&gt;"",'L3 input'!G28,"")</f>
+        <f>IF('L3 input'!H28&lt;&gt;"",'L3 input'!H28,"")</f>
         <v/>
       </c>
       <c r="E28" s="76">
-        <f>IF('L3 input'!M28&lt;&gt;"",'L3 input'!M28,"")</f>
+        <f>IF('L3 input'!N28&lt;&gt;"",'L3 input'!N28,"")</f>
         <v/>
       </c>
       <c r="F28" s="77" t="n"/>
@@ -18160,11 +18435,11 @@
         <v/>
       </c>
       <c r="D29" s="76">
-        <f>IF('L3 input'!G29&lt;&gt;"",'L3 input'!G29,"")</f>
+        <f>IF('L3 input'!H29&lt;&gt;"",'L3 input'!H29,"")</f>
         <v/>
       </c>
       <c r="E29" s="76">
-        <f>IF('L3 input'!M29&lt;&gt;"",'L3 input'!M29,"")</f>
+        <f>IF('L3 input'!N29&lt;&gt;"",'L3 input'!N29,"")</f>
         <v/>
       </c>
       <c r="F29" s="81" t="n"/>
@@ -18507,11 +18782,11 @@
         <v/>
       </c>
       <c r="D30" s="76">
-        <f>IF('L3 input'!G30&lt;&gt;"",'L3 input'!G30,"")</f>
+        <f>IF('L3 input'!H30&lt;&gt;"",'L3 input'!H30,"")</f>
         <v/>
       </c>
       <c r="E30" s="76">
-        <f>IF('L3 input'!M30&lt;&gt;"",'L3 input'!M30,"")</f>
+        <f>IF('L3 input'!N30&lt;&gt;"",'L3 input'!N30,"")</f>
         <v/>
       </c>
       <c r="F30" s="77" t="n"/>
@@ -18854,11 +19129,11 @@
         <v/>
       </c>
       <c r="D31" s="76">
-        <f>IF('L3 input'!G31&lt;&gt;"",'L3 input'!G31,"")</f>
+        <f>IF('L3 input'!H31&lt;&gt;"",'L3 input'!H31,"")</f>
         <v/>
       </c>
       <c r="E31" s="76">
-        <f>IF('L3 input'!M31&lt;&gt;"",'L3 input'!M31,"")</f>
+        <f>IF('L3 input'!N31&lt;&gt;"",'L3 input'!N31,"")</f>
         <v/>
       </c>
       <c r="F31" s="81" t="n"/>
@@ -19201,11 +19476,11 @@
         <v/>
       </c>
       <c r="D32" s="76">
-        <f>IF('L3 input'!G32&lt;&gt;"",'L3 input'!G32,"")</f>
+        <f>IF('L3 input'!H32&lt;&gt;"",'L3 input'!H32,"")</f>
         <v/>
       </c>
       <c r="E32" s="76">
-        <f>IF('L3 input'!M32&lt;&gt;"",'L3 input'!M32,"")</f>
+        <f>IF('L3 input'!N32&lt;&gt;"",'L3 input'!N32,"")</f>
         <v/>
       </c>
       <c r="F32" s="77" t="n"/>
@@ -19548,11 +19823,11 @@
         <v/>
       </c>
       <c r="D33" s="76">
-        <f>IF('L3 input'!G33&lt;&gt;"",'L3 input'!G33,"")</f>
+        <f>IF('L3 input'!H33&lt;&gt;"",'L3 input'!H33,"")</f>
         <v/>
       </c>
       <c r="E33" s="76">
-        <f>IF('L3 input'!M33&lt;&gt;"",'L3 input'!M33,"")</f>
+        <f>IF('L3 input'!N33&lt;&gt;"",'L3 input'!N33,"")</f>
         <v/>
       </c>
       <c r="F33" s="81" t="n"/>
@@ -19895,11 +20170,11 @@
         <v/>
       </c>
       <c r="D34" s="76">
-        <f>IF('L3 input'!G34&lt;&gt;"",'L3 input'!G34,"")</f>
+        <f>IF('L3 input'!H34&lt;&gt;"",'L3 input'!H34,"")</f>
         <v/>
       </c>
       <c r="E34" s="76">
-        <f>IF('L3 input'!M34&lt;&gt;"",'L3 input'!M34,"")</f>
+        <f>IF('L3 input'!N34&lt;&gt;"",'L3 input'!N34,"")</f>
         <v/>
       </c>
       <c r="F34" s="77" t="n"/>
@@ -20242,11 +20517,11 @@
         <v/>
       </c>
       <c r="D35" s="76">
-        <f>IF('L3 input'!G35&lt;&gt;"",'L3 input'!G35,"")</f>
+        <f>IF('L3 input'!H35&lt;&gt;"",'L3 input'!H35,"")</f>
         <v/>
       </c>
       <c r="E35" s="76">
-        <f>IF('L3 input'!M35&lt;&gt;"",'L3 input'!M35,"")</f>
+        <f>IF('L3 input'!N35&lt;&gt;"",'L3 input'!N35,"")</f>
         <v/>
       </c>
       <c r="F35" s="81" t="n"/>
@@ -20589,11 +20864,11 @@
         <v/>
       </c>
       <c r="D36" s="76">
-        <f>IF('L3 input'!G36&lt;&gt;"",'L3 input'!G36,"")</f>
+        <f>IF('L3 input'!H36&lt;&gt;"",'L3 input'!H36,"")</f>
         <v/>
       </c>
       <c r="E36" s="76">
-        <f>IF('L3 input'!M36&lt;&gt;"",'L3 input'!M36,"")</f>
+        <f>IF('L3 input'!N36&lt;&gt;"",'L3 input'!N36,"")</f>
         <v/>
       </c>
       <c r="F36" s="77" t="n"/>
@@ -20936,11 +21211,11 @@
         <v/>
       </c>
       <c r="D37" s="76">
-        <f>IF('L3 input'!G37&lt;&gt;"",'L3 input'!G37,"")</f>
+        <f>IF('L3 input'!H37&lt;&gt;"",'L3 input'!H37,"")</f>
         <v/>
       </c>
       <c r="E37" s="76">
-        <f>IF('L3 input'!M37&lt;&gt;"",'L3 input'!M37,"")</f>
+        <f>IF('L3 input'!N37&lt;&gt;"",'L3 input'!N37,"")</f>
         <v/>
       </c>
       <c r="F37" s="81" t="n"/>
@@ -21283,11 +21558,11 @@
         <v/>
       </c>
       <c r="D38" s="76">
-        <f>IF('L3 input'!G38&lt;&gt;"",'L3 input'!G38,"")</f>
+        <f>IF('L3 input'!H38&lt;&gt;"",'L3 input'!H38,"")</f>
         <v/>
       </c>
       <c r="E38" s="76">
-        <f>IF('L3 input'!M38&lt;&gt;"",'L3 input'!M38,"")</f>
+        <f>IF('L3 input'!N38&lt;&gt;"",'L3 input'!N38,"")</f>
         <v/>
       </c>
       <c r="F38" s="77" t="n"/>
@@ -21630,11 +21905,11 @@
         <v/>
       </c>
       <c r="D39" s="76">
-        <f>IF('L3 input'!G39&lt;&gt;"",'L3 input'!G39,"")</f>
+        <f>IF('L3 input'!H39&lt;&gt;"",'L3 input'!H39,"")</f>
         <v/>
       </c>
       <c r="E39" s="76">
-        <f>IF('L3 input'!M39&lt;&gt;"",'L3 input'!M39,"")</f>
+        <f>IF('L3 input'!N39&lt;&gt;"",'L3 input'!N39,"")</f>
         <v/>
       </c>
       <c r="F39" s="81" t="n"/>
@@ -21977,11 +22252,11 @@
         <v/>
       </c>
       <c r="D40" s="76">
-        <f>IF('L3 input'!G40&lt;&gt;"",'L3 input'!G40,"")</f>
+        <f>IF('L3 input'!H40&lt;&gt;"",'L3 input'!H40,"")</f>
         <v/>
       </c>
       <c r="E40" s="76">
-        <f>IF('L3 input'!M40&lt;&gt;"",'L3 input'!M40,"")</f>
+        <f>IF('L3 input'!N40&lt;&gt;"",'L3 input'!N40,"")</f>
         <v/>
       </c>
       <c r="F40" s="77" t="n"/>
@@ -22324,11 +22599,11 @@
         <v/>
       </c>
       <c r="D41" s="76">
-        <f>IF('L3 input'!G41&lt;&gt;"",'L3 input'!G41,"")</f>
+        <f>IF('L3 input'!H41&lt;&gt;"",'L3 input'!H41,"")</f>
         <v/>
       </c>
       <c r="E41" s="76">
-        <f>IF('L3 input'!M41&lt;&gt;"",'L3 input'!M41,"")</f>
+        <f>IF('L3 input'!N41&lt;&gt;"",'L3 input'!N41,"")</f>
         <v/>
       </c>
       <c r="F41" s="81" t="n"/>
@@ -22671,11 +22946,11 @@
         <v/>
       </c>
       <c r="D42" s="76">
-        <f>IF('L3 input'!G42&lt;&gt;"",'L3 input'!G42,"")</f>
+        <f>IF('L3 input'!H42&lt;&gt;"",'L3 input'!H42,"")</f>
         <v/>
       </c>
       <c r="E42" s="76">
-        <f>IF('L3 input'!M42&lt;&gt;"",'L3 input'!M42,"")</f>
+        <f>IF('L3 input'!N42&lt;&gt;"",'L3 input'!N42,"")</f>
         <v/>
       </c>
       <c r="F42" s="77" t="n"/>
@@ -23018,11 +23293,11 @@
         <v/>
       </c>
       <c r="D43" s="76">
-        <f>IF('L3 input'!G43&lt;&gt;"",'L3 input'!G43,"")</f>
+        <f>IF('L3 input'!H43&lt;&gt;"",'L3 input'!H43,"")</f>
         <v/>
       </c>
       <c r="E43" s="76">
-        <f>IF('L3 input'!M43&lt;&gt;"",'L3 input'!M43,"")</f>
+        <f>IF('L3 input'!N43&lt;&gt;"",'L3 input'!N43,"")</f>
         <v/>
       </c>
       <c r="F43" s="81" t="n"/>
@@ -23365,11 +23640,11 @@
         <v/>
       </c>
       <c r="D44" s="76">
-        <f>IF('L3 input'!G44&lt;&gt;"",'L3 input'!G44,"")</f>
+        <f>IF('L3 input'!H44&lt;&gt;"",'L3 input'!H44,"")</f>
         <v/>
       </c>
       <c r="E44" s="76">
-        <f>IF('L3 input'!M44&lt;&gt;"",'L3 input'!M44,"")</f>
+        <f>IF('L3 input'!N44&lt;&gt;"",'L3 input'!N44,"")</f>
         <v/>
       </c>
       <c r="F44" s="77" t="n"/>
@@ -23712,11 +23987,11 @@
         <v/>
       </c>
       <c r="D45" s="76">
-        <f>IF('L3 input'!G45&lt;&gt;"",'L3 input'!G45,"")</f>
+        <f>IF('L3 input'!H45&lt;&gt;"",'L3 input'!H45,"")</f>
         <v/>
       </c>
       <c r="E45" s="76">
-        <f>IF('L3 input'!M45&lt;&gt;"",'L3 input'!M45,"")</f>
+        <f>IF('L3 input'!N45&lt;&gt;"",'L3 input'!N45,"")</f>
         <v/>
       </c>
       <c r="F45" s="81" t="n"/>
@@ -24059,11 +24334,11 @@
         <v/>
       </c>
       <c r="D46" s="76">
-        <f>IF('L3 input'!G46&lt;&gt;"",'L3 input'!G46,"")</f>
+        <f>IF('L3 input'!H46&lt;&gt;"",'L3 input'!H46,"")</f>
         <v/>
       </c>
       <c r="E46" s="76">
-        <f>IF('L3 input'!M46&lt;&gt;"",'L3 input'!M46,"")</f>
+        <f>IF('L3 input'!N46&lt;&gt;"",'L3 input'!N46,"")</f>
         <v/>
       </c>
       <c r="F46" s="77" t="n"/>
@@ -24406,11 +24681,11 @@
         <v/>
       </c>
       <c r="D47" s="76">
-        <f>IF('L3 input'!G47&lt;&gt;"",'L3 input'!G47,"")</f>
+        <f>IF('L3 input'!H47&lt;&gt;"",'L3 input'!H47,"")</f>
         <v/>
       </c>
       <c r="E47" s="76">
-        <f>IF('L3 input'!M47&lt;&gt;"",'L3 input'!M47,"")</f>
+        <f>IF('L3 input'!N47&lt;&gt;"",'L3 input'!N47,"")</f>
         <v/>
       </c>
       <c r="F47" s="81" t="n"/>
@@ -24753,11 +25028,11 @@
         <v/>
       </c>
       <c r="D48" s="76">
-        <f>IF('L3 input'!G48&lt;&gt;"",'L3 input'!G48,"")</f>
+        <f>IF('L3 input'!H48&lt;&gt;"",'L3 input'!H48,"")</f>
         <v/>
       </c>
       <c r="E48" s="76">
-        <f>IF('L3 input'!M48&lt;&gt;"",'L3 input'!M48,"")</f>
+        <f>IF('L3 input'!N48&lt;&gt;"",'L3 input'!N48,"")</f>
         <v/>
       </c>
       <c r="F48" s="77" t="n"/>
@@ -25100,11 +25375,11 @@
         <v/>
       </c>
       <c r="D49" s="76">
-        <f>IF('L3 input'!G49&lt;&gt;"",'L3 input'!G49,"")</f>
+        <f>IF('L3 input'!H49&lt;&gt;"",'L3 input'!H49,"")</f>
         <v/>
       </c>
       <c r="E49" s="76">
-        <f>IF('L3 input'!M49&lt;&gt;"",'L3 input'!M49,"")</f>
+        <f>IF('L3 input'!N49&lt;&gt;"",'L3 input'!N49,"")</f>
         <v/>
       </c>
       <c r="F49" s="81" t="n"/>
@@ -25447,11 +25722,11 @@
         <v/>
       </c>
       <c r="D50" s="76">
-        <f>IF('L3 input'!G50&lt;&gt;"",'L3 input'!G50,"")</f>
+        <f>IF('L3 input'!H50&lt;&gt;"",'L3 input'!H50,"")</f>
         <v/>
       </c>
       <c r="E50" s="76">
-        <f>IF('L3 input'!M50&lt;&gt;"",'L3 input'!M50,"")</f>
+        <f>IF('L3 input'!N50&lt;&gt;"",'L3 input'!N50,"")</f>
         <v/>
       </c>
       <c r="F50" s="77" t="n"/>
@@ -25794,11 +26069,11 @@
         <v/>
       </c>
       <c r="D51" s="76">
-        <f>IF('L3 input'!G51&lt;&gt;"",'L3 input'!G51,"")</f>
+        <f>IF('L3 input'!H51&lt;&gt;"",'L3 input'!H51,"")</f>
         <v/>
       </c>
       <c r="E51" s="76">
-        <f>IF('L3 input'!M51&lt;&gt;"",'L3 input'!M51,"")</f>
+        <f>IF('L3 input'!N51&lt;&gt;"",'L3 input'!N51,"")</f>
         <v/>
       </c>
       <c r="F51" s="81" t="n"/>
@@ -26141,11 +26416,11 @@
         <v/>
       </c>
       <c r="D52" s="76">
-        <f>IF('L3 input'!G52&lt;&gt;"",'L3 input'!G52,"")</f>
+        <f>IF('L3 input'!H52&lt;&gt;"",'L3 input'!H52,"")</f>
         <v/>
       </c>
       <c r="E52" s="76">
-        <f>IF('L3 input'!M52&lt;&gt;"",'L3 input'!M52,"")</f>
+        <f>IF('L3 input'!N52&lt;&gt;"",'L3 input'!N52,"")</f>
         <v/>
       </c>
       <c r="F52" s="77" t="n"/>
@@ -26488,11 +26763,11 @@
         <v/>
       </c>
       <c r="D53" s="76">
-        <f>IF('L3 input'!G53&lt;&gt;"",'L3 input'!G53,"")</f>
+        <f>IF('L3 input'!H53&lt;&gt;"",'L3 input'!H53,"")</f>
         <v/>
       </c>
       <c r="E53" s="76">
-        <f>IF('L3 input'!M53&lt;&gt;"",'L3 input'!M53,"")</f>
+        <f>IF('L3 input'!N53&lt;&gt;"",'L3 input'!N53,"")</f>
         <v/>
       </c>
       <c r="F53" s="81" t="n"/>
@@ -26835,11 +27110,11 @@
         <v/>
       </c>
       <c r="D54" s="76">
-        <f>IF('L3 input'!G54&lt;&gt;"",'L3 input'!G54,"")</f>
+        <f>IF('L3 input'!H54&lt;&gt;"",'L3 input'!H54,"")</f>
         <v/>
       </c>
       <c r="E54" s="76">
-        <f>IF('L3 input'!M54&lt;&gt;"",'L3 input'!M54,"")</f>
+        <f>IF('L3 input'!N54&lt;&gt;"",'L3 input'!N54,"")</f>
         <v/>
       </c>
       <c r="F54" s="77" t="n"/>
@@ -27182,11 +27457,11 @@
         <v/>
       </c>
       <c r="D55" s="76">
-        <f>IF('L3 input'!G55&lt;&gt;"",'L3 input'!G55,"")</f>
+        <f>IF('L3 input'!H55&lt;&gt;"",'L3 input'!H55,"")</f>
         <v/>
       </c>
       <c r="E55" s="76">
-        <f>IF('L3 input'!M55&lt;&gt;"",'L3 input'!M55,"")</f>
+        <f>IF('L3 input'!N55&lt;&gt;"",'L3 input'!N55,"")</f>
         <v/>
       </c>
       <c r="F55" s="81" t="n"/>
@@ -27529,11 +27804,11 @@
         <v/>
       </c>
       <c r="D56" s="76">
-        <f>IF('L3 input'!G56&lt;&gt;"",'L3 input'!G56,"")</f>
+        <f>IF('L3 input'!H56&lt;&gt;"",'L3 input'!H56,"")</f>
         <v/>
       </c>
       <c r="E56" s="76">
-        <f>IF('L3 input'!M56&lt;&gt;"",'L3 input'!M56,"")</f>
+        <f>IF('L3 input'!N56&lt;&gt;"",'L3 input'!N56,"")</f>
         <v/>
       </c>
       <c r="F56" s="77" t="n"/>
@@ -27876,11 +28151,11 @@
         <v/>
       </c>
       <c r="D57" s="76">
-        <f>IF('L3 input'!G57&lt;&gt;"",'L3 input'!G57,"")</f>
+        <f>IF('L3 input'!H57&lt;&gt;"",'L3 input'!H57,"")</f>
         <v/>
       </c>
       <c r="E57" s="76">
-        <f>IF('L3 input'!M57&lt;&gt;"",'L3 input'!M57,"")</f>
+        <f>IF('L3 input'!N57&lt;&gt;"",'L3 input'!N57,"")</f>
         <v/>
       </c>
       <c r="F57" s="81" t="n"/>
@@ -28223,11 +28498,11 @@
         <v/>
       </c>
       <c r="D58" s="76">
-        <f>IF('L3 input'!G58&lt;&gt;"",'L3 input'!G58,"")</f>
+        <f>IF('L3 input'!H58&lt;&gt;"",'L3 input'!H58,"")</f>
         <v/>
       </c>
       <c r="E58" s="76">
-        <f>IF('L3 input'!M58&lt;&gt;"",'L3 input'!M58,"")</f>
+        <f>IF('L3 input'!N58&lt;&gt;"",'L3 input'!N58,"")</f>
         <v/>
       </c>
       <c r="F58" s="77" t="n"/>
@@ -28570,11 +28845,11 @@
         <v/>
       </c>
       <c r="D59" s="76">
-        <f>IF('L3 input'!G59&lt;&gt;"",'L3 input'!G59,"")</f>
+        <f>IF('L3 input'!H59&lt;&gt;"",'L3 input'!H59,"")</f>
         <v/>
       </c>
       <c r="E59" s="76">
-        <f>IF('L3 input'!M59&lt;&gt;"",'L3 input'!M59,"")</f>
+        <f>IF('L3 input'!N59&lt;&gt;"",'L3 input'!N59,"")</f>
         <v/>
       </c>
       <c r="F59" s="81" t="n"/>
@@ -28917,11 +29192,11 @@
         <v/>
       </c>
       <c r="D60" s="76">
-        <f>IF('L3 input'!G60&lt;&gt;"",'L3 input'!G60,"")</f>
+        <f>IF('L3 input'!H60&lt;&gt;"",'L3 input'!H60,"")</f>
         <v/>
       </c>
       <c r="E60" s="76">
-        <f>IF('L3 input'!M60&lt;&gt;"",'L3 input'!M60,"")</f>
+        <f>IF('L3 input'!N60&lt;&gt;"",'L3 input'!N60,"")</f>
         <v/>
       </c>
       <c r="F60" s="77" t="n"/>
@@ -29264,11 +29539,11 @@
         <v/>
       </c>
       <c r="D61" s="76">
-        <f>IF('L3 input'!G61&lt;&gt;"",'L3 input'!G61,"")</f>
+        <f>IF('L3 input'!H61&lt;&gt;"",'L3 input'!H61,"")</f>
         <v/>
       </c>
       <c r="E61" s="76">
-        <f>IF('L3 input'!M61&lt;&gt;"",'L3 input'!M61,"")</f>
+        <f>IF('L3 input'!N61&lt;&gt;"",'L3 input'!N61,"")</f>
         <v/>
       </c>
       <c r="F61" s="81" t="n"/>
@@ -29611,11 +29886,11 @@
         <v/>
       </c>
       <c r="D62" s="76">
-        <f>IF('L3 input'!G62&lt;&gt;"",'L3 input'!G62,"")</f>
+        <f>IF('L3 input'!H62&lt;&gt;"",'L3 input'!H62,"")</f>
         <v/>
       </c>
       <c r="E62" s="76">
-        <f>IF('L3 input'!M62&lt;&gt;"",'L3 input'!M62,"")</f>
+        <f>IF('L3 input'!N62&lt;&gt;"",'L3 input'!N62,"")</f>
         <v/>
       </c>
       <c r="F62" s="77" t="n"/>
@@ -29958,11 +30233,11 @@
         <v/>
       </c>
       <c r="D63" s="76">
-        <f>IF('L3 input'!G63&lt;&gt;"",'L3 input'!G63,"")</f>
+        <f>IF('L3 input'!H63&lt;&gt;"",'L3 input'!H63,"")</f>
         <v/>
       </c>
       <c r="E63" s="76">
-        <f>IF('L3 input'!M63&lt;&gt;"",'L3 input'!M63,"")</f>
+        <f>IF('L3 input'!N63&lt;&gt;"",'L3 input'!N63,"")</f>
         <v/>
       </c>
       <c r="F63" s="81" t="n"/>
@@ -30305,11 +30580,11 @@
         <v/>
       </c>
       <c r="D64" s="76">
-        <f>IF('L3 input'!G64&lt;&gt;"",'L3 input'!G64,"")</f>
+        <f>IF('L3 input'!H64&lt;&gt;"",'L3 input'!H64,"")</f>
         <v/>
       </c>
       <c r="E64" s="76">
-        <f>IF('L3 input'!M64&lt;&gt;"",'L3 input'!M64,"")</f>
+        <f>IF('L3 input'!N64&lt;&gt;"",'L3 input'!N64,"")</f>
         <v/>
       </c>
       <c r="F64" s="77" t="n"/>
@@ -30652,11 +30927,11 @@
         <v/>
       </c>
       <c r="D65" s="76">
-        <f>IF('L3 input'!G65&lt;&gt;"",'L3 input'!G65,"")</f>
+        <f>IF('L3 input'!H65&lt;&gt;"",'L3 input'!H65,"")</f>
         <v/>
       </c>
       <c r="E65" s="76">
-        <f>IF('L3 input'!M65&lt;&gt;"",'L3 input'!M65,"")</f>
+        <f>IF('L3 input'!N65&lt;&gt;"",'L3 input'!N65,"")</f>
         <v/>
       </c>
       <c r="F65" s="81" t="n"/>
@@ -30999,11 +31274,11 @@
         <v/>
       </c>
       <c r="D66" s="76">
-        <f>IF('L3 input'!G66&lt;&gt;"",'L3 input'!G66,"")</f>
+        <f>IF('L3 input'!H66&lt;&gt;"",'L3 input'!H66,"")</f>
         <v/>
       </c>
       <c r="E66" s="76">
-        <f>IF('L3 input'!M66&lt;&gt;"",'L3 input'!M66,"")</f>
+        <f>IF('L3 input'!N66&lt;&gt;"",'L3 input'!N66,"")</f>
         <v/>
       </c>
       <c r="F66" s="77" t="n"/>
@@ -31346,11 +31621,11 @@
         <v/>
       </c>
       <c r="D67" s="76">
-        <f>IF('L3 input'!G67&lt;&gt;"",'L3 input'!G67,"")</f>
+        <f>IF('L3 input'!H67&lt;&gt;"",'L3 input'!H67,"")</f>
         <v/>
       </c>
       <c r="E67" s="76">
-        <f>IF('L3 input'!M67&lt;&gt;"",'L3 input'!M67,"")</f>
+        <f>IF('L3 input'!N67&lt;&gt;"",'L3 input'!N67,"")</f>
         <v/>
       </c>
       <c r="F67" s="81" t="n"/>
@@ -31693,11 +31968,11 @@
         <v/>
       </c>
       <c r="D68" s="76">
-        <f>IF('L3 input'!G68&lt;&gt;"",'L3 input'!G68,"")</f>
+        <f>IF('L3 input'!H68&lt;&gt;"",'L3 input'!H68,"")</f>
         <v/>
       </c>
       <c r="E68" s="76">
-        <f>IF('L3 input'!M68&lt;&gt;"",'L3 input'!M68,"")</f>
+        <f>IF('L3 input'!N68&lt;&gt;"",'L3 input'!N68,"")</f>
         <v/>
       </c>
       <c r="F68" s="77" t="n"/>
@@ -32040,11 +32315,11 @@
         <v/>
       </c>
       <c r="D69" s="76">
-        <f>IF('L3 input'!G69&lt;&gt;"",'L3 input'!G69,"")</f>
+        <f>IF('L3 input'!H69&lt;&gt;"",'L3 input'!H69,"")</f>
         <v/>
       </c>
       <c r="E69" s="76">
-        <f>IF('L3 input'!M69&lt;&gt;"",'L3 input'!M69,"")</f>
+        <f>IF('L3 input'!N69&lt;&gt;"",'L3 input'!N69,"")</f>
         <v/>
       </c>
       <c r="F69" s="81" t="n"/>
@@ -32387,11 +32662,11 @@
         <v/>
       </c>
       <c r="D70" s="76">
-        <f>IF('L3 input'!G70&lt;&gt;"",'L3 input'!G70,"")</f>
+        <f>IF('L3 input'!H70&lt;&gt;"",'L3 input'!H70,"")</f>
         <v/>
       </c>
       <c r="E70" s="76">
-        <f>IF('L3 input'!M70&lt;&gt;"",'L3 input'!M70,"")</f>
+        <f>IF('L3 input'!N70&lt;&gt;"",'L3 input'!N70,"")</f>
         <v/>
       </c>
       <c r="F70" s="77" t="n"/>
@@ -32734,11 +33009,11 @@
         <v/>
       </c>
       <c r="D71" s="76">
-        <f>IF('L3 input'!G71&lt;&gt;"",'L3 input'!G71,"")</f>
+        <f>IF('L3 input'!H71&lt;&gt;"",'L3 input'!H71,"")</f>
         <v/>
       </c>
       <c r="E71" s="76">
-        <f>IF('L3 input'!M71&lt;&gt;"",'L3 input'!M71,"")</f>
+        <f>IF('L3 input'!N71&lt;&gt;"",'L3 input'!N71,"")</f>
         <v/>
       </c>
       <c r="F71" s="81" t="n"/>
@@ -33081,11 +33356,11 @@
         <v/>
       </c>
       <c r="D72" s="76">
-        <f>IF('L3 input'!G72&lt;&gt;"",'L3 input'!G72,"")</f>
+        <f>IF('L3 input'!H72&lt;&gt;"",'L3 input'!H72,"")</f>
         <v/>
       </c>
       <c r="E72" s="76">
-        <f>IF('L3 input'!M72&lt;&gt;"",'L3 input'!M72,"")</f>
+        <f>IF('L3 input'!N72&lt;&gt;"",'L3 input'!N72,"")</f>
         <v/>
       </c>
       <c r="F72" s="77" t="n"/>
@@ -33428,11 +33703,11 @@
         <v/>
       </c>
       <c r="D73" s="76">
-        <f>IF('L3 input'!G73&lt;&gt;"",'L3 input'!G73,"")</f>
+        <f>IF('L3 input'!H73&lt;&gt;"",'L3 input'!H73,"")</f>
         <v/>
       </c>
       <c r="E73" s="76">
-        <f>IF('L3 input'!M73&lt;&gt;"",'L3 input'!M73,"")</f>
+        <f>IF('L3 input'!N73&lt;&gt;"",'L3 input'!N73,"")</f>
         <v/>
       </c>
       <c r="F73" s="81" t="n"/>
@@ -33775,11 +34050,11 @@
         <v/>
       </c>
       <c r="D74" s="76">
-        <f>IF('L3 input'!G74&lt;&gt;"",'L3 input'!G74,"")</f>
+        <f>IF('L3 input'!H74&lt;&gt;"",'L3 input'!H74,"")</f>
         <v/>
       </c>
       <c r="E74" s="76">
-        <f>IF('L3 input'!M74&lt;&gt;"",'L3 input'!M74,"")</f>
+        <f>IF('L3 input'!N74&lt;&gt;"",'L3 input'!N74,"")</f>
         <v/>
       </c>
       <c r="F74" s="77" t="n"/>
@@ -34122,11 +34397,11 @@
         <v/>
       </c>
       <c r="D75" s="76">
-        <f>IF('L3 input'!G75&lt;&gt;"",'L3 input'!G75,"")</f>
+        <f>IF('L3 input'!H75&lt;&gt;"",'L3 input'!H75,"")</f>
         <v/>
       </c>
       <c r="E75" s="76">
-        <f>IF('L3 input'!M75&lt;&gt;"",'L3 input'!M75,"")</f>
+        <f>IF('L3 input'!N75&lt;&gt;"",'L3 input'!N75,"")</f>
         <v/>
       </c>
       <c r="F75" s="81" t="n"/>
@@ -34469,11 +34744,11 @@
         <v/>
       </c>
       <c r="D76" s="76">
-        <f>IF('L3 input'!G76&lt;&gt;"",'L3 input'!G76,"")</f>
+        <f>IF('L3 input'!H76&lt;&gt;"",'L3 input'!H76,"")</f>
         <v/>
       </c>
       <c r="E76" s="76">
-        <f>IF('L3 input'!M76&lt;&gt;"",'L3 input'!M76,"")</f>
+        <f>IF('L3 input'!N76&lt;&gt;"",'L3 input'!N76,"")</f>
         <v/>
       </c>
       <c r="F76" s="77" t="n"/>
@@ -34816,11 +35091,11 @@
         <v/>
       </c>
       <c r="D77" s="76">
-        <f>IF('L3 input'!G77&lt;&gt;"",'L3 input'!G77,"")</f>
+        <f>IF('L3 input'!H77&lt;&gt;"",'L3 input'!H77,"")</f>
         <v/>
       </c>
       <c r="E77" s="76">
-        <f>IF('L3 input'!M77&lt;&gt;"",'L3 input'!M77,"")</f>
+        <f>IF('L3 input'!N77&lt;&gt;"",'L3 input'!N77,"")</f>
         <v/>
       </c>
       <c r="F77" s="81" t="n"/>
@@ -35163,11 +35438,11 @@
         <v/>
       </c>
       <c r="D78" s="76">
-        <f>IF('L3 input'!G78&lt;&gt;"",'L3 input'!G78,"")</f>
+        <f>IF('L3 input'!H78&lt;&gt;"",'L3 input'!H78,"")</f>
         <v/>
       </c>
       <c r="E78" s="76">
-        <f>IF('L3 input'!M78&lt;&gt;"",'L3 input'!M78,"")</f>
+        <f>IF('L3 input'!N78&lt;&gt;"",'L3 input'!N78,"")</f>
         <v/>
       </c>
       <c r="F78" s="77" t="n"/>
@@ -35510,11 +35785,11 @@
         <v/>
       </c>
       <c r="D79" s="76">
-        <f>IF('L3 input'!G79&lt;&gt;"",'L3 input'!G79,"")</f>
+        <f>IF('L3 input'!H79&lt;&gt;"",'L3 input'!H79,"")</f>
         <v/>
       </c>
       <c r="E79" s="76">
-        <f>IF('L3 input'!M79&lt;&gt;"",'L3 input'!M79,"")</f>
+        <f>IF('L3 input'!N79&lt;&gt;"",'L3 input'!N79,"")</f>
         <v/>
       </c>
       <c r="F79" s="81" t="n"/>
@@ -35857,11 +36132,11 @@
         <v/>
       </c>
       <c r="D80" s="76">
-        <f>IF('L3 input'!G80&lt;&gt;"",'L3 input'!G80,"")</f>
+        <f>IF('L3 input'!H80&lt;&gt;"",'L3 input'!H80,"")</f>
         <v/>
       </c>
       <c r="E80" s="76">
-        <f>IF('L3 input'!M80&lt;&gt;"",'L3 input'!M80,"")</f>
+        <f>IF('L3 input'!N80&lt;&gt;"",'L3 input'!N80,"")</f>
         <v/>
       </c>
       <c r="F80" s="77" t="n"/>
@@ -36204,11 +36479,11 @@
         <v/>
       </c>
       <c r="D81" s="76">
-        <f>IF('L3 input'!G81&lt;&gt;"",'L3 input'!G81,"")</f>
+        <f>IF('L3 input'!H81&lt;&gt;"",'L3 input'!H81,"")</f>
         <v/>
       </c>
       <c r="E81" s="76">
-        <f>IF('L3 input'!M81&lt;&gt;"",'L3 input'!M81,"")</f>
+        <f>IF('L3 input'!N81&lt;&gt;"",'L3 input'!N81,"")</f>
         <v/>
       </c>
       <c r="F81" s="81" t="n"/>
@@ -36551,11 +36826,11 @@
         <v/>
       </c>
       <c r="D82" s="76">
-        <f>IF('L3 input'!G82&lt;&gt;"",'L3 input'!G82,"")</f>
+        <f>IF('L3 input'!H82&lt;&gt;"",'L3 input'!H82,"")</f>
         <v/>
       </c>
       <c r="E82" s="76">
-        <f>IF('L3 input'!M82&lt;&gt;"",'L3 input'!M82,"")</f>
+        <f>IF('L3 input'!N82&lt;&gt;"",'L3 input'!N82,"")</f>
         <v/>
       </c>
       <c r="F82" s="77" t="n"/>
@@ -36898,11 +37173,11 @@
         <v/>
       </c>
       <c r="D83" s="76">
-        <f>IF('L3 input'!G83&lt;&gt;"",'L3 input'!G83,"")</f>
+        <f>IF('L3 input'!H83&lt;&gt;"",'L3 input'!H83,"")</f>
         <v/>
       </c>
       <c r="E83" s="76">
-        <f>IF('L3 input'!M83&lt;&gt;"",'L3 input'!M83,"")</f>
+        <f>IF('L3 input'!N83&lt;&gt;"",'L3 input'!N83,"")</f>
         <v/>
       </c>
       <c r="F83" s="81" t="n"/>
@@ -37245,11 +37520,11 @@
         <v/>
       </c>
       <c r="D84" s="76">
-        <f>IF('L3 input'!G84&lt;&gt;"",'L3 input'!G84,"")</f>
+        <f>IF('L3 input'!H84&lt;&gt;"",'L3 input'!H84,"")</f>
         <v/>
       </c>
       <c r="E84" s="76">
-        <f>IF('L3 input'!M84&lt;&gt;"",'L3 input'!M84,"")</f>
+        <f>IF('L3 input'!N84&lt;&gt;"",'L3 input'!N84,"")</f>
         <v/>
       </c>
       <c r="F84" s="77" t="n"/>
@@ -37592,11 +37867,11 @@
         <v/>
       </c>
       <c r="D85" s="76">
-        <f>IF('L3 input'!G85&lt;&gt;"",'L3 input'!G85,"")</f>
+        <f>IF('L3 input'!H85&lt;&gt;"",'L3 input'!H85,"")</f>
         <v/>
       </c>
       <c r="E85" s="76">
-        <f>IF('L3 input'!M85&lt;&gt;"",'L3 input'!M85,"")</f>
+        <f>IF('L3 input'!N85&lt;&gt;"",'L3 input'!N85,"")</f>
         <v/>
       </c>
       <c r="F85" s="81" t="n"/>
@@ -37939,11 +38214,11 @@
         <v/>
       </c>
       <c r="D86" s="76">
-        <f>IF('L3 input'!G86&lt;&gt;"",'L3 input'!G86,"")</f>
+        <f>IF('L3 input'!H86&lt;&gt;"",'L3 input'!H86,"")</f>
         <v/>
       </c>
       <c r="E86" s="76">
-        <f>IF('L3 input'!M86&lt;&gt;"",'L3 input'!M86,"")</f>
+        <f>IF('L3 input'!N86&lt;&gt;"",'L3 input'!N86,"")</f>
         <v/>
       </c>
       <c r="F86" s="77" t="n"/>
@@ -38286,11 +38561,11 @@
         <v/>
       </c>
       <c r="D87" s="76">
-        <f>IF('L3 input'!G87&lt;&gt;"",'L3 input'!G87,"")</f>
+        <f>IF('L3 input'!H87&lt;&gt;"",'L3 input'!H87,"")</f>
         <v/>
       </c>
       <c r="E87" s="76">
-        <f>IF('L3 input'!M87&lt;&gt;"",'L3 input'!M87,"")</f>
+        <f>IF('L3 input'!N87&lt;&gt;"",'L3 input'!N87,"")</f>
         <v/>
       </c>
       <c r="F87" s="81" t="n"/>
@@ -38633,11 +38908,11 @@
         <v/>
       </c>
       <c r="D88" s="76">
-        <f>IF('L3 input'!G88&lt;&gt;"",'L3 input'!G88,"")</f>
+        <f>IF('L3 input'!H88&lt;&gt;"",'L3 input'!H88,"")</f>
         <v/>
       </c>
       <c r="E88" s="76">
-        <f>IF('L3 input'!M88&lt;&gt;"",'L3 input'!M88,"")</f>
+        <f>IF('L3 input'!N88&lt;&gt;"",'L3 input'!N88,"")</f>
         <v/>
       </c>
       <c r="F88" s="77" t="n"/>
@@ -38980,11 +39255,11 @@
         <v/>
       </c>
       <c r="D89" s="76">
-        <f>IF('L3 input'!G89&lt;&gt;"",'L3 input'!G89,"")</f>
+        <f>IF('L3 input'!H89&lt;&gt;"",'L3 input'!H89,"")</f>
         <v/>
       </c>
       <c r="E89" s="76">
-        <f>IF('L3 input'!M89&lt;&gt;"",'L3 input'!M89,"")</f>
+        <f>IF('L3 input'!N89&lt;&gt;"",'L3 input'!N89,"")</f>
         <v/>
       </c>
       <c r="F89" s="81" t="n"/>
@@ -39327,11 +39602,11 @@
         <v/>
       </c>
       <c r="D90" s="76">
-        <f>IF('L3 input'!G90&lt;&gt;"",'L3 input'!G90,"")</f>
+        <f>IF('L3 input'!H90&lt;&gt;"",'L3 input'!H90,"")</f>
         <v/>
       </c>
       <c r="E90" s="76">
-        <f>IF('L3 input'!M90&lt;&gt;"",'L3 input'!M90,"")</f>
+        <f>IF('L3 input'!N90&lt;&gt;"",'L3 input'!N90,"")</f>
         <v/>
       </c>
       <c r="F90" s="77" t="n"/>
@@ -39674,11 +39949,11 @@
         <v/>
       </c>
       <c r="D91" s="76">
-        <f>IF('L3 input'!G91&lt;&gt;"",'L3 input'!G91,"")</f>
+        <f>IF('L3 input'!H91&lt;&gt;"",'L3 input'!H91,"")</f>
         <v/>
       </c>
       <c r="E91" s="76">
-        <f>IF('L3 input'!M91&lt;&gt;"",'L3 input'!M91,"")</f>
+        <f>IF('L3 input'!N91&lt;&gt;"",'L3 input'!N91,"")</f>
         <v/>
       </c>
       <c r="F91" s="81" t="n"/>
@@ -40021,11 +40296,11 @@
         <v/>
       </c>
       <c r="D92" s="76">
-        <f>IF('L3 input'!G92&lt;&gt;"",'L3 input'!G92,"")</f>
+        <f>IF('L3 input'!H92&lt;&gt;"",'L3 input'!H92,"")</f>
         <v/>
       </c>
       <c r="E92" s="76">
-        <f>IF('L3 input'!M92&lt;&gt;"",'L3 input'!M92,"")</f>
+        <f>IF('L3 input'!N92&lt;&gt;"",'L3 input'!N92,"")</f>
         <v/>
       </c>
       <c r="F92" s="77" t="n"/>
@@ -40368,11 +40643,11 @@
         <v/>
       </c>
       <c r="D93" s="76">
-        <f>IF('L3 input'!G93&lt;&gt;"",'L3 input'!G93,"")</f>
+        <f>IF('L3 input'!H93&lt;&gt;"",'L3 input'!H93,"")</f>
         <v/>
       </c>
       <c r="E93" s="76">
-        <f>IF('L3 input'!M93&lt;&gt;"",'L3 input'!M93,"")</f>
+        <f>IF('L3 input'!N93&lt;&gt;"",'L3 input'!N93,"")</f>
         <v/>
       </c>
       <c r="F93" s="81" t="n"/>
@@ -40715,11 +40990,11 @@
         <v/>
       </c>
       <c r="D94" s="76">
-        <f>IF('L3 input'!G94&lt;&gt;"",'L3 input'!G94,"")</f>
+        <f>IF('L3 input'!H94&lt;&gt;"",'L3 input'!H94,"")</f>
         <v/>
       </c>
       <c r="E94" s="76">
-        <f>IF('L3 input'!M94&lt;&gt;"",'L3 input'!M94,"")</f>
+        <f>IF('L3 input'!N94&lt;&gt;"",'L3 input'!N94,"")</f>
         <v/>
       </c>
       <c r="F94" s="77" t="n"/>
@@ -41062,11 +41337,11 @@
         <v/>
       </c>
       <c r="D95" s="76">
-        <f>IF('L3 input'!G95&lt;&gt;"",'L3 input'!G95,"")</f>
+        <f>IF('L3 input'!H95&lt;&gt;"",'L3 input'!H95,"")</f>
         <v/>
       </c>
       <c r="E95" s="76">
-        <f>IF('L3 input'!M95&lt;&gt;"",'L3 input'!M95,"")</f>
+        <f>IF('L3 input'!N95&lt;&gt;"",'L3 input'!N95,"")</f>
         <v/>
       </c>
       <c r="F95" s="81" t="n"/>
@@ -41409,11 +41684,11 @@
         <v/>
       </c>
       <c r="D96" s="76">
-        <f>IF('L3 input'!G96&lt;&gt;"",'L3 input'!G96,"")</f>
+        <f>IF('L3 input'!H96&lt;&gt;"",'L3 input'!H96,"")</f>
         <v/>
       </c>
       <c r="E96" s="76">
-        <f>IF('L3 input'!M96&lt;&gt;"",'L3 input'!M96,"")</f>
+        <f>IF('L3 input'!N96&lt;&gt;"",'L3 input'!N96,"")</f>
         <v/>
       </c>
       <c r="F96" s="77" t="n"/>
@@ -41756,11 +42031,11 @@
         <v/>
       </c>
       <c r="D97" s="76">
-        <f>IF('L3 input'!G97&lt;&gt;"",'L3 input'!G97,"")</f>
+        <f>IF('L3 input'!H97&lt;&gt;"",'L3 input'!H97,"")</f>
         <v/>
       </c>
       <c r="E97" s="76">
-        <f>IF('L3 input'!M97&lt;&gt;"",'L3 input'!M97,"")</f>
+        <f>IF('L3 input'!N97&lt;&gt;"",'L3 input'!N97,"")</f>
         <v/>
       </c>
       <c r="F97" s="81" t="n"/>
@@ -42103,11 +42378,11 @@
         <v/>
       </c>
       <c r="D98" s="76">
-        <f>IF('L3 input'!G98&lt;&gt;"",'L3 input'!G98,"")</f>
+        <f>IF('L3 input'!H98&lt;&gt;"",'L3 input'!H98,"")</f>
         <v/>
       </c>
       <c r="E98" s="76">
-        <f>IF('L3 input'!M98&lt;&gt;"",'L3 input'!M98,"")</f>
+        <f>IF('L3 input'!N98&lt;&gt;"",'L3 input'!N98,"")</f>
         <v/>
       </c>
       <c r="F98" s="77" t="n"/>
@@ -42450,11 +42725,11 @@
         <v/>
       </c>
       <c r="D99" s="76">
-        <f>IF('L3 input'!G99&lt;&gt;"",'L3 input'!G99,"")</f>
+        <f>IF('L3 input'!H99&lt;&gt;"",'L3 input'!H99,"")</f>
         <v/>
       </c>
       <c r="E99" s="76">
-        <f>IF('L3 input'!M99&lt;&gt;"",'L3 input'!M99,"")</f>
+        <f>IF('L3 input'!N99&lt;&gt;"",'L3 input'!N99,"")</f>
         <v/>
       </c>
       <c r="F99" s="81" t="n"/>
@@ -42797,11 +43072,11 @@
         <v/>
       </c>
       <c r="D100" s="76">
-        <f>IF('L3 input'!G100&lt;&gt;"",'L3 input'!G100,"")</f>
+        <f>IF('L3 input'!H100&lt;&gt;"",'L3 input'!H100,"")</f>
         <v/>
       </c>
       <c r="E100" s="76">
-        <f>IF('L3 input'!M100&lt;&gt;"",'L3 input'!M100,"")</f>
+        <f>IF('L3 input'!N100&lt;&gt;"",'L3 input'!N100,"")</f>
         <v/>
       </c>
       <c r="F100" s="77" t="n"/>
@@ -43144,11 +43419,11 @@
         <v/>
       </c>
       <c r="D101" s="76">
-        <f>IF('L3 input'!G101&lt;&gt;"",'L3 input'!G101,"")</f>
+        <f>IF('L3 input'!H101&lt;&gt;"",'L3 input'!H101,"")</f>
         <v/>
       </c>
       <c r="E101" s="76">
-        <f>IF('L3 input'!M101&lt;&gt;"",'L3 input'!M101,"")</f>
+        <f>IF('L3 input'!N101&lt;&gt;"",'L3 input'!N101,"")</f>
         <v/>
       </c>
       <c r="F101" s="81" t="n"/>
@@ -43491,11 +43766,11 @@
         <v/>
       </c>
       <c r="D102" s="76">
-        <f>IF('L3 input'!G102&lt;&gt;"",'L3 input'!G102,"")</f>
+        <f>IF('L3 input'!H102&lt;&gt;"",'L3 input'!H102,"")</f>
         <v/>
       </c>
       <c r="E102" s="76">
-        <f>IF('L3 input'!M102&lt;&gt;"",'L3 input'!M102,"")</f>
+        <f>IF('L3 input'!N102&lt;&gt;"",'L3 input'!N102,"")</f>
         <v/>
       </c>
       <c r="F102" s="77" t="n"/>
@@ -43838,11 +44113,11 @@
         <v/>
       </c>
       <c r="D103" s="76">
-        <f>IF('L3 input'!G103&lt;&gt;"",'L3 input'!G103,"")</f>
+        <f>IF('L3 input'!H103&lt;&gt;"",'L3 input'!H103,"")</f>
         <v/>
       </c>
       <c r="E103" s="76">
-        <f>IF('L3 input'!M103&lt;&gt;"",'L3 input'!M103,"")</f>
+        <f>IF('L3 input'!N103&lt;&gt;"",'L3 input'!N103,"")</f>
         <v/>
       </c>
       <c r="F103" s="81" t="n"/>
@@ -44185,11 +44460,11 @@
         <v/>
       </c>
       <c r="D104" s="76">
-        <f>IF('L3 input'!G104&lt;&gt;"",'L3 input'!G104,"")</f>
+        <f>IF('L3 input'!H104&lt;&gt;"",'L3 input'!H104,"")</f>
         <v/>
       </c>
       <c r="E104" s="76">
-        <f>IF('L3 input'!M104&lt;&gt;"",'L3 input'!M104,"")</f>
+        <f>IF('L3 input'!N104&lt;&gt;"",'L3 input'!N104,"")</f>
         <v/>
       </c>
       <c r="F104" s="77" t="n"/>
@@ -44532,11 +44807,11 @@
         <v/>
       </c>
       <c r="D105" s="76">
-        <f>IF('L3 input'!G105&lt;&gt;"",'L3 input'!G105,"")</f>
+        <f>IF('L3 input'!H105&lt;&gt;"",'L3 input'!H105,"")</f>
         <v/>
       </c>
       <c r="E105" s="76">
-        <f>IF('L3 input'!M105&lt;&gt;"",'L3 input'!M105,"")</f>
+        <f>IF('L3 input'!N105&lt;&gt;"",'L3 input'!N105,"")</f>
         <v/>
       </c>
       <c r="F105" s="81" t="n"/>
@@ -44879,11 +45154,11 @@
         <v/>
       </c>
       <c r="D106" s="76">
-        <f>IF('L3 input'!G106&lt;&gt;"",'L3 input'!G106,"")</f>
+        <f>IF('L3 input'!H106&lt;&gt;"",'L3 input'!H106,"")</f>
         <v/>
       </c>
       <c r="E106" s="76">
-        <f>IF('L3 input'!M106&lt;&gt;"",'L3 input'!M106,"")</f>
+        <f>IF('L3 input'!N106&lt;&gt;"",'L3 input'!N106,"")</f>
         <v/>
       </c>
       <c r="F106" s="77" t="n"/>
@@ -45536,8 +45811,50 @@
           <xm:sqref>F7:LR106</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="expression" priority="112" id="{00000000-000E-0000-000C-00000000000C}">
-            <xm:f>AND(MOD(ROW()-7,50)=0,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
+          <x14:cfRule type="expression" priority="112" id="{00000000-000E-0000-0F00-000000000000}">
+            <xm:f>AND('L3 input'!$C7="Red",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
+            <x14:dxf>
+              <font>
+                <sz val="8"/>
+                <color rgb="FFE74B3B"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFE74B3B"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="114" id="{00000000-000E-0000-0F02-000000000002}">
+            <xm:f>AND('L3 input'!$C7="Yellow",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
+            <x14:dxf>
+              <font>
+                <sz val="8"/>
+                <color rgb="FFFFC000"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFC000"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="115" id="{00000000-000E-0000-0F03-000000000003}">
+            <xm:f>AND('L3 input'!$C7="Green",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
+            <x14:dxf>
+              <font>
+                <sz val="8"/>
+                <color rgb="FF70AD47"/>
+              </font>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FF70AD47"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <x14:cfRule type="expression" priority="116" id="{00000000-000E-0000-0F04-000000000004}">
+            <xm:f>AND('L3 input'!$C7="Blue",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
             <x14:dxf>
               <font>
                 <sz val="8"/>
@@ -45550,64 +45867,8 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="113" id="{00000000-000E-0000-000D-00000000000D}">
-            <xm:f>AND(MOD(ROW()-7,50)=1,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFED7D31"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFED7D31"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="114" id="{00000000-000E-0000-000E-00000000000E}">
-            <xm:f>AND(MOD(ROW()-7,50)=2,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF70AD47"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF70AD47"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="115" id="{00000000-000E-0000-000F-00000000000F}">
-            <xm:f>AND(MOD(ROW()-7,50)=3,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFFC000"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFC000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="116" id="{00000000-000E-0000-0010-000000000010}">
-            <xm:f>AND(MOD(ROW()-7,50)=4,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFF6B6B"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF6B6B"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="117" id="{00000000-000E-0000-0011-000000000011}">
-            <xm:f>AND(MOD(ROW()-7,50)=5,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
+          <x14:cfRule type="expression" priority="117" id="{00000000-000E-0000-0F05-000000000005}">
+            <xm:f>AND('L3 input'!$C7="Purple",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
             <x14:dxf>
               <font>
                 <sz val="8"/>
@@ -45620,618 +45881,16 @@
               </fill>
             </x14:dxf>
           </x14:cfRule>
-          <x14:cfRule type="expression" priority="118" id="{00000000-000E-0000-0012-000000000012}">
-            <xm:f>AND(MOD(ROW()-7,50)=6,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
+          <x14:cfRule type="expression" priority="118" id="{00000000-000E-0000-0F06-000000000006}">
+            <xm:f>AND('L3 input'!$C7="",'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$J7*100+'L3 input'!$I7),(F$4*100+F$6)&lt;=('L3 input'!$L7*100+'L3 input'!$K7))</xm:f>
             <x14:dxf>
               <font>
                 <sz val="8"/>
-                <color rgb="FF00BCD4"/>
+                <color rgb="FF98A2B3"/>
               </font>
               <fill>
                 <patternFill>
-                  <bgColor rgb="FF00BCD4"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="119" id="{00000000-000E-0000-0013-000000000013}">
-            <xm:f>AND(MOD(ROW()-7,50)=7,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFE74B3B"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFE74B3B"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="120" id="{00000000-000E-0000-0014-000000000014}">
-            <xm:f>AND(MOD(ROW()-7,50)=8,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF2ECC71"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF2ECC71"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="121" id="{00000000-000E-0000-0015-000000000015}">
-            <xm:f>AND(MOD(ROW()-7,50)=9,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFF39C12"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFF39C12"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="122" id="{00000000-000E-0000-0016-000000000016}">
-            <xm:f>AND(MOD(ROW()-7,50)=10,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF5B9BD5"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF5B9BD5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="123" id="{00000000-000E-0000-0017-000000000017}">
-            <xm:f>AND(MOD(ROW()-7,50)=11,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFA9D18E"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFA9D18E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="124" id="{00000000-000E-0000-0018-000000000018}">
-            <xm:f>AND(MOD(ROW()-7,50)=12,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFE91E63"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFE91E63"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="125" id="{00000000-000E-0000-0019-000000000019}">
-            <xm:f>AND(MOD(ROW()-7,50)=13,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF1ABC9C"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF1ABC9C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="126" id="{00000000-000E-0000-001A-00000000001A}">
-            <xm:f>AND(MOD(ROW()-7,50)=14,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF3498DB"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF3498DB"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="127" id="{00000000-000E-0000-001B-00000000001B}">
-            <xm:f>AND(MOD(ROW()-7,50)=15,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF7030A0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF7030A0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="128" id="{00000000-000E-0000-001C-00000000001C}">
-            <xm:f>AND(MOD(ROW()-7,50)=16,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF00B0F0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF00B0F0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="129" id="{00000000-000E-0000-001D-00000000001D}">
-            <xm:f>AND(MOD(ROW()-7,50)=17,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFF0000"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF0000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="130" id="{00000000-000E-0000-001E-00000000001E}">
-            <xm:f>AND(MOD(ROW()-7,50)=18,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF92D050"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF92D050"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="131" id="{00000000-000E-0000-001F-00000000001F}">
-            <xm:f>AND(MOD(ROW()-7,50)=19,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF4BACC6"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF4BACC6"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="132" id="{00000000-000E-0000-0020-000000000020}">
-            <xm:f>AND(MOD(ROW()-7,50)=20,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFC55A11"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC55A11"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="133" id="{00000000-000E-0000-0021-000000000021}">
-            <xm:f>AND(MOD(ROW()-7,50)=21,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF4A8136"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF4A8136"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="134" id="{00000000-000E-0000-0022-000000000022}">
-            <xm:f>AND(MOD(ROW()-7,50)=22,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF843C0C"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF843C0C"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="135" id="{00000000-000E-0000-0023-000000000023}">
-            <xm:f>AND(MOD(ROW()-7,50)=23,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF2E75B6"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF2E75B6"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="136" id="{00000000-000E-0000-0024-000000000024}">
-            <xm:f>AND(MOD(ROW()-7,50)=24,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF833C00"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF833C00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="137" id="{00000000-000E-0000-0025-000000000025}">
-            <xm:f>AND(MOD(ROW()-7,50)=25,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFBF8E00"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFBF8E00"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="138" id="{00000000-000E-0000-0026-000000000026}">
-            <xm:f>AND(MOD(ROW()-7,50)=26,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF375623"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF375623"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="139" id="{00000000-000E-0000-0027-000000000027}">
-            <xm:f>AND(MOD(ROW()-7,50)=27,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF1F3864"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF1F3864"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="140" id="{00000000-000E-0000-0028-000000000028}">
-            <xm:f>AND(MOD(ROW()-7,50)=28,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFC00000"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC00000"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="141" id="{00000000-000E-0000-0029-000000000029}">
-            <xm:f>AND(MOD(ROW()-7,50)=29,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF2C5494"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF2C5494"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="142" id="{00000000-000E-0000-002A-00000000002A}">
-            <xm:f>AND(MOD(ROW()-7,50)=30,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFF4B183"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFF4B183"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="143" id="{00000000-000E-0000-002B-00000000002B}">
-            <xm:f>AND(MOD(ROW()-7,50)=31,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFA9D18E"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFA9D18E"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="144" id="{00000000-000E-0000-002C-00000000002C}">
-            <xm:f>AND(MOD(ROW()-7,50)=32,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFF99CC"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF99CC"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="145" id="{00000000-000E-0000-002D-00000000002D}">
-            <xm:f>AND(MOD(ROW()-7,50)=33,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFD6DEE9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFD6DEE9"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="146" id="{00000000-000E-0000-002E-00000000002E}">
-            <xm:f>AND(MOD(ROW()-7,50)=34,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFB4C6E7"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFB4C6E7"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="147" id="{00000000-000E-0000-002F-00000000002F}">
-            <xm:f>AND(MOD(ROW()-7,50)=35,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFFD966"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFFD966"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="148" id="{00000000-000E-0000-0030-000000000030}">
-            <xm:f>AND(MOD(ROW()-7,50)=36,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFC9C9C9"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFC9C9C9"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="149" id="{00000000-000E-0000-0031-000000000031}">
-            <xm:f>AND(MOD(ROW()-7,50)=37,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF70AD47"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF70AD47"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="150" id="{00000000-000E-0000-0032-000000000032}">
-            <xm:f>AND(MOD(ROW()-7,50)=38,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFED7D31"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFED7D31"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="151" id="{00000000-000E-0000-0033-000000000033}">
-            <xm:f>AND(MOD(ROW()-7,50)=39,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF4472C4"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF4472C4"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="152" id="{00000000-000E-0000-0034-000000000034}">
-            <xm:f>AND(MOD(ROW()-7,50)=40,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF7030A0"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF7030A0"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="153" id="{00000000-000E-0000-0035-000000000035}">
-            <xm:f>AND(MOD(ROW()-7,50)=41,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFFF6B6B"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFFF6B6B"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="154" id="{00000000-000E-0000-0036-000000000036}">
-            <xm:f>AND(MOD(ROW()-7,50)=42,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF00BCD4"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF00BCD4"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="155" id="{00000000-000E-0000-0037-000000000037}">
-            <xm:f>AND(MOD(ROW()-7,50)=43,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF2ECC71"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF2ECC71"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="156" id="{00000000-000E-0000-0038-000000000038}">
-            <xm:f>AND(MOD(ROW()-7,50)=44,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFF39C12"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFF39C12"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="157" id="{00000000-000E-0000-0039-000000000039}">
-            <xm:f>AND(MOD(ROW()-7,50)=45,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FFE74B3B"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FFE74B3B"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="158" id="{00000000-000E-0000-003A-00000000003A}">
-            <xm:f>AND(MOD(ROW()-7,50)=46,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF9B59B6"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF9B59B6"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="159" id="{00000000-000E-0000-003B-00000000003B}">
-            <xm:f>AND(MOD(ROW()-7,50)=47,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF3498DB"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF3498DB"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="160" id="{00000000-000E-0000-003C-00000000003C}">
-            <xm:f>AND(MOD(ROW()-7,50)=48,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF5B9BD5"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF5B9BD5"/>
-                </patternFill>
-              </fill>
-            </x14:dxf>
-          </x14:cfRule>
-          <x14:cfRule type="expression" priority="161" id="{00000000-000E-0000-003D-00000000003D}">
-            <xm:f>AND(MOD(ROW()-7,50)=49,'L3 input'!$E7&lt;&gt;"",(F$4*100+F$6)&gt;=('L3 input'!$I7*100+'L3 input'!$H7),(F$4*100+F$6)&lt;=('L3 input'!$K7*100+'L3 input'!$J7))</xm:f>
-            <x14:dxf>
-              <font>
-                <sz val="8"/>
-                <color rgb="FF4472C4"/>
-              </font>
-              <fill>
-                <patternFill>
-                  <bgColor rgb="FF4472C4"/>
+                  <bgColor rgb="FF98A2B3"/>
                 </patternFill>
               </fill>
             </x14:dxf>
